--- a/scripts/ffn_l2/performance.xlsx
+++ b/scripts/ffn_l2/performance.xlsx
@@ -9,13 +9,18 @@
   <sheets>
     <sheet name="Models" sheetId="1" r:id="rId1"/>
     <sheet name="Ensemble" sheetId="2" r:id="rId2"/>
+    <sheet name="Ensemble optspreads" sheetId="3" r:id="rId3"/>
+    <sheet name="Ensemble opt-undspreads" sheetId="4" r:id="rId4"/>
+    <sheet name="Returns Long-Short 30-min" sheetId="5" r:id="rId5"/>
+    <sheet name="Returns Long-Short Daily" sheetId="6" r:id="rId6"/>
+    <sheet name="Returns Long-Short Weekly" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="472">
   <si>
     <t>Model</t>
   </si>
@@ -149,7 +154,1288 @@
     <t>H-L 10 portfolios, 0 turnover</t>
   </si>
   <si>
-    <t>[nan, nan]</t>
+    <t>[np.float64(0.00038481674607490196), np.float64(8.28011412985634e-31)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0004807296446980497), np.float64(0.8088022768222183)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.2842628825720335), np.float64(0.19941403830304955)]</t>
+  </si>
+  <si>
+    <t>delta_change_mean</t>
+  </si>
+  <si>
+    <t>delta_change_std</t>
+  </si>
+  <si>
+    <t>turnover_mean</t>
+  </si>
+  <si>
+    <t>turnover_std</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>inf</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.002921836742931771), np.float64(0.060753146584595664)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0034146312246807467), np.float64(0.10025403530704047)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0013606111171182388), np.float64(0.2440431358025614)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0016979701957197198), np.float64(0.46641131573107575)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0024598673434988866), np.float64(0.004737313816119646)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005143185923558299), np.float64(0.003228419635257749)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.012901588970501861), np.float64(0.003077453784330646)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.025769992385367622), np.float64(0.0030851308960180564)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.06509037438919943), np.float64(0.0034255995306865608)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.1273285515235829), np.float64(0.0016887399728852332)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0001000546998576493), np.float64(0.8116451034358028)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0004301000866872596), np.float64(0.4304969377549113)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0010130557905428477), np.float64(0.11815291946908621)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.002812195710572074), np.float64(0.030091348895770274)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.006088156167277729), np.float64(0.01882898529247525)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.012287953255336609), np.float64(0.017292867145844822)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.030624141756641313), np.float64(0.018004712095476154)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.05980825313191561), np.float64(0.01848431677223642)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.15060988411636625), np.float64(0.01968841462594211)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.29273562550612525), np.float64(0.014087654163783242)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0004267898429528826), np.float64(4.699585187637357e-17)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00022230847306452166), np.float64(6.765606480448053e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-5.640713524710103e-05), np.float64(0.3889004324568537)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00048013490280671297), np.float64(6.803414174107267e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.001185053379657178), np.float64(4.262189946512901e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0024019731335388783), np.float64(2.2647366692149106e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005765430021533734), np.float64(6.035504666339976e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.011244111395133262), np.float64(1.0242548192853885e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.027624318968130775), np.float64(1.2321734227746097e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.05355529468156108), np.float64(1.6357511912830659e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-9.639244189872022e-05), np.float64(0.39356344664195775)]</t>
+  </si>
+  <si>
+    <t>[np.float64(5.0180387830175585e-05), np.float64(0.719933958652874)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00020288456532922372), np.float64(0.24169985233103966)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0007370459136185712), np.float64(0.03149051734527224)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0016350648608453651), np.float64(0.015583474911352499)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0031585263179894213), np.float64(0.019363747077981584)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.007584793028780016), np.float64(0.02464370322819527)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.01485314826346237), np.float64(0.027754737608586964)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.03645216709570714), np.float64(0.027401965092865306)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.07604697832693724), np.float64(0.039315871945596575)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00011251513950960952), np.float64(0.05786651059014933)]</t>
+  </si>
+  <si>
+    <t>[np.float64(8.136962915365695e-06), np.float64(0.9050970372492975)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.4972122996273455e-05), np.float64(0.6162793939747413)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.000315718539253723), np.float64(1.0503050411548673e-08)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0005048103015857443), np.float64(2.0641581836260573e-08)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0008141158515993841), np.float64(7.959734814651467e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0015065191158204604), np.float64(0.00015758066112572702)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.002567442360460408), np.float64(0.0009980280351982419)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005621123673395095), np.float64(0.005134926251346304)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.010682166857952048), np.float64(0.005235687258892224)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00021426284351757334), np.float64(3.487478916147466e-19)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00025750418458371423), np.float64(5.29797935645101e-22)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00028957159005448587), np.float64(2.475008407901147e-24)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0003848167470441362), np.float64(8.280110022095287e-31)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00047331295680234177), np.float64(1.7962212181038553e-35)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0005449739744887237), np.float64(1.433288939448126e-37)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0006427453075924028), np.float64(4.923112817990861e-36)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0007469235717831822), np.float64(2.5861551735930144e-33)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0008895827515088727), np.float64(3.8014386273962426e-27)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0010311941698842777), np.float64(8.396424427748054e-24)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.233375653356294), np.float64(0.016225330497276202)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.31871216719831064), np.float64(0.01378919925444596)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.20334757788327662), np.float64(0.005395712497395623)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.40538821678459197), np.float64(0.005621061800574882)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.07293910995170741), np.float64(0.17862505717306196)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.1538403114277893), np.float64(0.15479318634193168)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.3995465370500252), np.float64(0.13407129410967647)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.9370090737362666), np.float64(0.07605576128554366)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.0649716847344006), np.float64(0.11869635091329603)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.673200719472579), np.float64(0.11689754837961892)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00019329885799518519), np.float64(0.9940980915683371)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.004785037573549373), np.float64(0.8877775532984835)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00451819198392472), np.float64(0.9109601989030094)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.015786412018125126), np.float64(0.8459475546978059)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.029079049202551235), np.float64(0.8566818625914269)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.04575938254219346), np.float64(0.885927390394521)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.15322909609121546), np.float64(0.8465451612857807)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.5761349689756132), np.float64(0.7094928830793666)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.1716532592711713), np.float64(0.7600729051089041)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.75012786530236), np.float64(0.7996688232693429)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.003316222245725002), np.float64(0.2844880100466502)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.004461633610763771), np.float64(0.19651576773758683)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.004771371492203413), np.float64(0.2433450636355704)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.010222403872073961), np.float64(0.174460808620525)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.015150767336118939), np.float64(0.2960789757703376)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.02544765675978626), np.float64(0.3710791429934825)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.05258443881815485), np.float64(0.45413135071984484)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.10229679086329492), np.float64(0.4618997346351354)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.20717332667988808), np.float64(0.5373745871531267)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.3948502829443774), np.float64(0.5273640712395942)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0029954145563763656), np.float64(0.6697458401391886)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.001476639662866), np.float64(0.8653999085581323)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0014631720660667623), np.float64(0.8925180391483497)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005408323314475527), np.float64(0.8006610132154117)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.001209332648314716), np.float64(0.9770000156748567)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.007426953650332405), np.float64(0.9289681372240591)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.04978119217257641), np.float64(0.8092488612898593)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.13216384563268005), np.float64(0.7461562529534214)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.36445747086069674), np.float64(0.7059890813548078)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.8794388274724293), np.float64(0.6723507053780338)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.009586282705995337), np.float64(0.00944436745895372)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.010870234969037683), np.float64(0.01057834932936585)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.007677740291831709), np.float64(0.07778287187616077)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.001626544973166801), np.float64(0.6326131119722461)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00549717375898141), np.float64(0.3195218056438854)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.002909194891488088), np.float64(0.7728772116757654)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.008037598929764007), np.float64(0.7397691273952581)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.013740703342096235), np.float64(0.7711148020820936)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.04398288430418333), np.float64(0.70927800825177)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.016479326380776666), np.float64(0.9384950962114582)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0008520668869899614), np.float64(0.5566812910443573)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.000855357970034898), np.float64(0.5958234138465812)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0008213227986630445), np.float64(0.631313784401901)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00048072961486585474), np.float64(0.8088022881778023)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0005561108585812694), np.float64(0.805145922540489)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0008473176651228288), np.float64(0.7336146637169347)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0011610360805758876), np.float64(0.6980784425873622)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00015865457995655225), np.float64(0.9646667682565357)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0005913749566027685), np.float64(0.8992625833692156)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00024184555934525815), np.float64(0.9661935380077358)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.350888567793097), np.float64(0.018965432518320356)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.9987921376204307), np.float64(0.04596174030219128)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.8283382945362059), np.float64(0.06786327582670613)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.9890486046926102), np.float64(0.3229321815255814)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.5766869429824975), np.float64(0.11525468050611289)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.4690672570016026), np.float64(0.01375010590073755)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.857641836465013), np.float64(0.0043764868200524614)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.967447560747297), np.float64(0.0030904661301306086)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.9722020247585803), np.float64(0.0030435160792824253)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.177052040523508), np.float64(0.001543721726812883)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.7391403094318527), np.float64(0.08238673329932734)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.9155100388279585), np.float64(0.36019406649983166)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.13951391660151505), np.float64(0.8890784433939385)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.2732853885042983), np.float64(0.2032789498246581)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.9471502477104645), np.float64(0.05185903217212727)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.2182268960135785), np.float64(0.026813613005210336)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.3180174496170554), np.float64(0.020694502385778975)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.3510248672380802), np.float64(0.018958534786416254)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.34223978856084), np.float64(0.019407643067169945)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.4671834647868978), np.float64(0.013822108973285762)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.7117321455384897), np.float64(0.006833879156919542)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.4307161134420747), np.float64(0.015283241985075163)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.1223592985622104), np.float64(0.03410783556663792)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.0159562167951701), np.float64(0.30995100054308633)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.31397695527573954), np.float64(0.753618692504208)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.12756516044374), np.float64(0.03367203910878841)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.92605043516552), np.float64(9.363258834856942e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.485028682881722), np.float64(8.333846644018014e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.764091831135486), np.float64(2.2446540160510472e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.789658978427653), np.float64(1.983616047853314e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.087220524670204), np.float64(0.03717757568210283)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.8678188758648322), np.float64(0.062145131635243364)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.5648951791400085), np.float64(0.1179947179607029)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.5652158072942761), np.float64(0.5720821577524687)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.6666470741444227), np.float64(0.5051858039542879)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.4873055592352291), np.float64(0.13731995011197504)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.9423522337541368), np.float64(0.0524377923662061)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.0574581916530734), np.float64(0.039959031534919115)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.1417823428511484), np.float64(0.03250611142369203)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.019158701002277), np.float64(0.043796865802671794)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.170043674704619), np.float64(0.03029103601927404)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.998098566416061), np.float64(0.046037026091176624)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.927709725656274), np.float64(0.05423758992798123)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.4427052416959285), np.float64(0.14948678208712574)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.046385286321954), np.float64(0.2956926552885384)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.3930604220961345), np.float64(0.6943773931905713)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.6587717418599036), np.float64(0.5102279661462656)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.7554603724479512), np.float64(0.07955533259373596)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.274821003697977), np.float64(0.023175041685863852)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.466775322446947), np.float64(0.013837753046867947)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.5334090803167348), np.float64(0.12556221811404591)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.4672496161311874), np.float64(0.14269299316119752)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.4130078859194712), np.float64(0.15803425196003396)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.284262879192827), np.float64(0.19941403948445044)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.0103099883851203), np.float64(0.3126459123296328)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.9536269661710186), np.float64(0.34055455413312513)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.7217444650601559), np.float64(0.470658102582927)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.5435372560764787), np.float64(0.586908220346307)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.5158766496227412), np.float64(0.606080139117097)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.5845341302129613), np.float64(0.5590223833296568)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.003955631121632965), np.float64(0.07521885062718534)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.005198808640860126), np.float64(0.10311538065946835)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0021329466068026296), np.float64(0.22551837172362196)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0019261839328877), np.float64(0.42664900353495533)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0022788592980102465), np.float64(0.000966991535687914)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00479167442794286), np.float64(0.0005600374433877758)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.012334933835328252), np.float64(0.001313255068993156)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.02554518541186909), np.float64(0.002926595502525131)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.06393456794531999), np.float64(0.002812860284167571)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.12652882395665926), np.float64(0.0016780830404557162)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00026851121550249273), np.float64(0.38110747413982515)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00015131135979159254), np.float64(0.6793068063257762)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0006857098033461435), np.float64(0.10021339269946312)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.002347213382973139), np.float64(0.0104540497725595)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005673588190576368), np.float64(0.016095801683547396)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.010535575170152292), np.float64(0.005795223836818929)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.02529850394868318), np.float64(0.004546022387198297)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.051495184380728906), np.float64(0.006503300336244617)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.13324320987994379), np.float64(0.012581329900638207)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.28197584931473474), np.float64(0.015347550350290257)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0003970551245202287), np.float64(0.00011335262566335531)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00011450401555480174), np.float64(0.3554484927960575)]</t>
+  </si>
+  <si>
+    <t>[np.float64(6.807901076836174e-05), np.float64(0.6570723306132875)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0004644632962621147), np.float64(0.00010672475995305048)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.001165533499716346), np.float64(5.182328445478472e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.002373590646006011), np.float64(2.117535986879587e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005701607630096754), np.float64(5.51222561362519e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.011149749093037169), np.float64(9.380248420070679e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.02730644098337458), np.float64(1.065454142787402e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.05284322908702431), np.float64(1.4827390836112442e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0001462557029152626), np.float64(0.15695624357937066)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.293227260996914e-05), np.float64(0.8663049914572573)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00017307484244817413), np.float64(0.29222062564372736)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0006790988999453588), np.float64(0.024608088812017953)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0015595285191015201), np.float64(0.010452056713636328)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0030134775181201974), np.float64(0.013665252223468032)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.007206482976986571), np.float64(0.018119806214695028)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.014369651303515345), np.float64(0.021943601278523114)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.035673324775333595), np.float64(0.025424681715116942)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0673740432691266), np.float64(0.021036471267878054)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0001494330006865607), np.float64(0.02990965691544904)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.3558182398341243e-05), np.float64(0.7704306440892206)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-5.726943412421989e-06), np.float64(0.9456260706197035)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00028823492502003334), np.float64(3.103606498294752e-08)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0005080586603845157), np.float64(4.3704086115813135e-09)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.000789980188242739), np.float64(7.957898277648033e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0014547758606580448), np.float64(0.0001753080328839033)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0025128466359574217), np.float64(0.0010315933069207435)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005461214929338189), np.float64(0.005096306894187122)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.010459354407951283), np.float64(0.005502093621651317)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00020841497621338368), np.float64(2.6627664845384996e-18)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0002518912398298224), np.float64(3.0710644018073888e-21)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0002837134337441948), np.float64(1.450395216026572e-23)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0003806589910565522), np.float64(3.1516029687224803e-30)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0004699777966385883), np.float64(8.611487990605447e-35)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0005412685373523158), np.float64(6.655647895396772e-37)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0006339618023169746), np.float64(7.868875689388644e-35)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0007348118229057813), np.float64(2.5231998551039424e-32)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.000884798153634328), np.float64(9.246157348649353e-27)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0010146775727800234), np.float64(1.4390809350117018e-22)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.32495224557967706), np.float64(0.01905781702550747)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.4942906266724865), np.float64(0.012780595645382307)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.3036439523517386), np.float64(0.005778483103491846)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.42152067918593344), np.float64(0.005553715016136329)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.05398300119937544), np.float64(0.2083344784991545)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.1190610500666124), np.float64(0.16478312254112304)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.3507720622066932), np.float64(0.13480660333006433)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.9004169591736105), np.float64(0.08347370810722797)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.014403782454828), np.float64(0.11339191826363212)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.549929605754027), np.float64(0.12469660025450689)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.005254254472875635), np.float64(0.7827467896659207)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0024374409186749416), np.float64(0.9146014038828817)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.005500947848775842), np.float64(0.8323033193029727)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00034878986879589337), np.float64(0.9951399518397974)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.01774514132027061), np.float64(0.9033929915085341)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00078484449170514), np.float64(0.9973433542179936)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0033296135972552647), np.float64(0.9951189431050289)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.2139128363205471), np.float64(0.8523941073951486)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.5341217570754531), np.float64(0.8663723896163256)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.7742599865809603), np.float64(0.7924084049522409)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00011742991726243543), np.float64(0.9852997344605924)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0006367924598226096), np.float64(0.9341242447062482)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0011721087091901886), np.float64(0.902474394281162)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.010277140020235968), np.float64(0.16960235443557034)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.015739773889320074), np.float64(0.27320258232783534)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.02511430334798823), np.float64(0.3695363300348747)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.054253616792812834), np.float64(0.43151414168420454)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.10819854367679829), np.float64(0.4296446203171315)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.2137339136562653), np.float64(0.5167110316017397)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.4625085935734777), np.float64(0.45576311275170095)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00028980359464498114), np.float64(0.9640247232168527)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0018395655016001336), np.float64(0.8280061793127143)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0017555969462712895), np.float64(0.8639890233583353)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00591754110806343), np.float64(0.7532637294274347)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.001349422936381803), np.float64(0.9715056460773688)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.006847780932587163), np.float64(0.9274854551060617)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.04629859217643816), np.float64(0.8035606885394755)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.14112940985494937), np.float64(0.710110883686843)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.3573687868334361), np.float64(0.7011118965297652)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.6425470564087333), np.float64(0.6964679362271001)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.01204000192793517), np.float64(0.0049177263098561875)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.01258343700548697), np.float64(0.012218822740671166)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.01005664920782241), np.float64(0.05461438184363754)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00478740685796666), np.float64(0.13574430036713936)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.003529458498082669), np.float64(0.504413067305287)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.004416050864827471), np.float64(0.6507618662184955)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.01182206643518256), np.float64(0.6153104281956394)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.01545494896323292), np.float64(0.7378083841907158)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.06308287429492057), np.float64(0.5799158334638375)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.012312476199394245), np.float64(0.9535604562587128)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0008688699530608666), np.float64(0.5487768262151611)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0008918344920232083), np.float64(0.5796943383689033)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0008746756922599274), np.float64(0.6086698164806503)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.000779228133079601), np.float64(0.6948282320961058)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0008047804770515978), np.float64(0.7220853977699069)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0010991930666889886), np.float64(0.6599140466599743)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0010446152652456538), np.float64(0.7278747037910694)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00011518759636649146), np.float64(0.9742132722835335)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0005875237666844771), np.float64(0.8994779546885118)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00032856762298493863), np.float64(0.9545333252864227)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.102860677127793), np.float64(0.03578329875870556)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.815501777855401), np.float64(0.06981331866024303)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.6371000497939197), np.float64(0.10199465676571771)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.0403672967444335), np.float64(0.29847706394418294)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.5853984955366875), np.float64(0.11326277835868469)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.783398334025237), np.float64(0.005503481109339003)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.0841908163726997), np.float64(0.0021097606145535166)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.9803064193848505), np.float64(0.002964985572706984)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.0358637555834354), np.float64(0.0024746131491407285)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.1822401181270368), np.float64(0.0015166678832018896)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.1459963071624153), np.float64(0.032167257558978236)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.4787438349299062), np.float64(0.13959422239055969)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.6550784731533754), np.float64(0.5126016232646391)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.2184111953586814), np.float64(0.2234194685297186)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.9524443677802996), np.float64(0.05122665192081672)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.5207589735578995), np.float64(0.011899559786050362)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.752686681500074), np.float64(0.006041941437519257)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.698623238270426), np.float64(0.007106432008637817)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.498406792492804), np.float64(0.012670741116065962)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.4359493108632413), np.float64(0.01506552459445617)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.6689286449766576), np.float64(0.007760305779656183)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.229385580759645), np.float64(0.026059399635924938)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.8621589435655763), np.float64(0.06293950107095593)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.0576512748249831), np.float64(0.29052707252449744)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.27542615884490285), np.float64(0.7830584918111908)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.1097256357936507), np.float64(0.035185560788595374)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.917647033308879), np.float64(9.689365953385587e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.5100479237348114), np.float64(7.430091444103677e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.796446487247832), np.float64(1.9193823918277786e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.815383486642546), np.float64(1.7505812294031483e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.2355982482125634), np.float64(0.02564750236597893)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.9626886749767254), np.float64(0.05002133377300204)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.6500281899392693), np.float64(0.09932153544677928)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.6660736456887794), np.float64(0.5055520503770233)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.6264618161035967), np.float64(0.5311870673099435)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.504194527981221), np.float64(0.13291774557494357)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.02090009997724), np.float64(0.04361583361734881)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.1342610697520072), np.float64(0.03311852861877645)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.1645279735378518), np.float64(0.030712846669673954)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.2646560761036585), np.float64(0.023795033810430143)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.26582068664848), np.float64(0.023723276815010626)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.065839243418576), np.float64(0.03915843460144123)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.0272031540020743), np.float64(0.042965866015903534)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.4867246977207467), np.float64(0.13747333495678152)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.0061109797177015), np.float64(0.31466007014399167)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.40422097359585063), np.float64(0.6861560225924649)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.6395811449606411), np.float64(0.5226242365520296)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.7387223613236555), np.float64(0.08246030517155904)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.276955093344432), np.float64(0.023046676296205815)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.4612560298596726), np.float64(0.014050850467698895)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.5496553578425094), np.float64(0.12161151642689814)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.4858819501559732), np.float64(0.13769610985761208)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.433950276012921), np.float64(0.15196906007002392)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.2956415801960095), np.float64(0.195464930681106)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.0266330061069089), np.float64(0.30489716039351195)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.9423640535383034), np.float64(0.3462848485278241)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.786757510525053), np.float64(0.43165198082682943)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.5550110964962329), np.float64(0.579038986554769)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.5406951925547787), np.float64(0.5888650671197357)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.4197733278898242), np.float64(0.6747614126965494)]</t>
+  </si>
+  <si>
+    <t>Returns</t>
   </si>
 </sst>
 </file>
@@ -1506,10 +2792,6169 @@
         <v>44</v>
       </c>
       <c r="V12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="W12" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P61"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2">
+        <v>0.0008050098240164398</v>
+      </c>
+      <c r="D2">
+        <v>-0.00265940953977406</v>
+      </c>
+      <c r="E2">
+        <v>0.04452139139175415</v>
+      </c>
+      <c r="F2">
+        <v>0.0008665401837788522</v>
+      </c>
+      <c r="G2">
+        <v>0.0009496851125732064</v>
+      </c>
+      <c r="H2">
+        <v>1.000454370655305</v>
+      </c>
+      <c r="I2">
+        <v>0.04907577443927672</v>
+      </c>
+      <c r="J2">
+        <v>-0.05973329767584801</v>
+      </c>
+      <c r="K2">
+        <v>-0.999837338924408</v>
+      </c>
+      <c r="L2">
+        <v>2.548242092132568</v>
+      </c>
+      <c r="M2">
+        <v>-3.418915987014771</v>
+      </c>
+      <c r="N2" t="s">
+        <v>111</v>
+      </c>
+      <c r="O2" t="s">
+        <v>171</v>
+      </c>
+      <c r="P2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3">
+        <v>0.001068991524220685</v>
+      </c>
+      <c r="D3">
+        <v>-0.003045185003429651</v>
+      </c>
+      <c r="E3">
+        <v>0.0593801774084568</v>
+      </c>
+      <c r="F3">
+        <v>0.0009865815518423915</v>
+      </c>
+      <c r="G3">
+        <v>0.001017054892145097</v>
+      </c>
+      <c r="H3">
+        <v>1.000616724338197</v>
+      </c>
+      <c r="I3">
+        <v>0.04905806272360625</v>
+      </c>
+      <c r="J3">
+        <v>-0.0512828528881073</v>
+      </c>
+      <c r="K3">
+        <v>-0.9999542236328125</v>
+      </c>
+      <c r="L3">
+        <v>3.398704767227173</v>
+      </c>
+      <c r="M3">
+        <v>-2.935243368148804</v>
+      </c>
+      <c r="N3" t="s">
+        <v>112</v>
+      </c>
+      <c r="O3" t="s">
+        <v>172</v>
+      </c>
+      <c r="P3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4">
+        <v>0.001329704591007501</v>
+      </c>
+      <c r="D4">
+        <v>-0.001126583316363394</v>
+      </c>
+      <c r="E4">
+        <v>0.03343213349580765</v>
+      </c>
+      <c r="F4">
+        <v>0.00108321791049093</v>
+      </c>
+      <c r="G4">
+        <v>0.001112383906729519</v>
+      </c>
+      <c r="H4">
+        <v>1.000692304937609</v>
+      </c>
+      <c r="I4">
+        <v>0.04913176131150539</v>
+      </c>
+      <c r="J4">
+        <v>-0.03369762003421783</v>
+      </c>
+      <c r="K4">
+        <v>-0.9750973582267761</v>
+      </c>
+      <c r="L4">
+        <v>1.913533329963684</v>
+      </c>
+      <c r="M4">
+        <v>-1.928728818893433</v>
+      </c>
+      <c r="N4" t="s">
+        <v>113</v>
+      </c>
+      <c r="O4" t="s">
+        <v>173</v>
+      </c>
+      <c r="P4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5">
+        <v>0.002604581958073144</v>
+      </c>
+      <c r="D5">
+        <v>-0.001272828434593976</v>
+      </c>
+      <c r="E5">
+        <v>0.06677450984716415</v>
+      </c>
+      <c r="F5">
+        <v>0.00137617823202163</v>
+      </c>
+      <c r="G5">
+        <v>0.001386361429467797</v>
+      </c>
+      <c r="H5">
+        <v>1.000744414544915</v>
+      </c>
+      <c r="I5">
+        <v>0.04928947882008945</v>
+      </c>
+      <c r="J5">
+        <v>-0.01906159147620201</v>
+      </c>
+      <c r="K5">
+        <v>-0.9845868945121765</v>
+      </c>
+      <c r="L5">
+        <v>3.821929216384888</v>
+      </c>
+      <c r="M5">
+        <v>-1.091015934944153</v>
+      </c>
+      <c r="N5" t="s">
+        <v>114</v>
+      </c>
+      <c r="O5" t="s">
+        <v>174</v>
+      </c>
+      <c r="P5" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6">
+        <v>0.005100197251408268</v>
+      </c>
+      <c r="D6">
+        <v>0.002528102835640311</v>
+      </c>
+      <c r="E6">
+        <v>0.02481105551123619</v>
+      </c>
+      <c r="F6">
+        <v>0.001617541187442839</v>
+      </c>
+      <c r="G6">
+        <v>0.001610578503459692</v>
+      </c>
+      <c r="H6">
+        <v>1.000858218780013</v>
+      </c>
+      <c r="I6">
+        <v>0.04941854405254224</v>
+      </c>
+      <c r="J6">
+        <v>0.1018942072987556</v>
+      </c>
+      <c r="K6">
+        <v>3909.853271484375</v>
+      </c>
+      <c r="L6">
+        <v>1.42009425163269</v>
+      </c>
+      <c r="M6">
+        <v>5.832052707672119</v>
+      </c>
+      <c r="N6" t="s">
+        <v>115</v>
+      </c>
+      <c r="O6" t="s">
+        <v>175</v>
+      </c>
+      <c r="P6" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7">
+        <v>0.0100449334737381</v>
+      </c>
+      <c r="D7">
+        <v>0.005269346293061972</v>
+      </c>
+      <c r="E7">
+        <v>0.04976559057831764</v>
+      </c>
+      <c r="F7">
+        <v>0.001875044661574066</v>
+      </c>
+      <c r="G7">
+        <v>0.001896378817036748</v>
+      </c>
+      <c r="H7">
+        <v>1.000993389558299</v>
+      </c>
+      <c r="I7">
+        <v>0.04923069392871805</v>
+      </c>
+      <c r="J7">
+        <v>0.1058833301067352</v>
+      </c>
+      <c r="K7">
+        <v>30004868</v>
+      </c>
+      <c r="L7">
+        <v>2.848400831222534</v>
+      </c>
+      <c r="M7">
+        <v>6.060375213623047</v>
+      </c>
+      <c r="N7" t="s">
+        <v>116</v>
+      </c>
+      <c r="O7" t="s">
+        <v>176</v>
+      </c>
+      <c r="P7" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8">
+        <v>0</v>
+      </c>
+      <c r="B8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8">
+        <v>0.02473045567685658</v>
+      </c>
+      <c r="D8">
+        <v>0.01321171410381794</v>
+      </c>
+      <c r="E8">
+        <v>0.1242461428046227</v>
+      </c>
+      <c r="F8">
+        <v>0.002118287142366171</v>
+      </c>
+      <c r="G8">
+        <v>0.002255836268886924</v>
+      </c>
+      <c r="H8">
+        <v>1.00127246994463</v>
+      </c>
+      <c r="I8">
+        <v>0.04999193635185949</v>
+      </c>
+      <c r="J8">
+        <v>0.1063350066542625</v>
+      </c>
+      <c r="K8">
+        <v>4.719333154588983E+18</v>
+      </c>
+      <c r="L8">
+        <v>7.111395835876465</v>
+      </c>
+      <c r="M8">
+        <v>6.086227893829346</v>
+      </c>
+      <c r="N8" t="s">
+        <v>117</v>
+      </c>
+      <c r="O8" t="s">
+        <v>177</v>
+      </c>
+      <c r="P8" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9">
+        <v>0.04917053167195581</v>
+      </c>
+      <c r="D9">
+        <v>0.02649210393428802</v>
+      </c>
+      <c r="E9">
+        <v>0.2483837902545929</v>
+      </c>
+      <c r="F9">
+        <v>0.002263428876176476</v>
+      </c>
+      <c r="G9">
+        <v>0.002486041281372309</v>
+      </c>
+      <c r="H9">
+        <v>1.001484286925181</v>
+      </c>
+      <c r="I9">
+        <v>0.05079585999257141</v>
+      </c>
+      <c r="J9">
+        <v>0.1066579446196556</v>
+      </c>
+      <c r="K9">
+        <v>1.58857916738681E+37</v>
+      </c>
+      <c r="L9">
+        <v>14.21658134460449</v>
+      </c>
+      <c r="M9">
+        <v>6.104711532592773</v>
+      </c>
+      <c r="N9" t="s">
+        <v>118</v>
+      </c>
+      <c r="O9" t="s">
+        <v>178</v>
+      </c>
+      <c r="P9" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10">
+        <v>0.1236644875638186</v>
+      </c>
+      <c r="D10">
+        <v>0.0665372833609581</v>
+      </c>
+      <c r="E10">
+        <v>0.6342219710350037</v>
+      </c>
+      <c r="F10">
+        <v>0.002465015044435859</v>
+      </c>
+      <c r="G10">
+        <v>0.002919439459219575</v>
+      </c>
+      <c r="H10">
+        <v>1.002447097306338</v>
+      </c>
+      <c r="I10">
+        <v>0.05595834230920001</v>
+      </c>
+      <c r="J10">
+        <v>0.1049116626381874</v>
+      </c>
+      <c r="K10" t="s">
+        <v>110</v>
+      </c>
+      <c r="L10">
+        <v>36.30055236816406</v>
+      </c>
+      <c r="M10">
+        <v>6.0047607421875</v>
+      </c>
+      <c r="N10" t="s">
+        <v>119</v>
+      </c>
+      <c r="O10" t="s">
+        <v>179</v>
+      </c>
+      <c r="P10" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11">
+        <v>0</v>
+      </c>
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11">
+        <v>0.239241328049243</v>
+      </c>
+      <c r="D11">
+        <v>0.1287835240364075</v>
+      </c>
+      <c r="E11">
+        <v>1.156597971916199</v>
+      </c>
+      <c r="F11">
+        <v>0.002610808471217752</v>
+      </c>
+      <c r="G11">
+        <v>0.003328176448121667</v>
+      </c>
+      <c r="H11">
+        <v>1.003794369645043</v>
+      </c>
+      <c r="I11">
+        <v>0.06507012628973952</v>
+      </c>
+      <c r="J11">
+        <v>0.1113468334078789</v>
+      </c>
+      <c r="K11" t="s">
+        <v>110</v>
+      </c>
+      <c r="L11">
+        <v>66.19944763183594</v>
+      </c>
+      <c r="M11">
+        <v>6.373086452484131</v>
+      </c>
+      <c r="N11" t="s">
+        <v>120</v>
+      </c>
+      <c r="O11" t="s">
+        <v>180</v>
+      </c>
+      <c r="P11" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12">
+        <v>0</v>
+      </c>
+      <c r="B12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12">
+        <v>0.001688430682226349</v>
+      </c>
+      <c r="D12">
+        <v>-0.0001002705612336285</v>
+      </c>
+      <c r="E12">
+        <v>0.01196807250380516</v>
+      </c>
+      <c r="F12">
+        <v>0.0008848440484143794</v>
+      </c>
+      <c r="G12">
+        <v>0.0009624735685065389</v>
+      </c>
+      <c r="H12">
+        <v>1.000392906445213</v>
+      </c>
+      <c r="I12">
+        <v>0.04912453952722107</v>
+      </c>
+      <c r="J12">
+        <v>-0.008378171361982822</v>
+      </c>
+      <c r="K12">
+        <v>-0.279962420463562</v>
+      </c>
+      <c r="L12">
+        <v>0.6850088238716125</v>
+      </c>
+      <c r="M12">
+        <v>-0.4795359671115875</v>
+      </c>
+      <c r="N12" t="s">
+        <v>121</v>
+      </c>
+      <c r="O12" t="s">
+        <v>181</v>
+      </c>
+      <c r="P12" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13">
+        <v>0</v>
+      </c>
+      <c r="B13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13">
+        <v>0.00224559421075024</v>
+      </c>
+      <c r="D13">
+        <v>0.0004355991550255567</v>
+      </c>
+      <c r="E13">
+        <v>0.01554691605269909</v>
+      </c>
+      <c r="F13">
+        <v>0.001019286224618554</v>
+      </c>
+      <c r="G13">
+        <v>0.00104432983789593</v>
+      </c>
+      <c r="H13">
+        <v>1.000523442923685</v>
+      </c>
+      <c r="I13">
+        <v>0.049138975350746</v>
+      </c>
+      <c r="J13">
+        <v>0.02801836468279362</v>
+      </c>
+      <c r="K13">
+        <v>3.164867877960205</v>
+      </c>
+      <c r="L13">
+        <v>0.8898487687110901</v>
+      </c>
+      <c r="M13">
+        <v>1.603668928146362</v>
+      </c>
+      <c r="N13" t="s">
+        <v>122</v>
+      </c>
+      <c r="O13" t="s">
+        <v>182</v>
+      </c>
+      <c r="P13" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14">
+        <v>0</v>
+      </c>
+      <c r="B14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14">
+        <v>0.002798683147564644</v>
+      </c>
+      <c r="D14">
+        <v>0.001018193666823208</v>
+      </c>
+      <c r="E14">
+        <v>0.01846519112586975</v>
+      </c>
+      <c r="F14">
+        <v>0.001128526520915329</v>
+      </c>
+      <c r="G14">
+        <v>0.001136953360401094</v>
+      </c>
+      <c r="H14">
+        <v>1.000619917799886</v>
+      </c>
+      <c r="I14">
+        <v>0.04917661293455219</v>
+      </c>
+      <c r="J14">
+        <v>0.05514124780893326</v>
+      </c>
+      <c r="K14">
+        <v>27.0451774597168</v>
+      </c>
+      <c r="L14">
+        <v>1.056880116462708</v>
+      </c>
+      <c r="M14">
+        <v>3.156083822250366</v>
+      </c>
+      <c r="N14" t="s">
+        <v>123</v>
+      </c>
+      <c r="O14" t="s">
+        <v>183</v>
+      </c>
+      <c r="P14" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15">
+        <v>0</v>
+      </c>
+      <c r="B15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15">
+        <v>0.005538566882942568</v>
+      </c>
+      <c r="D15">
+        <v>0.002828667173162103</v>
+      </c>
+      <c r="E15">
+        <v>0.03691790625452995</v>
+      </c>
+      <c r="F15">
+        <v>0.001408818759955466</v>
+      </c>
+      <c r="G15">
+        <v>0.001419564010575414</v>
+      </c>
+      <c r="H15">
+        <v>1.00060838604805</v>
+      </c>
+      <c r="I15">
+        <v>0.04936907574519762</v>
+      </c>
+      <c r="J15">
+        <v>0.07662046700716019</v>
+      </c>
+      <c r="K15">
+        <v>10443.1328125</v>
+      </c>
+      <c r="L15">
+        <v>2.113046169281006</v>
+      </c>
+      <c r="M15">
+        <v>4.385476112365723</v>
+      </c>
+      <c r="N15" t="s">
+        <v>124</v>
+      </c>
+      <c r="O15" t="s">
+        <v>184</v>
+      </c>
+      <c r="P15" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16">
+        <v>0</v>
+      </c>
+      <c r="B16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16">
+        <v>0.01095687059814771</v>
+      </c>
+      <c r="D16">
+        <v>0.006116700358688831</v>
+      </c>
+      <c r="E16">
+        <v>0.07380080223083496</v>
+      </c>
+      <c r="F16">
+        <v>0.001649361220188439</v>
+      </c>
+      <c r="G16">
+        <v>0.001649870071560144</v>
+      </c>
+      <c r="H16">
+        <v>1.00075940882393</v>
+      </c>
+      <c r="I16">
+        <v>0.04948887561097152</v>
+      </c>
+      <c r="J16">
+        <v>0.08288121968507767</v>
+      </c>
+      <c r="K16">
+        <v>474337472</v>
+      </c>
+      <c r="L16">
+        <v>4.224088668823242</v>
+      </c>
+      <c r="M16">
+        <v>4.743818759918213</v>
+      </c>
+      <c r="N16" t="s">
+        <v>125</v>
+      </c>
+      <c r="O16" t="s">
+        <v>185</v>
+      </c>
+      <c r="P16" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17">
+        <v>0</v>
+      </c>
+      <c r="B17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17">
+        <v>0.02169711955796414</v>
+      </c>
+      <c r="D17">
+        <v>0.01232734601944685</v>
+      </c>
+      <c r="E17">
+        <v>0.1470404118299484</v>
+      </c>
+      <c r="F17">
+        <v>0.001905202982015908</v>
+      </c>
+      <c r="G17">
+        <v>0.001915486296638846</v>
+      </c>
+      <c r="H17">
+        <v>1.000942748666821</v>
+      </c>
+      <c r="I17">
+        <v>0.04926228867336591</v>
+      </c>
+      <c r="J17">
+        <v>0.08383645117282867</v>
+      </c>
+      <c r="K17">
+        <v>2.700519786109993E+17</v>
+      </c>
+      <c r="L17">
+        <v>8.416056632995605</v>
+      </c>
+      <c r="M17">
+        <v>4.798492431640625</v>
+      </c>
+      <c r="N17" t="s">
+        <v>126</v>
+      </c>
+      <c r="O17" t="s">
+        <v>186</v>
+      </c>
+      <c r="P17" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18">
+        <v>0</v>
+      </c>
+      <c r="B18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18">
+        <v>0.05392436433725461</v>
+      </c>
+      <c r="D18">
+        <v>0.03075313568115234</v>
+      </c>
+      <c r="E18">
+        <v>0.3688085973262787</v>
+      </c>
+      <c r="F18">
+        <v>0.002132391091436148</v>
+      </c>
+      <c r="G18">
+        <v>0.002282249508425593</v>
+      </c>
+      <c r="H18">
+        <v>1.001250335500441</v>
+      </c>
+      <c r="I18">
+        <v>0.05002228349978139</v>
+      </c>
+      <c r="J18">
+        <v>0.08338508009910583</v>
+      </c>
+      <c r="K18" t="s">
+        <v>110</v>
+      </c>
+      <c r="L18">
+        <v>21.1092586517334</v>
+      </c>
+      <c r="M18">
+        <v>4.772657871246338</v>
+      </c>
+      <c r="N18" t="s">
+        <v>127</v>
+      </c>
+      <c r="O18" t="s">
+        <v>187</v>
+      </c>
+      <c r="P18" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19">
+        <v>0</v>
+      </c>
+      <c r="B19" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19">
+        <v>0.1063815114777297</v>
+      </c>
+      <c r="D19">
+        <v>0.06028300151228905</v>
+      </c>
+      <c r="E19">
+        <v>0.7233588695526123</v>
+      </c>
+      <c r="F19">
+        <v>0.002267488976940513</v>
+      </c>
+      <c r="G19">
+        <v>0.002509228186681867</v>
+      </c>
+      <c r="H19">
+        <v>1.001567051977347</v>
+      </c>
+      <c r="I19">
+        <v>0.05063548513858485</v>
+      </c>
+      <c r="J19">
+        <v>0.08333761245012283</v>
+      </c>
+      <c r="K19" t="s">
+        <v>110</v>
+      </c>
+      <c r="L19">
+        <v>41.40242385864258</v>
+      </c>
+      <c r="M19">
+        <v>4.769940853118896</v>
+      </c>
+      <c r="N19" t="s">
+        <v>128</v>
+      </c>
+      <c r="O19" t="s">
+        <v>188</v>
+      </c>
+      <c r="P19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20">
+        <v>0</v>
+      </c>
+      <c r="B20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20">
+        <v>0.2677224631057048</v>
+      </c>
+      <c r="D20">
+        <v>0.1514396071434021</v>
+      </c>
+      <c r="E20">
+        <v>1.840659499168396</v>
+      </c>
+      <c r="F20">
+        <v>0.002409176900982857</v>
+      </c>
+      <c r="G20">
+        <v>0.00290000275708735</v>
+      </c>
+      <c r="H20">
+        <v>1.002379097850334</v>
+      </c>
+      <c r="I20">
+        <v>0.05599506256775619</v>
+      </c>
+      <c r="J20">
+        <v>0.08227464556694031</v>
+      </c>
+      <c r="K20" t="s">
+        <v>110</v>
+      </c>
+      <c r="L20">
+        <v>105.3526306152344</v>
+      </c>
+      <c r="M20">
+        <v>4.709100723266602</v>
+      </c>
+      <c r="N20" t="s">
+        <v>129</v>
+      </c>
+      <c r="O20" t="s">
+        <v>189</v>
+      </c>
+      <c r="P20" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21">
+        <v>0</v>
+      </c>
+      <c r="B21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21">
+        <v>0.5175115462384302</v>
+      </c>
+      <c r="D21">
+        <v>0.2938013672828674</v>
+      </c>
+      <c r="E21">
+        <v>3.398927688598633</v>
+      </c>
+      <c r="F21">
+        <v>0.002581182168796659</v>
+      </c>
+      <c r="G21">
+        <v>0.003275485476478934</v>
+      </c>
+      <c r="H21">
+        <v>1.003794369645043</v>
+      </c>
+      <c r="I21">
+        <v>0.06507012628973952</v>
+      </c>
+      <c r="J21">
+        <v>0.08643943071365356</v>
+      </c>
+      <c r="K21" t="s">
+        <v>110</v>
+      </c>
+      <c r="L21">
+        <v>194.5422210693359</v>
+      </c>
+      <c r="M21">
+        <v>4.9474778175354</v>
+      </c>
+      <c r="N21" t="s">
+        <v>130</v>
+      </c>
+      <c r="O21" t="s">
+        <v>190</v>
+      </c>
+      <c r="P21" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22">
+        <v>0</v>
+      </c>
+      <c r="B22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22">
+        <v>0.0003891669535100285</v>
+      </c>
+      <c r="D22">
+        <v>-0.0004231484490446746</v>
+      </c>
+      <c r="E22">
+        <v>0.001419267966412008</v>
+      </c>
+      <c r="F22">
+        <v>0.0009149096440523863</v>
+      </c>
+      <c r="G22">
+        <v>0.0009639844647608697</v>
+      </c>
+      <c r="H22">
+        <v>1.000341509601267</v>
+      </c>
+      <c r="I22">
+        <v>0.04916892130688709</v>
+      </c>
+      <c r="J22">
+        <v>-0.2981455624103546</v>
+      </c>
+      <c r="K22">
+        <v>-0.7500459551811218</v>
+      </c>
+      <c r="L22">
+        <v>0.08123371750116348</v>
+      </c>
+      <c r="M22">
+        <v>-17.06476402282715</v>
+      </c>
+      <c r="N22" t="s">
+        <v>131</v>
+      </c>
+      <c r="O22" t="s">
+        <v>191</v>
+      </c>
+      <c r="P22" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23">
+        <v>0</v>
+      </c>
+      <c r="B23" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23">
+        <v>0.0005113454463323638</v>
+      </c>
+      <c r="D23">
+        <v>-0.0002171891246689484</v>
+      </c>
+      <c r="E23">
+        <v>0.001584133366122842</v>
+      </c>
+      <c r="F23">
+        <v>0.0010679941624403</v>
+      </c>
+      <c r="G23">
+        <v>0.001069855876266956</v>
+      </c>
+      <c r="H23">
+        <v>1.00048643517097</v>
+      </c>
+      <c r="I23">
+        <v>0.04917706219726947</v>
+      </c>
+      <c r="J23">
+        <v>-0.137102797627449</v>
+      </c>
+      <c r="K23">
+        <v>-0.5091527700424194</v>
+      </c>
+      <c r="L23">
+        <v>0.09067001193761826</v>
+      </c>
+      <c r="M23">
+        <v>-7.847263813018799</v>
+      </c>
+      <c r="N23" t="s">
+        <v>132</v>
+      </c>
+      <c r="O23" t="s">
+        <v>192</v>
+      </c>
+      <c r="P23" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24">
+        <v>0</v>
+      </c>
+      <c r="B24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24">
+        <v>0.0006293631302697726</v>
+      </c>
+      <c r="D24">
+        <v>-5.098081601317972E-05</v>
+      </c>
+      <c r="E24">
+        <v>0.001867087092250586</v>
+      </c>
+      <c r="F24">
+        <v>0.001173134311102331</v>
+      </c>
+      <c r="G24">
+        <v>0.001170306699350476</v>
+      </c>
+      <c r="H24">
+        <v>1.000526071935172</v>
+      </c>
+      <c r="I24">
+        <v>0.0492237022158057</v>
+      </c>
+      <c r="J24">
+        <v>-0.02730500139296055</v>
+      </c>
+      <c r="K24">
+        <v>-0.1537628769874573</v>
+      </c>
+      <c r="L24">
+        <v>0.1068652495741844</v>
+      </c>
+      <c r="M24">
+        <v>-1.562838673591614</v>
+      </c>
+      <c r="N24" t="s">
+        <v>133</v>
+      </c>
+      <c r="O24" t="s">
+        <v>193</v>
+      </c>
+      <c r="P24" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25">
+        <v>0</v>
+      </c>
+      <c r="B25" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25">
+        <v>0.001187585888634958</v>
+      </c>
+      <c r="D25">
+        <v>0.0004910089774057269</v>
+      </c>
+      <c r="E25">
+        <v>0.00342398090288043</v>
+      </c>
+      <c r="F25">
+        <v>0.001446132315322757</v>
+      </c>
+      <c r="G25">
+        <v>0.001459676423110068</v>
+      </c>
+      <c r="H25">
+        <v>1.000502194462696</v>
+      </c>
+      <c r="I25">
+        <v>0.04945640971917395</v>
+      </c>
+      <c r="J25">
+        <v>0.143402948975563</v>
+      </c>
+      <c r="K25">
+        <v>3.99379825592041</v>
+      </c>
+      <c r="L25">
+        <v>0.1959761679172516</v>
+      </c>
+      <c r="M25">
+        <v>8.20786190032959</v>
+      </c>
+      <c r="N25" t="s">
+        <v>134</v>
+      </c>
+      <c r="O25" t="s">
+        <v>194</v>
+      </c>
+      <c r="P25" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26">
+        <v>0</v>
+      </c>
+      <c r="B26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26">
+        <v>0.00224375161675438</v>
+      </c>
+      <c r="D26">
+        <v>0.001200394006446004</v>
+      </c>
+      <c r="E26">
+        <v>0.006635068450123072</v>
+      </c>
+      <c r="F26">
+        <v>0.001678759814240038</v>
+      </c>
+      <c r="G26">
+        <v>0.00169644202105701</v>
+      </c>
+      <c r="H26">
+        <v>1.000640609481732</v>
+      </c>
+      <c r="I26">
+        <v>0.04961221054909096</v>
+      </c>
+      <c r="J26">
+        <v>0.1809165924787521</v>
+      </c>
+      <c r="K26">
+        <v>49.92097091674805</v>
+      </c>
+      <c r="L26">
+        <v>0.379767119884491</v>
+      </c>
+      <c r="M26">
+        <v>10.35500526428223</v>
+      </c>
+      <c r="N26" t="s">
+        <v>135</v>
+      </c>
+      <c r="O26" t="s">
+        <v>195</v>
+      </c>
+      <c r="P26" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27">
+        <v>0</v>
+      </c>
+      <c r="B27" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27">
+        <v>0.004292482519518729</v>
+      </c>
+      <c r="D27">
+        <v>0.002424856647849083</v>
+      </c>
+      <c r="E27">
+        <v>0.0131371496245265</v>
+      </c>
+      <c r="F27">
+        <v>0.001930125756189227</v>
+      </c>
+      <c r="G27">
+        <v>0.001951037789694965</v>
+      </c>
+      <c r="H27">
+        <v>1.000840737013744</v>
+      </c>
+      <c r="I27">
+        <v>0.049337799884565</v>
+      </c>
+      <c r="J27">
+        <v>0.1845801174640656</v>
+      </c>
+      <c r="K27">
+        <v>2789.978759765625</v>
+      </c>
+      <c r="L27">
+        <v>0.7519224882125854</v>
+      </c>
+      <c r="M27">
+        <v>10.56469249725342</v>
+      </c>
+      <c r="N27" t="s">
+        <v>136</v>
+      </c>
+      <c r="O27" t="s">
+        <v>196</v>
+      </c>
+      <c r="P27" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28">
+        <v>0</v>
+      </c>
+      <c r="B28" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28">
+        <v>0.01034493076620222</v>
+      </c>
+      <c r="D28">
+        <v>0.005809733644127846</v>
+      </c>
+      <c r="E28">
+        <v>0.03273020684719086</v>
+      </c>
+      <c r="F28">
+        <v>0.002137345261871815</v>
+      </c>
+      <c r="G28">
+        <v>0.002297061495482922</v>
+      </c>
+      <c r="H28">
+        <v>1.001223097904029</v>
+      </c>
+      <c r="I28">
+        <v>0.05004695698117403</v>
+      </c>
+      <c r="J28">
+        <v>0.1775037199258804</v>
+      </c>
+      <c r="K28">
+        <v>174559632</v>
+      </c>
+      <c r="L28">
+        <v>1.873357653617859</v>
+      </c>
+      <c r="M28">
+        <v>10.15966510772705</v>
+      </c>
+      <c r="N28" t="s">
+        <v>137</v>
+      </c>
+      <c r="O28" t="s">
+        <v>197</v>
+      </c>
+      <c r="P28" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29">
+        <v>0</v>
+      </c>
+      <c r="B29" t="s">
+        <v>78</v>
+      </c>
+      <c r="C29">
+        <v>0.02030960256679828</v>
+      </c>
+      <c r="D29">
+        <v>0.01133132074028254</v>
+      </c>
+      <c r="E29">
+        <v>0.06519874185323715</v>
+      </c>
+      <c r="F29">
+        <v>0.002249523997306824</v>
+      </c>
+      <c r="G29">
+        <v>0.00253127864561975</v>
+      </c>
+      <c r="H29">
+        <v>1.00161926104584</v>
+      </c>
+      <c r="I29">
+        <v>0.05061322828605944</v>
+      </c>
+      <c r="J29">
+        <v>0.1737966239452362</v>
+      </c>
+      <c r="K29">
+        <v>1.073903744267059E+16</v>
+      </c>
+      <c r="L29">
+        <v>3.731738090515137</v>
+      </c>
+      <c r="M29">
+        <v>9.947484970092773</v>
+      </c>
+      <c r="N29" t="s">
+        <v>138</v>
+      </c>
+      <c r="O29" t="s">
+        <v>198</v>
+      </c>
+      <c r="P29" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30">
+        <v>0.05033193966848683</v>
+      </c>
+      <c r="D30">
+        <v>0.02779472805559635</v>
+      </c>
+      <c r="E30">
+        <v>0.16141177713871</v>
+      </c>
+      <c r="F30">
+        <v>0.002395869698375463</v>
+      </c>
+      <c r="G30">
+        <v>0.002902663080021739</v>
+      </c>
+      <c r="H30">
+        <v>1.002234599006325</v>
+      </c>
+      <c r="I30">
+        <v>0.0559064905600835</v>
+      </c>
+      <c r="J30">
+        <v>0.1721976399421692</v>
+      </c>
+      <c r="K30" t="s">
+        <v>110</v>
+      </c>
+      <c r="L30">
+        <v>9.238620758056641</v>
+      </c>
+      <c r="M30">
+        <v>9.855964660644531</v>
+      </c>
+      <c r="N30" t="s">
+        <v>139</v>
+      </c>
+      <c r="O30" t="s">
+        <v>199</v>
+      </c>
+      <c r="P30" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31">
+        <v>0</v>
+      </c>
+      <c r="B31" t="s">
+        <v>80</v>
+      </c>
+      <c r="C31">
+        <v>0.0980793010383043</v>
+      </c>
+      <c r="D31">
+        <v>0.05388117209076881</v>
+      </c>
+      <c r="E31">
+        <v>0.3167101442813873</v>
+      </c>
+      <c r="F31">
+        <v>0.002510020975023508</v>
+      </c>
+      <c r="G31">
+        <v>0.003188408445566893</v>
+      </c>
+      <c r="H31">
+        <v>1.003794369645043</v>
+      </c>
+      <c r="I31">
+        <v>0.06507012628973952</v>
+      </c>
+      <c r="J31">
+        <v>0.1701277047395706</v>
+      </c>
+      <c r="K31" t="s">
+        <v>110</v>
+      </c>
+      <c r="L31">
+        <v>18.12733268737793</v>
+      </c>
+      <c r="M31">
+        <v>9.737488746643066</v>
+      </c>
+      <c r="N31" t="s">
+        <v>140</v>
+      </c>
+      <c r="O31" t="s">
+        <v>200</v>
+      </c>
+      <c r="P31" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32">
+        <v>0</v>
+      </c>
+      <c r="B32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32">
+        <v>0.0005078989469885588</v>
+      </c>
+      <c r="D32">
+        <v>-9.310187306255102E-05</v>
+      </c>
+      <c r="E32">
+        <v>0.003220473881810904</v>
+      </c>
+      <c r="F32">
+        <v>0.0009695980115793645</v>
+      </c>
+      <c r="G32">
+        <v>0.0009965832578018308</v>
+      </c>
+      <c r="H32">
+        <v>1.000218347685139</v>
+      </c>
+      <c r="I32">
+        <v>0.04917624134876511</v>
+      </c>
+      <c r="J32">
+        <v>-0.02890937030315399</v>
+      </c>
+      <c r="K32">
+        <v>-0.2628898024559021</v>
+      </c>
+      <c r="L32">
+        <v>0.1843281686306</v>
+      </c>
+      <c r="M32">
+        <v>-1.654666900634766</v>
+      </c>
+      <c r="N32" t="s">
+        <v>141</v>
+      </c>
+      <c r="O32" t="s">
+        <v>201</v>
+      </c>
+      <c r="P32" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33">
+        <v>0</v>
+      </c>
+      <c r="B33" t="s">
+        <v>82</v>
+      </c>
+      <c r="C33">
+        <v>0.0006667078860544553</v>
+      </c>
+      <c r="D33">
+        <v>5.184818655834533E-05</v>
+      </c>
+      <c r="E33">
+        <v>0.003989147022366524</v>
+      </c>
+      <c r="F33">
+        <v>0.001120560220442712</v>
+      </c>
+      <c r="G33">
+        <v>0.001106181647628546</v>
+      </c>
+      <c r="H33">
+        <v>1.000339981570755</v>
+      </c>
+      <c r="I33">
+        <v>0.04925099745014674</v>
+      </c>
+      <c r="J33">
+        <v>0.01299731153994799</v>
+      </c>
+      <c r="K33">
+        <v>0.1851578950881958</v>
+      </c>
+      <c r="L33">
+        <v>0.228324219584465</v>
+      </c>
+      <c r="M33">
+        <v>0.7439186573028564</v>
+      </c>
+      <c r="N33" t="s">
+        <v>142</v>
+      </c>
+      <c r="O33" t="s">
+        <v>202</v>
+      </c>
+      <c r="P33" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34">
+        <v>0</v>
+      </c>
+      <c r="B34" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34">
+        <v>0.0008207895524249987</v>
+      </c>
+      <c r="D34">
+        <v>0.000204520023544319</v>
+      </c>
+      <c r="E34">
+        <v>0.004937675315886736</v>
+      </c>
+      <c r="F34">
+        <v>0.001225064042955637</v>
+      </c>
+      <c r="G34">
+        <v>0.001197798526845872</v>
+      </c>
+      <c r="H34">
+        <v>1.000341110006318</v>
+      </c>
+      <c r="I34">
+        <v>0.04937206831920085</v>
+      </c>
+      <c r="J34">
+        <v>0.04142030701041222</v>
+      </c>
+      <c r="K34">
+        <v>0.9543943405151367</v>
+      </c>
+      <c r="L34">
+        <v>0.282614529132843</v>
+      </c>
+      <c r="M34">
+        <v>2.370747327804565</v>
+      </c>
+      <c r="N34" t="s">
+        <v>143</v>
+      </c>
+      <c r="O34" t="s">
+        <v>203</v>
+      </c>
+      <c r="P34" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35">
+        <v>0</v>
+      </c>
+      <c r="B35" t="s">
+        <v>84</v>
+      </c>
+      <c r="C35">
+        <v>0.001556438774446598</v>
+      </c>
+      <c r="D35">
+        <v>0.000743054726626724</v>
+      </c>
+      <c r="E35">
+        <v>0.009754758328199387</v>
+      </c>
+      <c r="F35">
+        <v>0.001480791019275784</v>
+      </c>
+      <c r="G35">
+        <v>0.001487103989347816</v>
+      </c>
+      <c r="H35">
+        <v>1.000332645063462</v>
+      </c>
+      <c r="I35">
+        <v>0.04956829239737524</v>
+      </c>
+      <c r="J35">
+        <v>0.0761735662817955</v>
+      </c>
+      <c r="K35">
+        <v>10.39605617523193</v>
+      </c>
+      <c r="L35">
+        <v>0.558326780796051</v>
+      </c>
+      <c r="M35">
+        <v>4.359897136688232</v>
+      </c>
+      <c r="N35" t="s">
+        <v>144</v>
+      </c>
+      <c r="O35" t="s">
+        <v>204</v>
+      </c>
+      <c r="P35" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36">
+        <v>0</v>
+      </c>
+      <c r="B36" t="s">
+        <v>85</v>
+      </c>
+      <c r="C36">
+        <v>0.002966141098639653</v>
+      </c>
+      <c r="D36">
+        <v>0.001633795909583569</v>
+      </c>
+      <c r="E36">
+        <v>0.01924230717122555</v>
+      </c>
+      <c r="F36">
+        <v>0.00172440439928323</v>
+      </c>
+      <c r="G36">
+        <v>0.001727373688481748</v>
+      </c>
+      <c r="H36">
+        <v>1.000497136121214</v>
+      </c>
+      <c r="I36">
+        <v>0.04975068005732612</v>
+      </c>
+      <c r="J36">
+        <v>0.0849064439535141</v>
+      </c>
+      <c r="K36">
+        <v>209.1541442871094</v>
+      </c>
+      <c r="L36">
+        <v>1.101359486579895</v>
+      </c>
+      <c r="M36">
+        <v>4.859735012054443</v>
+      </c>
+      <c r="N36" t="s">
+        <v>145</v>
+      </c>
+      <c r="O36" t="s">
+        <v>205</v>
+      </c>
+      <c r="P36" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37">
+        <v>0</v>
+      </c>
+      <c r="B37" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37">
+        <v>0.005716156431690774</v>
+      </c>
+      <c r="D37">
+        <v>0.003151252632960677</v>
+      </c>
+      <c r="E37">
+        <v>0.03846012055873871</v>
+      </c>
+      <c r="F37">
+        <v>0.00195483467541635</v>
+      </c>
+      <c r="G37">
+        <v>0.001987630501389503</v>
+      </c>
+      <c r="H37">
+        <v>1.000736003443131</v>
+      </c>
+      <c r="I37">
+        <v>0.04949831594595207</v>
+      </c>
+      <c r="J37">
+        <v>0.08193559199571609</v>
+      </c>
+      <c r="K37">
+        <v>29953.009765625</v>
+      </c>
+      <c r="L37">
+        <v>2.201317071914673</v>
+      </c>
+      <c r="M37">
+        <v>4.689694404602051</v>
+      </c>
+      <c r="N37" t="s">
+        <v>146</v>
+      </c>
+      <c r="O37" t="s">
+        <v>206</v>
+      </c>
+      <c r="P37" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38">
+        <v>0</v>
+      </c>
+      <c r="B38" t="s">
+        <v>87</v>
+      </c>
+      <c r="C38">
+        <v>0.01386707140690443</v>
+      </c>
+      <c r="D38">
+        <v>0.007539675105363131</v>
+      </c>
+      <c r="E38">
+        <v>0.09616204351186752</v>
+      </c>
+      <c r="F38">
+        <v>0.002143418183550239</v>
+      </c>
+      <c r="G38">
+        <v>0.002333421958610415</v>
+      </c>
+      <c r="H38">
+        <v>1.001212551588986</v>
+      </c>
+      <c r="I38">
+        <v>0.05012040518739296</v>
+      </c>
+      <c r="J38">
+        <v>0.07840593904256821</v>
+      </c>
+      <c r="K38">
+        <v>48614092800</v>
+      </c>
+      <c r="L38">
+        <v>5.503964424133301</v>
+      </c>
+      <c r="M38">
+        <v>4.487669944763184</v>
+      </c>
+      <c r="N38" t="s">
+        <v>147</v>
+      </c>
+      <c r="O38" t="s">
+        <v>207</v>
+      </c>
+      <c r="P38" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39">
+        <v>0</v>
+      </c>
+      <c r="B39" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39">
+        <v>0.02739345807874787</v>
+      </c>
+      <c r="D39">
+        <v>0.01474186219274998</v>
+      </c>
+      <c r="E39">
+        <v>0.1923292577266693</v>
+      </c>
+      <c r="F39">
+        <v>0.002230606973171234</v>
+      </c>
+      <c r="G39">
+        <v>0.002557012718170881</v>
+      </c>
+      <c r="H39">
+        <v>1.001581579517817</v>
+      </c>
+      <c r="I39">
+        <v>0.05053879492780765</v>
+      </c>
+      <c r="J39">
+        <v>0.07664908468723297</v>
+      </c>
+      <c r="K39">
+        <v>6.620950807367574E+20</v>
+      </c>
+      <c r="L39">
+        <v>11.00822448730469</v>
+      </c>
+      <c r="M39">
+        <v>4.38711404800415</v>
+      </c>
+      <c r="N39" t="s">
+        <v>148</v>
+      </c>
+      <c r="O39" t="s">
+        <v>208</v>
+      </c>
+      <c r="P39" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40">
+        <v>0</v>
+      </c>
+      <c r="B40" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40">
+        <v>0.06745732789443001</v>
+      </c>
+      <c r="D40">
+        <v>0.03614725917577744</v>
+      </c>
+      <c r="E40">
+        <v>0.4709928631782532</v>
+      </c>
+      <c r="F40">
+        <v>0.002348160604014993</v>
+      </c>
+      <c r="G40">
+        <v>0.002857878338545561</v>
+      </c>
+      <c r="H40">
+        <v>1.002302598462329</v>
+      </c>
+      <c r="I40">
+        <v>0.0558021473622935</v>
+      </c>
+      <c r="J40">
+        <v>0.07674693316221237</v>
+      </c>
+      <c r="K40" t="s">
+        <v>110</v>
+      </c>
+      <c r="L40">
+        <v>26.95791244506836</v>
+      </c>
+      <c r="M40">
+        <v>4.392714500427246</v>
+      </c>
+      <c r="N40" t="s">
+        <v>149</v>
+      </c>
+      <c r="O40" t="s">
+        <v>209</v>
+      </c>
+      <c r="P40" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41">
+        <v>0</v>
+      </c>
+      <c r="B41" t="s">
+        <v>90</v>
+      </c>
+      <c r="C41">
+        <v>0.1413683485568585</v>
+      </c>
+      <c r="D41">
+        <v>0.0752175971865654</v>
+      </c>
+      <c r="E41">
+        <v>1.051662087440491</v>
+      </c>
+      <c r="F41">
+        <v>0.00249294494278729</v>
+      </c>
+      <c r="G41">
+        <v>0.003214019816368818</v>
+      </c>
+      <c r="H41">
+        <v>1.003916768665851</v>
+      </c>
+      <c r="I41">
+        <v>0.06496861889375367</v>
+      </c>
+      <c r="J41">
+        <v>0.07152259349822998</v>
+      </c>
+      <c r="K41" t="s">
+        <v>110</v>
+      </c>
+      <c r="L41">
+        <v>60.19330215454102</v>
+      </c>
+      <c r="M41">
+        <v>4.093692302703857</v>
+      </c>
+      <c r="N41" t="s">
+        <v>150</v>
+      </c>
+      <c r="O41" t="s">
+        <v>210</v>
+      </c>
+      <c r="P41" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42">
+        <v>0</v>
+      </c>
+      <c r="B42" t="s">
+        <v>91</v>
+      </c>
+      <c r="C42">
+        <v>0.0001836933316416593</v>
+      </c>
+      <c r="D42">
+        <v>-0.000101865669421386</v>
+      </c>
+      <c r="E42">
+        <v>0.001696147606708109</v>
+      </c>
+      <c r="F42">
+        <v>0.001044473960064352</v>
+      </c>
+      <c r="G42">
+        <v>0.001065181335434318</v>
+      </c>
+      <c r="H42">
+        <v>1.00000108441247</v>
+      </c>
+      <c r="I42">
+        <v>0.04939841612426772</v>
+      </c>
+      <c r="J42">
+        <v>-0.06005707755684853</v>
+      </c>
+      <c r="K42">
+        <v>-0.283748984336853</v>
+      </c>
+      <c r="L42">
+        <v>0.09708129614591599</v>
+      </c>
+      <c r="M42">
+        <v>-3.437448024749756</v>
+      </c>
+      <c r="N42" t="s">
+        <v>151</v>
+      </c>
+      <c r="O42" t="s">
+        <v>211</v>
+      </c>
+      <c r="P42" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43">
+        <v>0</v>
+      </c>
+      <c r="B43" t="s">
+        <v>92</v>
+      </c>
+      <c r="C43">
+        <v>0.0002296950682095322</v>
+      </c>
+      <c r="D43">
+        <v>2.050730836344883E-05</v>
+      </c>
+      <c r="E43">
+        <v>0.001953081926330924</v>
+      </c>
+      <c r="F43">
+        <v>0.001203597406856716</v>
+      </c>
+      <c r="G43">
+        <v>0.001187061658129096</v>
+      </c>
+      <c r="H43">
+        <v>1.000135127302089</v>
+      </c>
+      <c r="I43">
+        <v>0.04944002354340452</v>
+      </c>
+      <c r="J43">
+        <v>0.01049997378140688</v>
+      </c>
+      <c r="K43">
+        <v>0.06947767734527588</v>
+      </c>
+      <c r="L43">
+        <v>0.1117872819304466</v>
+      </c>
+      <c r="M43">
+        <v>0.6009801626205444</v>
+      </c>
+      <c r="N43" t="s">
+        <v>152</v>
+      </c>
+      <c r="O43" t="s">
+        <v>212</v>
+      </c>
+      <c r="P43" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44">
+        <v>0</v>
+      </c>
+      <c r="B44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C44">
+        <v>0.0002700852183138571</v>
+      </c>
+      <c r="D44">
+        <v>4.359517697594129E-05</v>
+      </c>
+      <c r="E44">
+        <v>0.001992861973121762</v>
+      </c>
+      <c r="F44">
+        <v>0.001294818124733865</v>
+      </c>
+      <c r="G44">
+        <v>0.001294419053010643</v>
+      </c>
+      <c r="H44">
+        <v>1.000124807979521</v>
+      </c>
+      <c r="I44">
+        <v>0.04956955625321992</v>
+      </c>
+      <c r="J44">
+        <v>0.0218756627291441</v>
+      </c>
+      <c r="K44">
+        <v>0.1536499261856079</v>
+      </c>
+      <c r="L44">
+        <v>0.1140641495585442</v>
+      </c>
+      <c r="M44">
+        <v>1.25208306312561</v>
+      </c>
+      <c r="N44" t="s">
+        <v>153</v>
+      </c>
+      <c r="O44" t="s">
+        <v>213</v>
+      </c>
+      <c r="P44" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45">
+        <v>0</v>
+      </c>
+      <c r="B45" t="s">
+        <v>94</v>
+      </c>
+      <c r="C45">
+        <v>0.0004310563757510046</v>
+      </c>
+      <c r="D45">
+        <v>0.0003175538731738925</v>
+      </c>
+      <c r="E45">
+        <v>0.001557081239297986</v>
+      </c>
+      <c r="F45">
+        <v>0.001524688326753676</v>
+      </c>
+      <c r="G45">
+        <v>0.001511171576566994</v>
+      </c>
+      <c r="H45">
+        <v>1.000136596764461</v>
+      </c>
+      <c r="I45">
+        <v>0.04982560784794313</v>
+      </c>
+      <c r="J45">
+        <v>0.203941747546196</v>
+      </c>
+      <c r="K45">
+        <v>1.829799175262451</v>
+      </c>
+      <c r="L45">
+        <v>0.08912164717912674</v>
+      </c>
+      <c r="M45">
+        <v>11.67288112640381</v>
+      </c>
+      <c r="N45" t="s">
+        <v>154</v>
+      </c>
+      <c r="O45" t="s">
+        <v>214</v>
+      </c>
+      <c r="P45" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46">
+        <v>0</v>
+      </c>
+      <c r="B46" t="s">
+        <v>95</v>
+      </c>
+      <c r="C46">
+        <v>0.0006837241144362744</v>
+      </c>
+      <c r="D46">
+        <v>0.0005108841578476131</v>
+      </c>
+      <c r="E46">
+        <v>0.002543657785281539</v>
+      </c>
+      <c r="F46">
+        <v>0.001781121245585382</v>
+      </c>
+      <c r="G46">
+        <v>0.001775255892425776</v>
+      </c>
+      <c r="H46">
+        <v>1.000242840654345</v>
+      </c>
+      <c r="I46">
+        <v>0.04998335503305031</v>
+      </c>
+      <c r="J46">
+        <v>0.200846254825592</v>
+      </c>
+      <c r="K46">
+        <v>4.330166816711426</v>
+      </c>
+      <c r="L46">
+        <v>0.1455896943807602</v>
+      </c>
+      <c r="M46">
+        <v>11.49570655822754</v>
+      </c>
+      <c r="N46" t="s">
+        <v>155</v>
+      </c>
+      <c r="O46" t="s">
+        <v>215</v>
+      </c>
+      <c r="P46" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47">
+        <v>0</v>
+      </c>
+      <c r="B47" t="s">
+        <v>96</v>
+      </c>
+      <c r="C47">
+        <v>0.001120604813077965</v>
+      </c>
+      <c r="D47">
+        <v>0.0008171660010702908</v>
+      </c>
+      <c r="E47">
+        <v>0.004667893517762423</v>
+      </c>
+      <c r="F47">
+        <v>0.00197109067812562</v>
+      </c>
+      <c r="G47">
+        <v>0.002045564819127321</v>
+      </c>
+      <c r="H47">
+        <v>1.000478012725913</v>
+      </c>
+      <c r="I47">
+        <v>0.04979682779208618</v>
+      </c>
+      <c r="J47">
+        <v>0.175060972571373</v>
+      </c>
+      <c r="K47">
+        <v>13.526686668396</v>
+      </c>
+      <c r="L47">
+        <v>0.2671732008457184</v>
+      </c>
+      <c r="M47">
+        <v>10.01985168457031</v>
+      </c>
+      <c r="N47" t="s">
+        <v>156</v>
+      </c>
+      <c r="O47" t="s">
+        <v>216</v>
+      </c>
+      <c r="P47" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48">
+        <v>0</v>
+      </c>
+      <c r="B48" t="s">
+        <v>97</v>
+      </c>
+      <c r="C48">
+        <v>0.002312581436992856</v>
+      </c>
+      <c r="D48">
+        <v>0.001515030395239592</v>
+      </c>
+      <c r="E48">
+        <v>0.01131921634078026</v>
+      </c>
+      <c r="F48">
+        <v>0.002104348735883832</v>
+      </c>
+      <c r="G48">
+        <v>0.00237182411365211</v>
+      </c>
+      <c r="H48">
+        <v>1.00123547555371</v>
+      </c>
+      <c r="I48">
+        <v>0.05016697282132367</v>
+      </c>
+      <c r="J48">
+        <v>0.1338458806276321</v>
+      </c>
+      <c r="K48">
+        <v>141.5204010009766</v>
+      </c>
+      <c r="L48">
+        <v>0.647870659828186</v>
+      </c>
+      <c r="M48">
+        <v>7.660849571228027</v>
+      </c>
+      <c r="N48" t="s">
+        <v>157</v>
+      </c>
+      <c r="O48" t="s">
+        <v>217</v>
+      </c>
+      <c r="P48" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
+      <c r="A49">
+        <v>0</v>
+      </c>
+      <c r="B49" t="s">
+        <v>98</v>
+      </c>
+      <c r="C49">
+        <v>0.004204962812138446</v>
+      </c>
+      <c r="D49">
+        <v>0.002579710679128766</v>
+      </c>
+      <c r="E49">
+        <v>0.02218599990010262</v>
+      </c>
+      <c r="F49">
+        <v>0.00215145805850625</v>
+      </c>
+      <c r="G49">
+        <v>0.002542072208598256</v>
+      </c>
+      <c r="H49">
+        <v>1.001576722413817</v>
+      </c>
+      <c r="I49">
+        <v>0.05057294411497562</v>
+      </c>
+      <c r="J49">
+        <v>0.1162765100598335</v>
+      </c>
+      <c r="K49">
+        <v>4628.38525390625</v>
+      </c>
+      <c r="L49">
+        <v>1.269845724105835</v>
+      </c>
+      <c r="M49">
+        <v>6.655242919921875</v>
+      </c>
+      <c r="N49" t="s">
+        <v>158</v>
+      </c>
+      <c r="O49" t="s">
+        <v>218</v>
+      </c>
+      <c r="P49" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
+      <c r="A50">
+        <v>0</v>
+      </c>
+      <c r="B50" t="s">
+        <v>99</v>
+      </c>
+      <c r="C50">
+        <v>0.009985676067108337</v>
+      </c>
+      <c r="D50">
+        <v>0.005662266165018082</v>
+      </c>
+      <c r="E50">
+        <v>0.05717657133936882</v>
+      </c>
+      <c r="F50">
+        <v>0.002270851517096162</v>
+      </c>
+      <c r="G50">
+        <v>0.002875051693990827</v>
+      </c>
+      <c r="H50">
+        <v>1.002670524090353</v>
+      </c>
+      <c r="I50">
+        <v>0.05575669690240725</v>
+      </c>
+      <c r="J50">
+        <v>0.0990312322974205</v>
+      </c>
+      <c r="K50">
+        <v>107978968</v>
+      </c>
+      <c r="L50">
+        <v>3.272578239440918</v>
+      </c>
+      <c r="M50">
+        <v>5.668186187744141</v>
+      </c>
+      <c r="N50" t="s">
+        <v>159</v>
+      </c>
+      <c r="O50" t="s">
+        <v>219</v>
+      </c>
+      <c r="P50" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
+      <c r="A51">
+        <v>0</v>
+      </c>
+      <c r="B51" t="s">
+        <v>100</v>
+      </c>
+      <c r="C51">
+        <v>0.01928384885976879</v>
+      </c>
+      <c r="D51">
+        <v>0.01066326443105936</v>
+      </c>
+      <c r="E51">
+        <v>0.1088334918022156</v>
+      </c>
+      <c r="F51">
+        <v>0.00236134696751833</v>
+      </c>
+      <c r="G51">
+        <v>0.003166307462379336</v>
+      </c>
+      <c r="H51">
+        <v>1.003916768665851</v>
+      </c>
+      <c r="I51">
+        <v>0.06496861889375367</v>
+      </c>
+      <c r="J51">
+        <v>0.09797778725624084</v>
+      </c>
+      <c r="K51">
+        <v>1232646352928768</v>
+      </c>
+      <c r="L51">
+        <v>6.229231834411621</v>
+      </c>
+      <c r="M51">
+        <v>5.607891082763672</v>
+      </c>
+      <c r="N51" t="s">
+        <v>160</v>
+      </c>
+      <c r="O51" t="s">
+        <v>220</v>
+      </c>
+      <c r="P51" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
+      <c r="A52">
+        <v>0</v>
+      </c>
+      <c r="B52" t="s">
+        <v>101</v>
+      </c>
+      <c r="C52">
+        <v>0.0001951252904759884</v>
+      </c>
+      <c r="D52">
+        <v>0.0002151808585040271</v>
+      </c>
+      <c r="E52">
+        <v>0.0006658271886408329</v>
+      </c>
+      <c r="F52">
+        <v>0.001139958156272769</v>
+      </c>
+      <c r="G52">
+        <v>0.001189738512039185</v>
+      </c>
+      <c r="H52">
+        <v>0.9995035257211279</v>
+      </c>
+      <c r="I52">
+        <v>0.04979690127740079</v>
+      </c>
+      <c r="J52">
+        <v>0.323178231716156</v>
+      </c>
+      <c r="K52">
+        <v>1.023503065109253</v>
+      </c>
+      <c r="L52">
+        <v>0.03810951858758926</v>
+      </c>
+      <c r="M52">
+        <v>18.49754333496094</v>
+      </c>
+      <c r="N52" t="s">
+        <v>161</v>
+      </c>
+      <c r="O52" t="s">
+        <v>221</v>
+      </c>
+      <c r="P52" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
+      <c r="A53">
+        <v>0</v>
+      </c>
+      <c r="B53" t="s">
+        <v>102</v>
+      </c>
+      <c r="C53">
+        <v>0.0002319529400828082</v>
+      </c>
+      <c r="D53">
+        <v>0.0002584303729236126</v>
+      </c>
+      <c r="E53">
+        <v>0.0007399044116027653</v>
+      </c>
+      <c r="F53">
+        <v>0.001232985639944673</v>
+      </c>
+      <c r="G53">
+        <v>0.001262433244846761</v>
+      </c>
+      <c r="H53">
+        <v>0.9995699904953091</v>
+      </c>
+      <c r="I53">
+        <v>0.04984174528130734</v>
+      </c>
+      <c r="J53">
+        <v>0.3492753505706787</v>
+      </c>
+      <c r="K53">
+        <v>1.331609725952148</v>
+      </c>
+      <c r="L53">
+        <v>0.0423494279384613</v>
+      </c>
+      <c r="M53">
+        <v>19.99124717712402</v>
+      </c>
+      <c r="N53" t="s">
+        <v>162</v>
+      </c>
+      <c r="O53" t="s">
+        <v>222</v>
+      </c>
+      <c r="P53" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
+      <c r="A54">
+        <v>0</v>
+      </c>
+      <c r="B54" t="s">
+        <v>103</v>
+      </c>
+      <c r="C54">
+        <v>0.0002601151348156795</v>
+      </c>
+      <c r="D54">
+        <v>0.0002904625434894115</v>
+      </c>
+      <c r="E54">
+        <v>0.0007855754811316729</v>
+      </c>
+      <c r="F54">
+        <v>0.00130942277610302</v>
+      </c>
+      <c r="G54">
+        <v>0.001318543334491551</v>
+      </c>
+      <c r="H54">
+        <v>0.9995694471557323</v>
+      </c>
+      <c r="I54">
+        <v>0.04993981344108614</v>
+      </c>
+      <c r="J54">
+        <v>0.3697449266910553</v>
+      </c>
+      <c r="K54">
+        <v>1.589804887771606</v>
+      </c>
+      <c r="L54">
+        <v>0.04496347531676292</v>
+      </c>
+      <c r="M54">
+        <v>21.16285133361816</v>
+      </c>
+      <c r="N54" t="s">
+        <v>163</v>
+      </c>
+      <c r="O54" t="s">
+        <v>223</v>
+      </c>
+      <c r="P54" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16">
+      <c r="A55">
+        <v>0</v>
+      </c>
+      <c r="B55" t="s">
+        <v>43</v>
+      </c>
+      <c r="C55">
+        <v>0.0003475503896269344</v>
+      </c>
+      <c r="D55">
+        <v>0.0003853494126815349</v>
+      </c>
+      <c r="E55">
+        <v>0.0009120872127823532</v>
+      </c>
+      <c r="F55">
+        <v>0.001544017693959177</v>
+      </c>
+      <c r="G55">
+        <v>0.001496097887866199</v>
+      </c>
+      <c r="H55">
+        <v>0.9996226686592679</v>
+      </c>
+      <c r="I55">
+        <v>0.0500813719261658</v>
+      </c>
+      <c r="J55">
+        <v>0.4224918484687805</v>
+      </c>
+      <c r="K55">
+        <v>2.533677339553833</v>
+      </c>
+      <c r="L55">
+        <v>0.05220454558730125</v>
+      </c>
+      <c r="M55">
+        <v>24.18189239501953</v>
+      </c>
+      <c r="N55" t="s">
+        <v>164</v>
+      </c>
+      <c r="O55" t="s">
+        <v>224</v>
+      </c>
+      <c r="P55" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16">
+      <c r="A56">
+        <v>0</v>
+      </c>
+      <c r="B56" t="s">
+        <v>104</v>
+      </c>
+      <c r="C56">
+        <v>0.0004344097679045951</v>
+      </c>
+      <c r="D56">
+        <v>0.0004738927527796477</v>
+      </c>
+      <c r="E56">
+        <v>0.001034821616485715</v>
+      </c>
+      <c r="F56">
+        <v>0.001670499914325774</v>
+      </c>
+      <c r="G56">
+        <v>0.001729986281134188</v>
+      </c>
+      <c r="H56">
+        <v>0.9997521443823632</v>
+      </c>
+      <c r="I56">
+        <v>0.0505069983699525</v>
+      </c>
+      <c r="J56">
+        <v>0.4579463303089142</v>
+      </c>
+      <c r="K56">
+        <v>3.720844268798828</v>
+      </c>
+      <c r="L56">
+        <v>0.05922941491007805</v>
+      </c>
+      <c r="M56">
+        <v>26.21117782592773</v>
+      </c>
+      <c r="N56" t="s">
+        <v>165</v>
+      </c>
+      <c r="O56" t="s">
+        <v>225</v>
+      </c>
+      <c r="P56" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16">
+      <c r="A57">
+        <v>0</v>
+      </c>
+      <c r="B57" t="s">
+        <v>105</v>
+      </c>
+      <c r="C57">
+        <v>0.000517478766572634</v>
+      </c>
+      <c r="D57">
+        <v>0.000545895250979811</v>
+      </c>
+      <c r="E57">
+        <v>0.001152475480921566</v>
+      </c>
+      <c r="F57">
+        <v>0.001688505406491458</v>
+      </c>
+      <c r="G57">
+        <v>0.001980789238587022</v>
+      </c>
+      <c r="H57">
+        <v>1.000252133479038</v>
+      </c>
+      <c r="I57">
+        <v>0.04994548845534855</v>
+      </c>
+      <c r="J57">
+        <v>0.4736719131469727</v>
+      </c>
+      <c r="K57">
+        <v>4.975975036621094</v>
+      </c>
+      <c r="L57">
+        <v>0.0659634917974472</v>
+      </c>
+      <c r="M57">
+        <v>27.11125183105469</v>
+      </c>
+      <c r="N57" t="s">
+        <v>166</v>
+      </c>
+      <c r="O57" t="s">
+        <v>226</v>
+      </c>
+      <c r="P57" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16">
+      <c r="A58">
+        <v>0</v>
+      </c>
+      <c r="B58" t="s">
+        <v>106</v>
+      </c>
+      <c r="C58">
+        <v>0.0006140091445460494</v>
+      </c>
+      <c r="D58">
+        <v>0.000643971492536366</v>
+      </c>
+      <c r="E58">
+        <v>0.001392650185152888</v>
+      </c>
+      <c r="F58">
+        <v>0.001736903679557145</v>
+      </c>
+      <c r="G58">
+        <v>0.002279308857396245</v>
+      </c>
+      <c r="H58">
+        <v>1.00115076213259</v>
+      </c>
+      <c r="I58">
+        <v>0.04979970255795006</v>
+      </c>
+      <c r="J58">
+        <v>0.4624072015285492</v>
+      </c>
+      <c r="K58">
+        <v>7.23968505859375</v>
+      </c>
+      <c r="L58">
+        <v>0.0797102153301239</v>
+      </c>
+      <c r="M58">
+        <v>26.46650123596191</v>
+      </c>
+      <c r="N58" t="s">
+        <v>167</v>
+      </c>
+      <c r="O58" t="s">
+        <v>227</v>
+      </c>
+      <c r="P58" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16">
+      <c r="A59">
+        <v>0</v>
+      </c>
+      <c r="B59" t="s">
+        <v>107</v>
+      </c>
+      <c r="C59">
+        <v>0.0006784947161607125</v>
+      </c>
+      <c r="D59">
+        <v>0.0007470922428183258</v>
+      </c>
+      <c r="E59">
+        <v>0.001693130820058286</v>
+      </c>
+      <c r="F59">
+        <v>0.001796294120140374</v>
+      </c>
+      <c r="G59">
+        <v>0.00253187888301909</v>
+      </c>
+      <c r="H59">
+        <v>1.001513053751057</v>
+      </c>
+      <c r="I59">
+        <v>0.05026986617394747</v>
+      </c>
+      <c r="J59">
+        <v>0.4412489831447601</v>
+      </c>
+      <c r="K59">
+        <v>10.54826736450195</v>
+      </c>
+      <c r="L59">
+        <v>0.09690862894058228</v>
+      </c>
+      <c r="M59">
+        <v>25.2554817199707</v>
+      </c>
+      <c r="N59" t="s">
+        <v>168</v>
+      </c>
+      <c r="O59" t="s">
+        <v>228</v>
+      </c>
+      <c r="P59" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
+      <c r="A60">
+        <v>0</v>
+      </c>
+      <c r="B60" t="s">
+        <v>108</v>
+      </c>
+      <c r="C60">
+        <v>0.0007553386776813119</v>
+      </c>
+      <c r="D60">
+        <v>0.0008902919944375753</v>
+      </c>
+      <c r="E60">
+        <v>0.002266445197165012</v>
+      </c>
+      <c r="F60">
+        <v>0.001913485699333251</v>
+      </c>
+      <c r="G60">
+        <v>0.003058606060221791</v>
+      </c>
+      <c r="H60">
+        <v>1.002082571651115</v>
+      </c>
+      <c r="I60">
+        <v>0.05654315356317301</v>
+      </c>
+      <c r="J60">
+        <v>0.3928142488002777</v>
+      </c>
+      <c r="K60">
+        <v>17.45209312438965</v>
+      </c>
+      <c r="L60">
+        <v>0.1297230571508408</v>
+      </c>
+      <c r="M60">
+        <v>22.48325347900391</v>
+      </c>
+      <c r="N60" t="s">
+        <v>169</v>
+      </c>
+      <c r="O60" t="s">
+        <v>229</v>
+      </c>
+      <c r="P60" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16">
+      <c r="A61">
+        <v>0</v>
+      </c>
+      <c r="B61" t="s">
+        <v>109</v>
+      </c>
+      <c r="C61">
+        <v>0.000806672425029645</v>
+      </c>
+      <c r="D61">
+        <v>0.001030857907608151</v>
+      </c>
+      <c r="E61">
+        <v>0.002829903271049261</v>
+      </c>
+      <c r="F61">
+        <v>0.002020331798121333</v>
+      </c>
+      <c r="G61">
+        <v>0.00362722622230649</v>
+      </c>
+      <c r="H61">
+        <v>1.003396572827417</v>
+      </c>
+      <c r="I61">
+        <v>0.06542662656125277</v>
+      </c>
+      <c r="J61">
+        <v>0.3642731904983521</v>
+      </c>
+      <c r="K61">
+        <v>28.2292652130127</v>
+      </c>
+      <c r="L61">
+        <v>0.1619733422994614</v>
+      </c>
+      <c r="M61">
+        <v>20.84966850280762</v>
+      </c>
+      <c r="N61" t="s">
+        <v>170</v>
+      </c>
+      <c r="O61" t="s">
+        <v>230</v>
+      </c>
+      <c r="P61" t="s">
+        <v>290</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P61"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2">
+        <v>0.00074978764217332</v>
+      </c>
+      <c r="D2">
+        <v>-0.003586565610021353</v>
+      </c>
+      <c r="E2">
+        <v>0.06352409720420837</v>
+      </c>
+      <c r="F2">
+        <v>0.0008692191913723946</v>
+      </c>
+      <c r="G2">
+        <v>0.000952202535700053</v>
+      </c>
+      <c r="H2">
+        <v>1.000435605683071</v>
+      </c>
+      <c r="I2">
+        <v>0.04905584506162601</v>
+      </c>
+      <c r="J2">
+        <v>-0.05645992234349251</v>
+      </c>
+      <c r="K2">
+        <v>-0.9999922513961792</v>
+      </c>
+      <c r="L2">
+        <v>3.635887622833252</v>
+      </c>
+      <c r="M2">
+        <v>-3.231559991836548</v>
+      </c>
+      <c r="N2" t="s">
+        <v>291</v>
+      </c>
+      <c r="O2" t="s">
+        <v>351</v>
+      </c>
+      <c r="P2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3">
+        <v>0.0009955526813665405</v>
+      </c>
+      <c r="D3">
+        <v>-0.004622497130185366</v>
+      </c>
+      <c r="E3">
+        <v>0.09117256850004196</v>
+      </c>
+      <c r="F3">
+        <v>0.0009868377819657326</v>
+      </c>
+      <c r="G3">
+        <v>0.001013136468827724</v>
+      </c>
+      <c r="H3">
+        <v>1.00060108887963</v>
+      </c>
+      <c r="I3">
+        <v>0.04902651366201658</v>
+      </c>
+      <c r="J3">
+        <v>-0.05070052668452263</v>
+      </c>
+      <c r="K3">
+        <v>-0.9999997615814209</v>
+      </c>
+      <c r="L3">
+        <v>5.218385219573975</v>
+      </c>
+      <c r="M3">
+        <v>-2.901913166046143</v>
+      </c>
+      <c r="N3" t="s">
+        <v>292</v>
+      </c>
+      <c r="O3" t="s">
+        <v>352</v>
+      </c>
+      <c r="P3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4">
+        <v>0.001238100490911266</v>
+      </c>
+      <c r="D4">
+        <v>-0.001781205995939672</v>
+      </c>
+      <c r="E4">
+        <v>0.05036817491054535</v>
+      </c>
+      <c r="F4">
+        <v>0.001084626303054392</v>
+      </c>
+      <c r="G4">
+        <v>0.001108705415390432</v>
+      </c>
+      <c r="H4">
+        <v>1.00067619160994</v>
+      </c>
+      <c r="I4">
+        <v>0.04909957991719125</v>
+      </c>
+      <c r="J4">
+        <v>-0.03536371886730194</v>
+      </c>
+      <c r="K4">
+        <v>-0.997092604637146</v>
+      </c>
+      <c r="L4">
+        <v>2.882890462875366</v>
+      </c>
+      <c r="M4">
+        <v>-2.02409029006958</v>
+      </c>
+      <c r="N4" t="s">
+        <v>293</v>
+      </c>
+      <c r="O4" t="s">
+        <v>353</v>
+      </c>
+      <c r="P4" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5">
+        <v>0.002422929112968646</v>
+      </c>
+      <c r="D5">
+        <v>-0.001482618506997824</v>
+      </c>
+      <c r="E5">
+        <v>0.06940021365880966</v>
+      </c>
+      <c r="F5">
+        <v>0.001378793152980506</v>
+      </c>
+      <c r="G5">
+        <v>0.001387963420711458</v>
+      </c>
+      <c r="H5">
+        <v>1.000722170423297</v>
+      </c>
+      <c r="I5">
+        <v>0.04924639900645814</v>
+      </c>
+      <c r="J5">
+        <v>-0.02136331237852573</v>
+      </c>
+      <c r="K5">
+        <v>-0.9922543168067932</v>
+      </c>
+      <c r="L5">
+        <v>3.972214937210083</v>
+      </c>
+      <c r="M5">
+        <v>-1.222758054733276</v>
+      </c>
+      <c r="N5" t="s">
+        <v>294</v>
+      </c>
+      <c r="O5" t="s">
+        <v>354</v>
+      </c>
+      <c r="P5" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6">
+        <v>0.004739176933291308</v>
+      </c>
+      <c r="D6">
+        <v>0.002330430317670107</v>
+      </c>
+      <c r="E6">
+        <v>0.01965106651186943</v>
+      </c>
+      <c r="F6">
+        <v>0.001621181378141046</v>
+      </c>
+      <c r="G6">
+        <v>0.001608380698598921</v>
+      </c>
+      <c r="H6">
+        <v>1.000855594206876</v>
+      </c>
+      <c r="I6">
+        <v>0.04943416707721798</v>
+      </c>
+      <c r="J6">
+        <v>0.1185905262827873</v>
+      </c>
+      <c r="K6">
+        <v>2048.972900390625</v>
+      </c>
+      <c r="L6">
+        <v>1.124755382537842</v>
+      </c>
+      <c r="M6">
+        <v>6.787689208984375</v>
+      </c>
+      <c r="N6" t="s">
+        <v>295</v>
+      </c>
+      <c r="O6" t="s">
+        <v>355</v>
+      </c>
+      <c r="P6" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7">
+        <v>0.009323053731717483</v>
+      </c>
+      <c r="D7">
+        <v>0.004887211136519909</v>
+      </c>
+      <c r="E7">
+        <v>0.039536964148283</v>
+      </c>
+      <c r="F7">
+        <v>0.001882482320070267</v>
+      </c>
+      <c r="G7">
+        <v>0.001908659818582237</v>
+      </c>
+      <c r="H7">
+        <v>1.000992426484885</v>
+      </c>
+      <c r="I7">
+        <v>0.04923679579104031</v>
+      </c>
+      <c r="J7">
+        <v>0.1236111894249916</v>
+      </c>
+      <c r="K7">
+        <v>8636834</v>
+      </c>
+      <c r="L7">
+        <v>2.262951612472534</v>
+      </c>
+      <c r="M7">
+        <v>7.075053215026855</v>
+      </c>
+      <c r="N7" t="s">
+        <v>296</v>
+      </c>
+      <c r="O7" t="s">
+        <v>356</v>
+      </c>
+      <c r="P7" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8">
+        <v>0</v>
+      </c>
+      <c r="B8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8">
+        <v>0.02293222391483294</v>
+      </c>
+      <c r="D8">
+        <v>0.01260559353977442</v>
+      </c>
+      <c r="E8">
+        <v>0.1093776747584343</v>
+      </c>
+      <c r="F8">
+        <v>0.002129894681274891</v>
+      </c>
+      <c r="G8">
+        <v>0.002255001338198781</v>
+      </c>
+      <c r="H8">
+        <v>1.001260230042549</v>
+      </c>
+      <c r="I8">
+        <v>0.05000327668638207</v>
+      </c>
+      <c r="J8">
+        <v>0.1152483224868774</v>
+      </c>
+      <c r="K8">
+        <v>6.64402028755157E+17</v>
+      </c>
+      <c r="L8">
+        <v>6.260378837585449</v>
+      </c>
+      <c r="M8">
+        <v>6.596393585205078</v>
+      </c>
+      <c r="N8" t="s">
+        <v>297</v>
+      </c>
+      <c r="O8" t="s">
+        <v>357</v>
+      </c>
+      <c r="P8" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9">
+        <v>0.04557706740298695</v>
+      </c>
+      <c r="D9">
+        <v>0.02626829408109188</v>
+      </c>
+      <c r="E9">
+        <v>0.2448223084211349</v>
+      </c>
+      <c r="F9">
+        <v>0.002287745242938399</v>
+      </c>
+      <c r="G9">
+        <v>0.002511302707716823</v>
+      </c>
+      <c r="H9">
+        <v>1.001484286925181</v>
+      </c>
+      <c r="I9">
+        <v>0.05079585999257141</v>
+      </c>
+      <c r="J9">
+        <v>0.1072953417897224</v>
+      </c>
+      <c r="K9">
+        <v>7.774590500567047E+36</v>
+      </c>
+      <c r="L9">
+        <v>14.01273536682129</v>
+      </c>
+      <c r="M9">
+        <v>6.141193866729736</v>
+      </c>
+      <c r="N9" t="s">
+        <v>298</v>
+      </c>
+      <c r="O9" t="s">
+        <v>358</v>
+      </c>
+      <c r="P9" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10">
+        <v>0.1144981155517731</v>
+      </c>
+      <c r="D10">
+        <v>0.0654420405626297</v>
+      </c>
+      <c r="E10">
+        <v>0.6101747751235962</v>
+      </c>
+      <c r="F10">
+        <v>0.002498393645510077</v>
+      </c>
+      <c r="G10">
+        <v>0.002972888993099332</v>
+      </c>
+      <c r="H10">
+        <v>1.002370597918333</v>
+      </c>
+      <c r="I10">
+        <v>0.05583317887376561</v>
+      </c>
+      <c r="J10">
+        <v>0.107251301407814</v>
+      </c>
+      <c r="K10" t="s">
+        <v>110</v>
+      </c>
+      <c r="L10">
+        <v>34.92417907714844</v>
+      </c>
+      <c r="M10">
+        <v>6.138673305511475</v>
+      </c>
+      <c r="N10" t="s">
+        <v>299</v>
+      </c>
+      <c r="O10" t="s">
+        <v>359</v>
+      </c>
+      <c r="P10" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11">
+        <v>0</v>
+      </c>
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11">
+        <v>0.2225678818794051</v>
+      </c>
+      <c r="D11">
+        <v>0.1281538158655167</v>
+      </c>
+      <c r="E11">
+        <v>1.148483633995056</v>
+      </c>
+      <c r="F11">
+        <v>0.002646255074068904</v>
+      </c>
+      <c r="G11">
+        <v>0.003354998305439949</v>
+      </c>
+      <c r="H11">
+        <v>1.003794369645043</v>
+      </c>
+      <c r="I11">
+        <v>0.06507012628973952</v>
+      </c>
+      <c r="J11">
+        <v>0.1115852370858192</v>
+      </c>
+      <c r="K11" t="s">
+        <v>110</v>
+      </c>
+      <c r="L11">
+        <v>65.73501586914062</v>
+      </c>
+      <c r="M11">
+        <v>6.386731624603271</v>
+      </c>
+      <c r="N11" t="s">
+        <v>300</v>
+      </c>
+      <c r="O11" t="s">
+        <v>360</v>
+      </c>
+      <c r="P11" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12">
+        <v>0</v>
+      </c>
+      <c r="B12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12">
+        <v>0.001278676210597228</v>
+      </c>
+      <c r="D12">
+        <v>-0.000274306075880304</v>
+      </c>
+      <c r="E12">
+        <v>0.008737786673009396</v>
+      </c>
+      <c r="F12">
+        <v>0.0008878696826286614</v>
+      </c>
+      <c r="G12">
+        <v>0.0009640696807764471</v>
+      </c>
+      <c r="H12">
+        <v>1.000393947293611</v>
+      </c>
+      <c r="I12">
+        <v>0.04911670755003009</v>
+      </c>
+      <c r="J12">
+        <v>-0.03139308467507362</v>
+      </c>
+      <c r="K12">
+        <v>-0.5929144620895386</v>
+      </c>
+      <c r="L12">
+        <v>0.5001190304756165</v>
+      </c>
+      <c r="M12">
+        <v>-1.796825647354126</v>
+      </c>
+      <c r="N12" t="s">
+        <v>301</v>
+      </c>
+      <c r="O12" t="s">
+        <v>361</v>
+      </c>
+      <c r="P12" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13">
+        <v>0</v>
+      </c>
+      <c r="B13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13">
+        <v>0.001699569126291119</v>
+      </c>
+      <c r="D13">
+        <v>0.0001485305838286877</v>
+      </c>
+      <c r="E13">
+        <v>0.01043173298239708</v>
+      </c>
+      <c r="F13">
+        <v>0.001023766119033098</v>
+      </c>
+      <c r="G13">
+        <v>0.001048948499374092</v>
+      </c>
+      <c r="H13">
+        <v>1.000537208192047</v>
+      </c>
+      <c r="I13">
+        <v>0.04909475362144211</v>
+      </c>
+      <c r="J13">
+        <v>0.01423834264278412</v>
+      </c>
+      <c r="K13">
+        <v>0.6267168521881104</v>
+      </c>
+      <c r="L13">
+        <v>0.5970743298530579</v>
+      </c>
+      <c r="M13">
+        <v>0.8149507641792297</v>
+      </c>
+      <c r="N13" t="s">
+        <v>302</v>
+      </c>
+      <c r="O13" t="s">
+        <v>362</v>
+      </c>
+      <c r="P13" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14">
+        <v>0</v>
+      </c>
+      <c r="B14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14">
+        <v>0.002116519755643486</v>
+      </c>
+      <c r="D14">
+        <v>0.0006794510409235954</v>
+      </c>
+      <c r="E14">
+        <v>0.01188012771308422</v>
+      </c>
+      <c r="F14">
+        <v>0.001130773336626589</v>
+      </c>
+      <c r="G14">
+        <v>0.001148982439190149</v>
+      </c>
+      <c r="H14">
+        <v>1.000620139958102</v>
+      </c>
+      <c r="I14">
+        <v>0.04915556854665912</v>
+      </c>
+      <c r="J14">
+        <v>0.05719223245978355</v>
+      </c>
+      <c r="K14">
+        <v>8.255916595458984</v>
+      </c>
+      <c r="L14">
+        <v>0.679975152015686</v>
+      </c>
+      <c r="M14">
+        <v>3.27347469329834</v>
+      </c>
+      <c r="N14" t="s">
+        <v>303</v>
+      </c>
+      <c r="O14" t="s">
+        <v>363</v>
+      </c>
+      <c r="P14" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15">
+        <v>0</v>
+      </c>
+      <c r="B15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15">
+        <v>0.004174557888484301</v>
+      </c>
+      <c r="D15">
+        <v>0.002347577828913927</v>
+      </c>
+      <c r="E15">
+        <v>0.02608625404536724</v>
+      </c>
+      <c r="F15">
+        <v>0.001410942757502198</v>
+      </c>
+      <c r="G15">
+        <v>0.001415285747498274</v>
+      </c>
+      <c r="H15">
+        <v>1.000617043006649</v>
+      </c>
+      <c r="I15">
+        <v>0.04934661324762185</v>
+      </c>
+      <c r="J15">
+        <v>0.08999290317296982</v>
+      </c>
+      <c r="K15">
+        <v>2167.274169921875</v>
+      </c>
+      <c r="L15">
+        <v>1.493082046508789</v>
+      </c>
+      <c r="M15">
+        <v>5.15086555480957</v>
+      </c>
+      <c r="N15" t="s">
+        <v>304</v>
+      </c>
+      <c r="O15" t="s">
+        <v>364</v>
+      </c>
+      <c r="P15" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16">
+        <v>0</v>
+      </c>
+      <c r="B16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16">
+        <v>0.008231780234134095</v>
+      </c>
+      <c r="D16">
+        <v>0.005691055208444595</v>
+      </c>
+      <c r="E16">
+        <v>0.06711596250534058</v>
+      </c>
+      <c r="F16">
+        <v>0.001651371130719781</v>
+      </c>
+      <c r="G16">
+        <v>0.001649188925512135</v>
+      </c>
+      <c r="H16">
+        <v>1.000750718187618</v>
+      </c>
+      <c r="I16">
+        <v>0.04949348535631793</v>
+      </c>
+      <c r="J16">
+        <v>0.08479436486959457</v>
+      </c>
+      <c r="K16">
+        <v>118572296</v>
+      </c>
+      <c r="L16">
+        <v>3.841472864151001</v>
+      </c>
+      <c r="M16">
+        <v>4.853320121765137</v>
+      </c>
+      <c r="N16" t="s">
+        <v>305</v>
+      </c>
+      <c r="O16" t="s">
+        <v>365</v>
+      </c>
+      <c r="P16" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17">
+        <v>0</v>
+      </c>
+      <c r="B17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17">
+        <v>0.01626960979375064</v>
+      </c>
+      <c r="D17">
+        <v>0.0105362432077527</v>
+      </c>
+      <c r="E17">
+        <v>0.1087037101387978</v>
+      </c>
+      <c r="F17">
+        <v>0.001919021946378052</v>
+      </c>
+      <c r="G17">
+        <v>0.001945622148923576</v>
+      </c>
+      <c r="H17">
+        <v>1.000947522303709</v>
+      </c>
+      <c r="I17">
+        <v>0.04926985175994775</v>
+      </c>
+      <c r="J17">
+        <v>0.096926249563694</v>
+      </c>
+      <c r="K17">
+        <v>816462142898176</v>
+      </c>
+      <c r="L17">
+        <v>6.221803665161133</v>
+      </c>
+      <c r="M17">
+        <v>5.547704696655273</v>
+      </c>
+      <c r="N17" t="s">
+        <v>306</v>
+      </c>
+      <c r="O17" t="s">
+        <v>366</v>
+      </c>
+      <c r="P17" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18">
+        <v>0</v>
+      </c>
+      <c r="B18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18">
+        <v>0.04031969249884048</v>
+      </c>
+      <c r="D18">
+        <v>0.02530124597251415</v>
+      </c>
+      <c r="E18">
+        <v>0.2538067400455475</v>
+      </c>
+      <c r="F18">
+        <v>0.002143650781363249</v>
+      </c>
+      <c r="G18">
+        <v>0.00228808936662972</v>
+      </c>
+      <c r="H18">
+        <v>1.001250335500441</v>
+      </c>
+      <c r="I18">
+        <v>0.05002228349978139</v>
+      </c>
+      <c r="J18">
+        <v>0.09968705475330353</v>
+      </c>
+      <c r="K18">
+        <v>3.543451838593593E+35</v>
+      </c>
+      <c r="L18">
+        <v>14.5269718170166</v>
+      </c>
+      <c r="M18">
+        <v>5.705723285675049</v>
+      </c>
+      <c r="N18" t="s">
+        <v>307</v>
+      </c>
+      <c r="O18" t="s">
+        <v>367</v>
+      </c>
+      <c r="P18" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19">
+        <v>0</v>
+      </c>
+      <c r="B19" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19">
+        <v>0.07967771172412777</v>
+      </c>
+      <c r="D19">
+        <v>0.05166903883218765</v>
+      </c>
+      <c r="E19">
+        <v>0.5388450622558594</v>
+      </c>
+      <c r="F19">
+        <v>0.002294742967933416</v>
+      </c>
+      <c r="G19">
+        <v>0.002545219380408525</v>
+      </c>
+      <c r="H19">
+        <v>1.001542572173185</v>
+      </c>
+      <c r="I19">
+        <v>0.05076675945553048</v>
+      </c>
+      <c r="J19">
+        <v>0.09588848799467087</v>
+      </c>
+      <c r="K19" t="s">
+        <v>110</v>
+      </c>
+      <c r="L19">
+        <v>30.84152603149414</v>
+      </c>
+      <c r="M19">
+        <v>5.488306999206543</v>
+      </c>
+      <c r="N19" t="s">
+        <v>308</v>
+      </c>
+      <c r="O19" t="s">
+        <v>368</v>
+      </c>
+      <c r="P19" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20">
+        <v>0</v>
+      </c>
+      <c r="B20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20">
+        <v>0.1998727141594987</v>
+      </c>
+      <c r="D20">
+        <v>0.1336354464292526</v>
+      </c>
+      <c r="E20">
+        <v>1.521401643753052</v>
+      </c>
+      <c r="F20">
+        <v>0.002463339595124125</v>
+      </c>
+      <c r="G20">
+        <v>0.002945890184491873</v>
+      </c>
+      <c r="H20">
+        <v>1.002379097850334</v>
+      </c>
+      <c r="I20">
+        <v>0.05599506256775619</v>
+      </c>
+      <c r="J20">
+        <v>0.08783706277608871</v>
+      </c>
+      <c r="K20" t="s">
+        <v>110</v>
+      </c>
+      <c r="L20">
+        <v>87.07947540283203</v>
+      </c>
+      <c r="M20">
+        <v>5.027472972869873</v>
+      </c>
+      <c r="N20" t="s">
+        <v>309</v>
+      </c>
+      <c r="O20" t="s">
+        <v>369</v>
+      </c>
+      <c r="P20" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21">
+        <v>0</v>
+      </c>
+      <c r="B21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21">
+        <v>0.391651343933029</v>
+      </c>
+      <c r="D21">
+        <v>0.2830109894275665</v>
+      </c>
+      <c r="E21">
+        <v>3.316121339797974</v>
+      </c>
+      <c r="F21">
+        <v>0.002635214943438768</v>
+      </c>
+      <c r="G21">
+        <v>0.00335051747970283</v>
+      </c>
+      <c r="H21">
+        <v>1.003794369645043</v>
+      </c>
+      <c r="I21">
+        <v>0.06507012628973952</v>
+      </c>
+      <c r="J21">
+        <v>0.08534397929906845</v>
+      </c>
+      <c r="K21" t="s">
+        <v>110</v>
+      </c>
+      <c r="L21">
+        <v>189.8026885986328</v>
+      </c>
+      <c r="M21">
+        <v>4.884778022766113</v>
+      </c>
+      <c r="N21" t="s">
+        <v>310</v>
+      </c>
+      <c r="O21" t="s">
+        <v>370</v>
+      </c>
+      <c r="P21" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22">
+        <v>0</v>
+      </c>
+      <c r="B22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22">
+        <v>0.000382534599889776</v>
+      </c>
+      <c r="D22">
+        <v>-0.0003969231329392642</v>
+      </c>
+      <c r="E22">
+        <v>0.002918642712756991</v>
+      </c>
+      <c r="F22">
+        <v>0.000917418859899044</v>
+      </c>
+      <c r="G22">
+        <v>0.0009623861405998468</v>
+      </c>
+      <c r="H22">
+        <v>1.000303092024041</v>
+      </c>
+      <c r="I22">
+        <v>0.04916762360319164</v>
+      </c>
+      <c r="J22">
+        <v>-0.1359957903623581</v>
+      </c>
+      <c r="K22">
+        <v>-0.7276116609573364</v>
+      </c>
+      <c r="L22">
+        <v>0.1670524626970291</v>
+      </c>
+      <c r="M22">
+        <v>-7.783902645111084</v>
+      </c>
+      <c r="N22" t="s">
+        <v>311</v>
+      </c>
+      <c r="O22" t="s">
+        <v>371</v>
+      </c>
+      <c r="P22" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23">
+        <v>0</v>
+      </c>
+      <c r="B23" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23">
+        <v>0.0005027870464176188</v>
+      </c>
+      <c r="D23">
+        <v>-0.0001152467157226056</v>
+      </c>
+      <c r="E23">
+        <v>0.00353048974648118</v>
+      </c>
+      <c r="F23">
+        <v>0.001063776202499866</v>
+      </c>
+      <c r="G23">
+        <v>0.001073351595550776</v>
+      </c>
+      <c r="H23">
+        <v>1.000435968504282</v>
+      </c>
+      <c r="I23">
+        <v>0.04919200041859039</v>
+      </c>
+      <c r="J23">
+        <v>-0.03264326602220535</v>
+      </c>
+      <c r="K23">
+        <v>-0.3145391941070557</v>
+      </c>
+      <c r="L23">
+        <v>0.2020723521709442</v>
+      </c>
+      <c r="M23">
+        <v>-1.868381381034851</v>
+      </c>
+      <c r="N23" t="s">
+        <v>312</v>
+      </c>
+      <c r="O23" t="s">
+        <v>372</v>
+      </c>
+      <c r="P23" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24">
+        <v>0</v>
+      </c>
+      <c r="B24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24">
+        <v>0.0006189693076837036</v>
+      </c>
+      <c r="D24">
+        <v>6.942467734916136E-05</v>
+      </c>
+      <c r="E24">
+        <v>0.004370279610157013</v>
+      </c>
+      <c r="F24">
+        <v>0.001174430828541517</v>
+      </c>
+      <c r="G24">
+        <v>0.001176260760985315</v>
+      </c>
+      <c r="H24">
+        <v>1.000503433844927</v>
+      </c>
+      <c r="I24">
+        <v>0.04921245708817611</v>
+      </c>
+      <c r="J24">
+        <v>0.01588563807308674</v>
+      </c>
+      <c r="K24">
+        <v>0.2551816701889038</v>
+      </c>
+      <c r="L24">
+        <v>0.2501388490200043</v>
+      </c>
+      <c r="M24">
+        <v>0.909235954284668</v>
+      </c>
+      <c r="N24" t="s">
+        <v>313</v>
+      </c>
+      <c r="O24" t="s">
+        <v>373</v>
+      </c>
+      <c r="P24" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25">
+        <v>0</v>
+      </c>
+      <c r="B25" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25">
+        <v>0.001168624214656161</v>
+      </c>
+      <c r="D25">
+        <v>0.0004754792898893356</v>
+      </c>
+      <c r="E25">
+        <v>0.003405659459531307</v>
+      </c>
+      <c r="F25">
+        <v>0.001447601360268891</v>
+      </c>
+      <c r="G25">
+        <v>0.001457486301660538</v>
+      </c>
+      <c r="H25">
+        <v>1.000475639374618</v>
+      </c>
+      <c r="I25">
+        <v>0.04941866107455785</v>
+      </c>
+      <c r="J25">
+        <v>0.1396144479513168</v>
+      </c>
+      <c r="K25">
+        <v>3.746713161468506</v>
+      </c>
+      <c r="L25">
+        <v>0.1949275135993958</v>
+      </c>
+      <c r="M25">
+        <v>7.991021633148193</v>
+      </c>
+      <c r="N25" t="s">
+        <v>314</v>
+      </c>
+      <c r="O25" t="s">
+        <v>374</v>
+      </c>
+      <c r="P25" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26">
+        <v>0</v>
+      </c>
+      <c r="B26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26">
+        <v>0.002208576674798283</v>
+      </c>
+      <c r="D26">
+        <v>0.001181541010737419</v>
+      </c>
+      <c r="E26">
+        <v>0.006575524806976318</v>
+      </c>
+      <c r="F26">
+        <v>0.001687707961536944</v>
+      </c>
+      <c r="G26">
+        <v>0.001698868698440492</v>
+      </c>
+      <c r="H26">
+        <v>1.00063028268133</v>
+      </c>
+      <c r="I26">
+        <v>0.04961804786326855</v>
+      </c>
+      <c r="J26">
+        <v>0.1796877086162567</v>
+      </c>
+      <c r="K26">
+        <v>46.8587760925293</v>
+      </c>
+      <c r="L26">
+        <v>0.3763590455055237</v>
+      </c>
+      <c r="M26">
+        <v>10.28466892242432</v>
+      </c>
+      <c r="N26" t="s">
+        <v>315</v>
+      </c>
+      <c r="O26" t="s">
+        <v>375</v>
+      </c>
+      <c r="P26" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27">
+        <v>0</v>
+      </c>
+      <c r="B27" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27">
+        <v>0.004225547786339393</v>
+      </c>
+      <c r="D27">
+        <v>0.002395933959633112</v>
+      </c>
+      <c r="E27">
+        <v>0.01295059267431498</v>
+      </c>
+      <c r="F27">
+        <v>0.001951917423866689</v>
+      </c>
+      <c r="G27">
+        <v>0.001963469432666898</v>
+      </c>
+      <c r="H27">
+        <v>1.000824330762487</v>
+      </c>
+      <c r="I27">
+        <v>0.04933552944529958</v>
+      </c>
+      <c r="J27">
+        <v>0.1850057393312454</v>
+      </c>
+      <c r="K27">
+        <v>2538.8662109375</v>
+      </c>
+      <c r="L27">
+        <v>0.7412446737289429</v>
+      </c>
+      <c r="M27">
+        <v>10.5890531539917</v>
+      </c>
+      <c r="N27" t="s">
+        <v>316</v>
+      </c>
+      <c r="O27" t="s">
+        <v>376</v>
+      </c>
+      <c r="P27" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28">
+        <v>0</v>
+      </c>
+      <c r="B28" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28">
+        <v>0.01018386096088184</v>
+      </c>
+      <c r="D28">
+        <v>0.005747633054852486</v>
+      </c>
+      <c r="E28">
+        <v>0.03225397691130638</v>
+      </c>
+      <c r="F28">
+        <v>0.002157139824703336</v>
+      </c>
+      <c r="G28">
+        <v>0.002312176162377</v>
+      </c>
+      <c r="H28">
+        <v>1.001223097904029</v>
+      </c>
+      <c r="I28">
+        <v>0.05004695698117403</v>
+      </c>
+      <c r="J28">
+        <v>0.1781992018222809</v>
+      </c>
+      <c r="K28">
+        <v>142589456</v>
+      </c>
+      <c r="L28">
+        <v>1.846099972724915</v>
+      </c>
+      <c r="M28">
+        <v>10.19947242736816</v>
+      </c>
+      <c r="N28" t="s">
+        <v>317</v>
+      </c>
+      <c r="O28" t="s">
+        <v>377</v>
+      </c>
+      <c r="P28" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29">
+        <v>0</v>
+      </c>
+      <c r="B29" t="s">
+        <v>78</v>
+      </c>
+      <c r="C29">
+        <v>0.01999400667464019</v>
+      </c>
+      <c r="D29">
+        <v>0.01123868208378553</v>
+      </c>
+      <c r="E29">
+        <v>0.06443009525537491</v>
+      </c>
+      <c r="F29">
+        <v>0.002287763636559248</v>
+      </c>
+      <c r="G29">
+        <v>0.002579099265858531</v>
+      </c>
+      <c r="H29">
+        <v>1.001594781241679</v>
+      </c>
+      <c r="I29">
+        <v>0.05074458539785971</v>
+      </c>
+      <c r="J29">
+        <v>0.1744321882724762</v>
+      </c>
+      <c r="K29">
+        <v>7955233988673536</v>
+      </c>
+      <c r="L29">
+        <v>3.687743663787842</v>
+      </c>
+      <c r="M29">
+        <v>9.983861923217773</v>
+      </c>
+      <c r="N29" t="s">
+        <v>318</v>
+      </c>
+      <c r="O29" t="s">
+        <v>378</v>
+      </c>
+      <c r="P29" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30">
+        <v>0.04955670511942464</v>
+      </c>
+      <c r="D30">
+        <v>0.02747481688857079</v>
+      </c>
+      <c r="E30">
+        <v>0.1586204320192337</v>
+      </c>
+      <c r="F30">
+        <v>0.002440592972561717</v>
+      </c>
+      <c r="G30">
+        <v>0.002959404373541474</v>
+      </c>
+      <c r="H30">
+        <v>1.002234599006325</v>
+      </c>
+      <c r="I30">
+        <v>0.0559064905600835</v>
+      </c>
+      <c r="J30">
+        <v>0.173211082816124</v>
+      </c>
+      <c r="K30" t="s">
+        <v>110</v>
+      </c>
+      <c r="L30">
+        <v>9.078854560852051</v>
+      </c>
+      <c r="M30">
+        <v>9.913969993591309</v>
+      </c>
+      <c r="N30" t="s">
+        <v>319</v>
+      </c>
+      <c r="O30" t="s">
+        <v>379</v>
+      </c>
+      <c r="P30" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31">
+        <v>0</v>
+      </c>
+      <c r="B31" t="s">
+        <v>80</v>
+      </c>
+      <c r="C31">
+        <v>0.09657252974808705</v>
+      </c>
+      <c r="D31">
+        <v>0.05321699008345604</v>
+      </c>
+      <c r="E31">
+        <v>0.3112423419952393</v>
+      </c>
+      <c r="F31">
+        <v>0.002585073234513402</v>
+      </c>
+      <c r="G31">
+        <v>0.003344469470903277</v>
+      </c>
+      <c r="H31">
+        <v>1.003794369645043</v>
+      </c>
+      <c r="I31">
+        <v>0.06507012628973952</v>
+      </c>
+      <c r="J31">
+        <v>0.1709824949502945</v>
+      </c>
+      <c r="K31" t="s">
+        <v>110</v>
+      </c>
+      <c r="L31">
+        <v>17.81437683105469</v>
+      </c>
+      <c r="M31">
+        <v>9.78641414642334</v>
+      </c>
+      <c r="N31" t="s">
+        <v>320</v>
+      </c>
+      <c r="O31" t="s">
+        <v>380</v>
+      </c>
+      <c r="P31" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32">
+        <v>0</v>
+      </c>
+      <c r="B32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32">
+        <v>0.0004267283875466625</v>
+      </c>
+      <c r="D32">
+        <v>-0.0001465828099753708</v>
+      </c>
+      <c r="E32">
+        <v>0.002943586092442274</v>
+      </c>
+      <c r="F32">
+        <v>0.0009653062443248928</v>
+      </c>
+      <c r="G32">
+        <v>0.0009995605796575546</v>
+      </c>
+      <c r="H32">
+        <v>1.000222193954316</v>
+      </c>
+      <c r="I32">
+        <v>0.04917662378132336</v>
+      </c>
+      <c r="J32">
+        <v>-0.04979735612869263</v>
+      </c>
+      <c r="K32">
+        <v>-0.3813350200653076</v>
+      </c>
+      <c r="L32">
+        <v>0.1684801280498505</v>
+      </c>
+      <c r="M32">
+        <v>-2.850219011306763</v>
+      </c>
+      <c r="N32" t="s">
+        <v>321</v>
+      </c>
+      <c r="O32" t="s">
+        <v>381</v>
+      </c>
+      <c r="P32" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33">
+        <v>0</v>
+      </c>
+      <c r="B33" t="s">
+        <v>82</v>
+      </c>
+      <c r="C33">
+        <v>0.0005588834894231253</v>
+      </c>
+      <c r="D33">
+        <v>2.506000055291224E-05</v>
+      </c>
+      <c r="E33">
+        <v>0.003882266581058502</v>
+      </c>
+      <c r="F33">
+        <v>0.001118496293202043</v>
+      </c>
+      <c r="G33">
+        <v>0.001108899596147239</v>
+      </c>
+      <c r="H33">
+        <v>1.000343891560137</v>
+      </c>
+      <c r="I33">
+        <v>0.04923089260316802</v>
+      </c>
+      <c r="J33">
+        <v>0.006454992108047009</v>
+      </c>
+      <c r="K33">
+        <v>0.08546686172485352</v>
+      </c>
+      <c r="L33">
+        <v>0.2222067713737488</v>
+      </c>
+      <c r="M33">
+        <v>0.3694601953029633</v>
+      </c>
+      <c r="N33" t="s">
+        <v>322</v>
+      </c>
+      <c r="O33" t="s">
+        <v>382</v>
+      </c>
+      <c r="P33" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34">
+        <v>0</v>
+      </c>
+      <c r="B34" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34">
+        <v>0.0006864468660032198</v>
+      </c>
+      <c r="D34">
+        <v>0.0001750677183736116</v>
+      </c>
+      <c r="E34">
+        <v>0.004682125989347696</v>
+      </c>
+      <c r="F34">
+        <v>0.001222050748765469</v>
+      </c>
+      <c r="G34">
+        <v>0.001197944045998156</v>
+      </c>
+      <c r="H34">
+        <v>1.000329526329591</v>
+      </c>
+      <c r="I34">
+        <v>0.0493591999909708</v>
+      </c>
+      <c r="J34">
+        <v>0.03739064559340477</v>
+      </c>
+      <c r="K34">
+        <v>0.7747113704681396</v>
+      </c>
+      <c r="L34">
+        <v>0.2679878175258636</v>
+      </c>
+      <c r="M34">
+        <v>2.140104055404663</v>
+      </c>
+      <c r="N34" t="s">
+        <v>323</v>
+      </c>
+      <c r="O34" t="s">
+        <v>383</v>
+      </c>
+      <c r="P34" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35">
+        <v>0</v>
+      </c>
+      <c r="B35" t="s">
+        <v>84</v>
+      </c>
+      <c r="C35">
+        <v>0.001289942581792997</v>
+      </c>
+      <c r="D35">
+        <v>0.0006856477702967823</v>
+      </c>
+      <c r="E35">
+        <v>0.008600556291639805</v>
+      </c>
+      <c r="F35">
+        <v>0.001487225061282516</v>
+      </c>
+      <c r="G35">
+        <v>0.001484352978877723</v>
+      </c>
+      <c r="H35">
+        <v>1.000315630655536</v>
+      </c>
+      <c r="I35">
+        <v>0.04956139507659735</v>
+      </c>
+      <c r="J35">
+        <v>0.07972133159637451</v>
+      </c>
+      <c r="K35">
+        <v>8.445672035217285</v>
+      </c>
+      <c r="L35">
+        <v>0.492264449596405</v>
+      </c>
+      <c r="M35">
+        <v>4.562958240509033</v>
+      </c>
+      <c r="N35" t="s">
+        <v>324</v>
+      </c>
+      <c r="O35" t="s">
+        <v>384</v>
+      </c>
+      <c r="P35" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36">
+        <v>0</v>
+      </c>
+      <c r="B36" t="s">
+        <v>85</v>
+      </c>
+      <c r="C36">
+        <v>0.002435149323738106</v>
+      </c>
+      <c r="D36">
+        <v>0.001558124902658165</v>
+      </c>
+      <c r="E36">
+        <v>0.01733257807791233</v>
+      </c>
+      <c r="F36">
+        <v>0.001734408899210393</v>
+      </c>
+      <c r="G36">
+        <v>0.001741023152135313</v>
+      </c>
+      <c r="H36">
+        <v>1.000491609721374</v>
+      </c>
+      <c r="I36">
+        <v>0.04977145873004191</v>
+      </c>
+      <c r="J36">
+        <v>0.08989574015140533</v>
+      </c>
+      <c r="K36">
+        <v>163.0629272460938</v>
+      </c>
+      <c r="L36">
+        <v>0.9920535087585449</v>
+      </c>
+      <c r="M36">
+        <v>5.145304203033447</v>
+      </c>
+      <c r="N36" t="s">
+        <v>325</v>
+      </c>
+      <c r="O36" t="s">
+        <v>385</v>
+      </c>
+      <c r="P36" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37">
+        <v>0</v>
+      </c>
+      <c r="B37" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37">
+        <v>0.004658124421919908</v>
+      </c>
+      <c r="D37">
+        <v>0.003006724873557687</v>
+      </c>
+      <c r="E37">
+        <v>0.03478960320353508</v>
+      </c>
+      <c r="F37">
+        <v>0.001962651032954454</v>
+      </c>
+      <c r="G37">
+        <v>0.001995007274672389</v>
+      </c>
+      <c r="H37">
+        <v>1.000707943981245</v>
+      </c>
+      <c r="I37">
+        <v>0.04952988405469294</v>
+      </c>
+      <c r="J37">
+        <v>0.08642596006393433</v>
+      </c>
+      <c r="K37">
+        <v>18678.091796875</v>
+      </c>
+      <c r="L37">
+        <v>1.991229891777039</v>
+      </c>
+      <c r="M37">
+        <v>4.946706771850586</v>
+      </c>
+      <c r="N37" t="s">
+        <v>326</v>
+      </c>
+      <c r="O37" t="s">
+        <v>386</v>
+      </c>
+      <c r="P37" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38">
+        <v>0</v>
+      </c>
+      <c r="B38" t="s">
+        <v>87</v>
+      </c>
+      <c r="C38">
+        <v>0.01122887002618697</v>
+      </c>
+      <c r="D38">
+        <v>0.007164372131228447</v>
+      </c>
+      <c r="E38">
+        <v>0.08685759454965591</v>
+      </c>
+      <c r="F38">
+        <v>0.002173441229388118</v>
+      </c>
+      <c r="G38">
+        <v>0.002350415103137493</v>
+      </c>
+      <c r="H38">
+        <v>1.001183408964985</v>
+      </c>
+      <c r="I38">
+        <v>0.05012803256291542</v>
+      </c>
+      <c r="J38">
+        <v>0.08248411864042282</v>
+      </c>
+      <c r="K38">
+        <v>14346394624</v>
+      </c>
+      <c r="L38">
+        <v>4.97141170501709</v>
+      </c>
+      <c r="M38">
+        <v>4.721089839935303</v>
+      </c>
+      <c r="N38" t="s">
+        <v>327</v>
+      </c>
+      <c r="O38" t="s">
+        <v>387</v>
+      </c>
+      <c r="P38" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39">
+        <v>0</v>
+      </c>
+      <c r="B39" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39">
+        <v>0.02212012135323081</v>
+      </c>
+      <c r="D39">
+        <v>0.01425058487802744</v>
+      </c>
+      <c r="E39">
+        <v>0.1786908209323883</v>
+      </c>
+      <c r="F39">
+        <v>0.00226171943359077</v>
+      </c>
+      <c r="G39">
+        <v>0.002568668220192194</v>
+      </c>
+      <c r="H39">
+        <v>1.001534482503289</v>
+      </c>
+      <c r="I39">
+        <v>0.05082324673770988</v>
+      </c>
+      <c r="J39">
+        <v>0.07974995672702789</v>
+      </c>
+      <c r="K39">
+        <v>1.355083166067416E+20</v>
+      </c>
+      <c r="L39">
+        <v>10.22761058807373</v>
+      </c>
+      <c r="M39">
+        <v>4.564596652984619</v>
+      </c>
+      <c r="N39" t="s">
+        <v>328</v>
+      </c>
+      <c r="O39" t="s">
+        <v>388</v>
+      </c>
+      <c r="P39" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40">
+        <v>0</v>
+      </c>
+      <c r="B40" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40">
+        <v>0.05455203231045545</v>
+      </c>
+      <c r="D40">
+        <v>0.03535487502813339</v>
+      </c>
+      <c r="E40">
+        <v>0.4548310935497284</v>
+      </c>
+      <c r="F40">
+        <v>0.002402603393420577</v>
+      </c>
+      <c r="G40">
+        <v>0.002933573210611939</v>
+      </c>
+      <c r="H40">
+        <v>1.002166599550321</v>
+      </c>
+      <c r="I40">
+        <v>0.05601055671979264</v>
+      </c>
+      <c r="J40">
+        <v>0.07773187756538391</v>
+      </c>
+      <c r="K40" t="s">
+        <v>110</v>
+      </c>
+      <c r="L40">
+        <v>26.03287124633789</v>
+      </c>
+      <c r="M40">
+        <v>4.449089050292969</v>
+      </c>
+      <c r="N40" t="s">
+        <v>329</v>
+      </c>
+      <c r="O40" t="s">
+        <v>389</v>
+      </c>
+      <c r="P40" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41">
+        <v>0</v>
+      </c>
+      <c r="B41" t="s">
+        <v>90</v>
+      </c>
+      <c r="C41">
+        <v>0.11258810468325</v>
+      </c>
+      <c r="D41">
+        <v>0.0668039470911026</v>
+      </c>
+      <c r="E41">
+        <v>0.8320429921150208</v>
+      </c>
+      <c r="F41">
+        <v>0.002535337349399924</v>
+      </c>
+      <c r="G41">
+        <v>0.003236496821045876</v>
+      </c>
+      <c r="H41">
+        <v>1.003916768665851</v>
+      </c>
+      <c r="I41">
+        <v>0.06496861889375367</v>
+      </c>
+      <c r="J41">
+        <v>0.08028905838727951</v>
+      </c>
+      <c r="K41" t="s">
+        <v>110</v>
+      </c>
+      <c r="L41">
+        <v>47.62310409545898</v>
+      </c>
+      <c r="M41">
+        <v>4.595452785491943</v>
+      </c>
+      <c r="N41" t="s">
+        <v>330</v>
+      </c>
+      <c r="O41" t="s">
+        <v>390</v>
+      </c>
+      <c r="P41" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42">
+        <v>0</v>
+      </c>
+      <c r="B42" t="s">
+        <v>91</v>
+      </c>
+      <c r="C42">
+        <v>0.0001794947794545635</v>
+      </c>
+      <c r="D42">
+        <v>-0.0001358174777124077</v>
+      </c>
+      <c r="E42">
+        <v>0.001968387048691511</v>
+      </c>
+      <c r="F42">
+        <v>0.001048509846441448</v>
+      </c>
+      <c r="G42">
+        <v>0.001065461430698633</v>
+      </c>
+      <c r="H42">
+        <v>1.000021159059956</v>
+      </c>
+      <c r="I42">
+        <v>0.04937793962120619</v>
+      </c>
+      <c r="J42">
+        <v>-0.06899937242269516</v>
+      </c>
+      <c r="K42">
+        <v>-0.3592005372047424</v>
+      </c>
+      <c r="L42">
+        <v>0.1126632913947105</v>
+      </c>
+      <c r="M42">
+        <v>-3.949272394180298</v>
+      </c>
+      <c r="N42" t="s">
+        <v>331</v>
+      </c>
+      <c r="O42" t="s">
+        <v>391</v>
+      </c>
+      <c r="P42" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43">
+        <v>0</v>
+      </c>
+      <c r="B43" t="s">
+        <v>92</v>
+      </c>
+      <c r="C43">
+        <v>0.0002246302635099158</v>
+      </c>
+      <c r="D43">
+        <v>-9.094681445276365E-06</v>
+      </c>
+      <c r="E43">
+        <v>0.002309769857674837</v>
+      </c>
+      <c r="F43">
+        <v>0.001215444994159043</v>
+      </c>
+      <c r="G43">
+        <v>0.001199242426082492</v>
+      </c>
+      <c r="H43">
+        <v>1.000127624004343</v>
+      </c>
+      <c r="I43">
+        <v>0.04944057478733452</v>
+      </c>
+      <c r="J43">
+        <v>-0.003937483765184879</v>
+      </c>
+      <c r="K43">
+        <v>-0.02943378686904907</v>
+      </c>
+      <c r="L43">
+        <v>0.1322028040885925</v>
+      </c>
+      <c r="M43">
+        <v>-0.2253672033548355</v>
+      </c>
+      <c r="N43" t="s">
+        <v>332</v>
+      </c>
+      <c r="O43" t="s">
+        <v>392</v>
+      </c>
+      <c r="P43" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44">
+        <v>0</v>
+      </c>
+      <c r="B44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C44">
+        <v>0.0002642918292033972</v>
+      </c>
+      <c r="D44">
+        <v>5.774127203039825E-06</v>
+      </c>
+      <c r="E44">
+        <v>0.002398795448243618</v>
+      </c>
+      <c r="F44">
+        <v>0.001302729360759258</v>
+      </c>
+      <c r="G44">
+        <v>0.001297563780099154</v>
+      </c>
+      <c r="H44">
+        <v>1.000122683100952</v>
+      </c>
+      <c r="I44">
+        <v>0.04955725148853286</v>
+      </c>
+      <c r="J44">
+        <v>0.002407094463706017</v>
+      </c>
+      <c r="K44">
+        <v>0.01892220973968506</v>
+      </c>
+      <c r="L44">
+        <v>0.1372983008623123</v>
+      </c>
+      <c r="M44">
+        <v>0.1377733051776886</v>
+      </c>
+      <c r="N44" t="s">
+        <v>333</v>
+      </c>
+      <c r="O44" t="s">
+        <v>393</v>
+      </c>
+      <c r="P44" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45">
+        <v>0</v>
+      </c>
+      <c r="B45" t="s">
+        <v>94</v>
+      </c>
+      <c r="C45">
+        <v>0.0004222852511373331</v>
+      </c>
+      <c r="D45">
+        <v>0.0002936337841674685</v>
+      </c>
+      <c r="E45">
+        <v>0.00147230876609683</v>
+      </c>
+      <c r="F45">
+        <v>0.001531677320599556</v>
+      </c>
+      <c r="G45">
+        <v>0.001520636840723455</v>
+      </c>
+      <c r="H45">
+        <v>1.000129849992502</v>
+      </c>
+      <c r="I45">
+        <v>0.04983165803468878</v>
+      </c>
+      <c r="J45">
+        <v>0.1994376331567764</v>
+      </c>
+      <c r="K45">
+        <v>1.616227149963379</v>
+      </c>
+      <c r="L45">
+        <v>0.08426958322525024</v>
+      </c>
+      <c r="M45">
+        <v>11.41508197784424</v>
+      </c>
+      <c r="N45" t="s">
+        <v>334</v>
+      </c>
+      <c r="O45" t="s">
+        <v>394</v>
+      </c>
+      <c r="P45" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46">
+        <v>0</v>
+      </c>
+      <c r="B46" t="s">
+        <v>95</v>
+      </c>
+      <c r="C46">
+        <v>0.0006698148495797513</v>
+      </c>
+      <c r="D46">
+        <v>0.0005118893459439278</v>
+      </c>
+      <c r="E46">
+        <v>0.002442462602630258</v>
+      </c>
+      <c r="F46">
+        <v>0.001787740271538496</v>
+      </c>
+      <c r="G46">
+        <v>0.001784366089850664</v>
+      </c>
+      <c r="H46">
+        <v>1.000223064859287</v>
+      </c>
+      <c r="I46">
+        <v>0.04996824725956723</v>
+      </c>
+      <c r="J46">
+        <v>0.209579199552536</v>
+      </c>
+      <c r="K46">
+        <v>4.346837043762207</v>
+      </c>
+      <c r="L46">
+        <v>0.139797642827034</v>
+      </c>
+      <c r="M46">
+        <v>11.99554824829102</v>
+      </c>
+      <c r="N46" t="s">
+        <v>335</v>
+      </c>
+      <c r="O46" t="s">
+        <v>395</v>
+      </c>
+      <c r="P46" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47">
+        <v>0</v>
+      </c>
+      <c r="B47" t="s">
+        <v>96</v>
+      </c>
+      <c r="C47">
+        <v>0.001097216241437979</v>
+      </c>
+      <c r="D47">
+        <v>0.0007945381221361458</v>
+      </c>
+      <c r="E47">
+        <v>0.004530145321041346</v>
+      </c>
+      <c r="F47">
+        <v>0.001985907088965178</v>
+      </c>
+      <c r="G47">
+        <v>0.002051212126389146</v>
+      </c>
+      <c r="H47">
+        <v>1.000466643925988</v>
+      </c>
+      <c r="I47">
+        <v>0.04980622977639557</v>
+      </c>
+      <c r="J47">
+        <v>0.1753890961408615</v>
+      </c>
+      <c r="K47">
+        <v>12.48862171173096</v>
+      </c>
+      <c r="L47">
+        <v>0.2592889964580536</v>
+      </c>
+      <c r="M47">
+        <v>10.03863143920898</v>
+      </c>
+      <c r="N47" t="s">
+        <v>336</v>
+      </c>
+      <c r="O47" t="s">
+        <v>396</v>
+      </c>
+      <c r="P47" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48">
+        <v>0</v>
+      </c>
+      <c r="B48" t="s">
+        <v>97</v>
+      </c>
+      <c r="C48">
+        <v>0.002262375416603107</v>
+      </c>
+      <c r="D48">
+        <v>0.001466941321268678</v>
+      </c>
+      <c r="E48">
+        <v>0.01101097092032433</v>
+      </c>
+      <c r="F48">
+        <v>0.002129695611074567</v>
+      </c>
+      <c r="G48">
+        <v>0.002402075566351414</v>
+      </c>
+      <c r="H48">
+        <v>1.001178337706246</v>
+      </c>
+      <c r="I48">
+        <v>0.05025641971654946</v>
+      </c>
+      <c r="J48">
+        <v>0.1332254260778427</v>
+      </c>
+      <c r="K48">
+        <v>120.7946014404297</v>
+      </c>
+      <c r="L48">
+        <v>0.63022780418396</v>
+      </c>
+      <c r="M48">
+        <v>7.62533712387085</v>
+      </c>
+      <c r="N48" t="s">
+        <v>337</v>
+      </c>
+      <c r="O48" t="s">
+        <v>397</v>
+      </c>
+      <c r="P48" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
+      <c r="A49">
+        <v>0</v>
+      </c>
+      <c r="B49" t="s">
+        <v>98</v>
+      </c>
+      <c r="C49">
+        <v>0.004112614106294083</v>
+      </c>
+      <c r="D49">
+        <v>0.002526354975998402</v>
+      </c>
+      <c r="E49">
+        <v>0.02177823521196842</v>
+      </c>
+      <c r="F49">
+        <v>0.002194986678659916</v>
+      </c>
+      <c r="G49">
+        <v>0.00259551452472806</v>
+      </c>
+      <c r="H49">
+        <v>1.001523505448249</v>
+      </c>
+      <c r="I49">
+        <v>0.05073464476821757</v>
+      </c>
+      <c r="J49">
+        <v>0.1160036623477936</v>
+      </c>
+      <c r="K49">
+        <v>3888.582763671875</v>
+      </c>
+      <c r="L49">
+        <v>1.246506690979004</v>
+      </c>
+      <c r="M49">
+        <v>6.639626502990723</v>
+      </c>
+      <c r="N49" t="s">
+        <v>338</v>
+      </c>
+      <c r="O49" t="s">
+        <v>398</v>
+      </c>
+      <c r="P49" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
+      <c r="A50">
+        <v>0</v>
+      </c>
+      <c r="B50" t="s">
+        <v>99</v>
+      </c>
+      <c r="C50">
+        <v>0.009757823131376854</v>
+      </c>
+      <c r="D50">
+        <v>0.005519339814782143</v>
+      </c>
+      <c r="E50">
+        <v>0.05551044642925262</v>
+      </c>
+      <c r="F50">
+        <v>0.002338645281270146</v>
+      </c>
+      <c r="G50">
+        <v>0.002918199170380831</v>
+      </c>
+      <c r="H50">
+        <v>1.002670524090353</v>
+      </c>
+      <c r="I50">
+        <v>0.05575669690240725</v>
+      </c>
+      <c r="J50">
+        <v>0.09942884743213654</v>
+      </c>
+      <c r="K50">
+        <v>67781872</v>
+      </c>
+      <c r="L50">
+        <v>3.177215337753296</v>
+      </c>
+      <c r="M50">
+        <v>5.690944194793701</v>
+      </c>
+      <c r="N50" t="s">
+        <v>339</v>
+      </c>
+      <c r="O50" t="s">
+        <v>399</v>
+      </c>
+      <c r="P50" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
+      <c r="A51">
+        <v>0</v>
+      </c>
+      <c r="B51" t="s">
+        <v>100</v>
+      </c>
+      <c r="C51">
+        <v>0.01886328629718548</v>
+      </c>
+      <c r="D51">
+        <v>0.01044591143727303</v>
+      </c>
+      <c r="E51">
+        <v>0.1072028800845146</v>
+      </c>
+      <c r="F51">
+        <v>0.002438319148495793</v>
+      </c>
+      <c r="G51">
+        <v>0.003238451201468706</v>
+      </c>
+      <c r="H51">
+        <v>1.003916768665851</v>
+      </c>
+      <c r="I51">
+        <v>0.06496861889375367</v>
+      </c>
+      <c r="J51">
+        <v>0.09744058549404144</v>
+      </c>
+      <c r="K51">
+        <v>609365866315776</v>
+      </c>
+      <c r="L51">
+        <v>6.13590145111084</v>
+      </c>
+      <c r="M51">
+        <v>5.577143669128418</v>
+      </c>
+      <c r="N51" t="s">
+        <v>340</v>
+      </c>
+      <c r="O51" t="s">
+        <v>400</v>
+      </c>
+      <c r="P51" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
+      <c r="A52">
+        <v>0</v>
+      </c>
+      <c r="B52" t="s">
+        <v>101</v>
+      </c>
+      <c r="C52">
+        <v>0.0001898901075328047</v>
+      </c>
+      <c r="D52">
+        <v>0.0002093537041218951</v>
+      </c>
+      <c r="E52">
+        <v>0.0006653441814705729</v>
+      </c>
+      <c r="F52">
+        <v>0.001150485826656222</v>
+      </c>
+      <c r="G52">
+        <v>0.001200916827656329</v>
+      </c>
+      <c r="H52">
+        <v>0.9995213100529909</v>
+      </c>
+      <c r="I52">
+        <v>0.04978005809323156</v>
+      </c>
+      <c r="J52">
+        <v>0.3146547377109528</v>
+      </c>
+      <c r="K52">
+        <v>0.9851574897766113</v>
+      </c>
+      <c r="L52">
+        <v>0.03808187320828438</v>
+      </c>
+      <c r="M52">
+        <v>18.00968933105469</v>
+      </c>
+      <c r="N52" t="s">
+        <v>341</v>
+      </c>
+      <c r="O52" t="s">
+        <v>401</v>
+      </c>
+      <c r="P52" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
+      <c r="A53">
+        <v>0</v>
+      </c>
+      <c r="B53" t="s">
+        <v>102</v>
+      </c>
+      <c r="C53">
+        <v>0.0002260548820411488</v>
+      </c>
+      <c r="D53">
+        <v>0.0002528608893044293</v>
+      </c>
+      <c r="E53">
+        <v>0.0007385003264062107</v>
+      </c>
+      <c r="F53">
+        <v>0.001247508800588548</v>
+      </c>
+      <c r="G53">
+        <v>0.001277093891985714</v>
+      </c>
+      <c r="H53">
+        <v>0.9995830383500868</v>
+      </c>
+      <c r="I53">
+        <v>0.04982452087093247</v>
+      </c>
+      <c r="J53">
+        <v>0.3423978090286255</v>
+      </c>
+      <c r="K53">
+        <v>1.289214372634888</v>
+      </c>
+      <c r="L53">
+        <v>0.04226906225085258</v>
+      </c>
+      <c r="M53">
+        <v>19.59760093688965</v>
+      </c>
+      <c r="N53" t="s">
+        <v>342</v>
+      </c>
+      <c r="O53" t="s">
+        <v>402</v>
+      </c>
+      <c r="P53" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
+      <c r="A54">
+        <v>0</v>
+      </c>
+      <c r="B54" t="s">
+        <v>103</v>
+      </c>
+      <c r="C54">
+        <v>0.0002537607926484374</v>
+      </c>
+      <c r="D54">
+        <v>0.0002846671850420535</v>
+      </c>
+      <c r="E54">
+        <v>0.0007838875753805041</v>
+      </c>
+      <c r="F54">
+        <v>0.001319339033216238</v>
+      </c>
+      <c r="G54">
+        <v>0.001329585793428123</v>
+      </c>
+      <c r="H54">
+        <v>0.9996007645701245</v>
+      </c>
+      <c r="I54">
+        <v>0.04989780337758544</v>
+      </c>
+      <c r="J54">
+        <v>0.3631479740142822</v>
+      </c>
+      <c r="K54">
+        <v>1.540731430053711</v>
+      </c>
+      <c r="L54">
+        <v>0.04486686363816261</v>
+      </c>
+      <c r="M54">
+        <v>20.78526496887207</v>
+      </c>
+      <c r="N54" t="s">
+        <v>343</v>
+      </c>
+      <c r="O54" t="s">
+        <v>403</v>
+      </c>
+      <c r="P54" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16">
+      <c r="A55">
+        <v>0</v>
+      </c>
+      <c r="B55" t="s">
+        <v>43</v>
+      </c>
+      <c r="C55">
+        <v>0.0003398510499977769</v>
+      </c>
+      <c r="D55">
+        <v>0.0003815244126599282</v>
+      </c>
+      <c r="E55">
+        <v>0.0009121635230258107</v>
+      </c>
+      <c r="F55">
+        <v>0.001557257492095232</v>
+      </c>
+      <c r="G55">
+        <v>0.001505801803432405</v>
+      </c>
+      <c r="H55">
+        <v>0.9996411749580352</v>
+      </c>
+      <c r="I55">
+        <v>0.05007232586610909</v>
+      </c>
+      <c r="J55">
+        <v>0.418263167142868</v>
+      </c>
+      <c r="K55">
+        <v>2.488446474075317</v>
+      </c>
+      <c r="L55">
+        <v>0.05220891162753105</v>
+      </c>
+      <c r="M55">
+        <v>23.93985748291016</v>
+      </c>
+      <c r="N55" t="s">
+        <v>344</v>
+      </c>
+      <c r="O55" t="s">
+        <v>404</v>
+      </c>
+      <c r="P55" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16">
+      <c r="A56">
+        <v>0</v>
+      </c>
+      <c r="B56" t="s">
+        <v>104</v>
+      </c>
+      <c r="C56">
+        <v>0.0004253556700982484</v>
+      </c>
+      <c r="D56">
+        <v>0.000470821833005175</v>
+      </c>
+      <c r="E56">
+        <v>0.001039086258970201</v>
+      </c>
+      <c r="F56">
+        <v>0.00169878697488457</v>
+      </c>
+      <c r="G56">
+        <v>0.001739307655952871</v>
+      </c>
+      <c r="H56">
+        <v>0.9997449908092959</v>
+      </c>
+      <c r="I56">
+        <v>0.05051977394426099</v>
+      </c>
+      <c r="J56">
+        <v>0.4531114101409912</v>
+      </c>
+      <c r="K56">
+        <v>3.674999237060547</v>
+      </c>
+      <c r="L56">
+        <v>0.05947350710630417</v>
+      </c>
+      <c r="M56">
+        <v>25.93444442749023</v>
+      </c>
+      <c r="N56" t="s">
+        <v>345</v>
+      </c>
+      <c r="O56" t="s">
+        <v>405</v>
+      </c>
+      <c r="P56" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16">
+      <c r="A57">
+        <v>0</v>
+      </c>
+      <c r="B57" t="s">
+        <v>105</v>
+      </c>
+      <c r="C57">
+        <v>0.0005071406809620028</v>
+      </c>
+      <c r="D57">
+        <v>0.0005424528499133885</v>
+      </c>
+      <c r="E57">
+        <v>0.001156656420789659</v>
+      </c>
+      <c r="F57">
+        <v>0.00171778560616076</v>
+      </c>
+      <c r="G57">
+        <v>0.001992170698940754</v>
+      </c>
+      <c r="H57">
+        <v>1.000214261871015</v>
+      </c>
+      <c r="I57">
+        <v>0.05008868772960415</v>
+      </c>
+      <c r="J57">
+        <v>0.4689835608005524</v>
+      </c>
+      <c r="K57">
+        <v>4.908713340759277</v>
+      </c>
+      <c r="L57">
+        <v>0.0662027895450592</v>
+      </c>
+      <c r="M57">
+        <v>26.8429069519043</v>
+      </c>
+      <c r="N57" t="s">
+        <v>346</v>
+      </c>
+      <c r="O57" t="s">
+        <v>406</v>
+      </c>
+      <c r="P57" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16">
+      <c r="A58">
+        <v>0</v>
+      </c>
+      <c r="B58" t="s">
+        <v>106</v>
+      </c>
+      <c r="C58">
+        <v>0.0006022236339851594</v>
+      </c>
+      <c r="D58">
+        <v>0.0006350959301926196</v>
+      </c>
+      <c r="E58">
+        <v>0.001400616252794862</v>
+      </c>
+      <c r="F58">
+        <v>0.001768385875038803</v>
+      </c>
+      <c r="G58">
+        <v>0.002299160929396749</v>
+      </c>
+      <c r="H58">
+        <v>1.001189617433305</v>
+      </c>
+      <c r="I58">
+        <v>0.04986667777099436</v>
+      </c>
+      <c r="J58">
+        <v>0.4534403681755066</v>
+      </c>
+      <c r="K58">
+        <v>7.005120277404785</v>
+      </c>
+      <c r="L58">
+        <v>0.08016616106033325</v>
+      </c>
+      <c r="M58">
+        <v>25.95327186584473</v>
+      </c>
+      <c r="N58" t="s">
+        <v>347</v>
+      </c>
+      <c r="O58" t="s">
+        <v>407</v>
+      </c>
+      <c r="P58" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16">
+      <c r="A59">
+        <v>0</v>
+      </c>
+      <c r="B59" t="s">
+        <v>107</v>
+      </c>
+      <c r="C59">
+        <v>0.0006656315024140139</v>
+      </c>
+      <c r="D59">
+        <v>0.0007346898200921714</v>
+      </c>
+      <c r="E59">
+        <v>0.00169483944773674</v>
+      </c>
+      <c r="F59">
+        <v>0.001827562926337123</v>
+      </c>
+      <c r="G59">
+        <v>0.002591700991615653</v>
+      </c>
+      <c r="H59">
+        <v>1.001514263227547</v>
+      </c>
+      <c r="I59">
+        <v>0.0502567003487565</v>
+      </c>
+      <c r="J59">
+        <v>0.4334863722324371</v>
+      </c>
+      <c r="K59">
+        <v>10.08896446228027</v>
+      </c>
+      <c r="L59">
+        <v>0.0970064252614975</v>
+      </c>
+      <c r="M59">
+        <v>24.81117820739746</v>
+      </c>
+      <c r="N59" t="s">
+        <v>348</v>
+      </c>
+      <c r="O59" t="s">
+        <v>408</v>
+      </c>
+      <c r="P59" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
+      <c r="A60">
+        <v>0</v>
+      </c>
+      <c r="B60" t="s">
+        <v>108</v>
+      </c>
+      <c r="C60">
+        <v>0.0007415195571884598</v>
+      </c>
+      <c r="D60">
+        <v>0.0008855100022628903</v>
+      </c>
+      <c r="E60">
+        <v>0.002272734418511391</v>
+      </c>
+      <c r="F60">
+        <v>0.001938214991241693</v>
+      </c>
+      <c r="G60">
+        <v>0.003090918995440006</v>
+      </c>
+      <c r="H60">
+        <v>1.002227070495124</v>
+      </c>
+      <c r="I60">
+        <v>0.05630982479745593</v>
+      </c>
+      <c r="J60">
+        <v>0.3896231651306152</v>
+      </c>
+      <c r="K60">
+        <v>17.16634178161621</v>
+      </c>
+      <c r="L60">
+        <v>0.1300830245018005</v>
+      </c>
+      <c r="M60">
+        <v>22.30060768127441</v>
+      </c>
+      <c r="N60" t="s">
+        <v>349</v>
+      </c>
+      <c r="O60" t="s">
+        <v>409</v>
+      </c>
+      <c r="P60" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16">
+      <c r="A61">
+        <v>0</v>
+      </c>
+      <c r="B61" t="s">
+        <v>109</v>
+      </c>
+      <c r="C61">
+        <v>0.0007923049871225148</v>
+      </c>
+      <c r="D61">
+        <v>0.001014259061776102</v>
+      </c>
+      <c r="E61">
+        <v>0.002871983451768756</v>
+      </c>
+      <c r="F61">
+        <v>0.002080648904666305</v>
+      </c>
+      <c r="G61">
+        <v>0.003840302349999547</v>
+      </c>
+      <c r="H61">
+        <v>1.0031211750306</v>
+      </c>
+      <c r="I61">
+        <v>0.06567985857614762</v>
+      </c>
+      <c r="J61">
+        <v>0.3531562983989716</v>
+      </c>
+      <c r="K61">
+        <v>26.68642616271973</v>
+      </c>
+      <c r="L61">
+        <v>0.1643818467855453</v>
+      </c>
+      <c r="M61">
+        <v>20.21337699890137</v>
+      </c>
+      <c r="N61" t="s">
+        <v>350</v>
+      </c>
+      <c r="O61" t="s">
+        <v>410</v>
+      </c>
+      <c r="P61" t="s">
+        <v>470</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="2:2">
+      <c r="B1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="2:2">
+      <c r="B1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="2:2">
+      <c r="B1" t="s">
+        <v>471</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/ffn_l2/performance.xlsx
+++ b/scripts/ffn_l2/performance.xlsx
@@ -8919,12 +8919,6556 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1"/>
+  <dimension ref="A1:B819"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:2">
+    <row r="1" spans="1:2">
       <c r="B1" t="s">
         <v>471</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.0005167557392269373</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>-0.0005517522222362459</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0.0009631994762457907</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>-0.0008690807153470814</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>-0.000870599877089262</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>-0.0003111491387244314</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>-0.0001719160645734519</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>0.0001937279885169119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>0.000597533886320889</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>7.098731293808669E-05</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>-0.0001636145025258884</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>0.001265499042347074</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>-0.002343899104744196</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>-0.001106761279515922</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>0.0006816422683186829</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>-0.0004558538203127682</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>-0.001076230779290199</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <v>0.0005106716998852789</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <v>0.0003751883341465145</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21">
+        <v>0.0002284495276398957</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <v>-0.0002672085829544812</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23">
+        <v>0.0006838959525339305</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24">
+        <v>0.0005475226207636297</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25">
+        <v>0.0007187617593444884</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26">
+        <v>0.00177828420419246</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27">
+        <v>0.0003804467851296067</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28">
+        <v>7.463435031240806E-05</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29">
+        <v>-0.0005856390343979001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30">
+        <v>0.0004761152958963066</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31">
+        <v>-0.001234455383382738</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32">
+        <v>-0.0003643793170340359</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33">
+        <v>0.0005505584413185716</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34">
+        <v>-0.0002313674194738269</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35">
+        <v>0.0001761356979841366</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36">
+        <v>0.0005225491477176547</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37">
+        <v>0.0003545509825926274</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38">
+        <v>-2.025414869422093E-05</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39">
+        <v>-0.0002970093337353319</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40">
+        <v>0.0008004606352187693</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41">
+        <v>0.0004115570045541972</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42">
+        <v>-5.217300349613652E-05</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43">
+        <v>0.0003844283928629011</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44">
+        <v>-0.001146517344750464</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45">
+        <v>0.001615688903257251</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46">
+        <v>0.0005586827173829079</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47">
+        <v>-0.0001015484376694076</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48">
+        <v>-7.724586612312123E-05</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49">
+        <v>0.0004144061822444201</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50">
+        <v>0.0003822262224275619</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51">
+        <v>0.0002021069667534903</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52">
+        <v>0.00194819865282625</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53">
+        <v>9.125391443376429E-06</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54">
+        <v>-5.091518323752098E-05</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55">
+        <v>0.001022838638164103</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56">
+        <v>-0.0004722692829091102</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="B57">
+        <v>0.0009470940567553043</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="B58">
+        <v>-0.0008612033561803401</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="B59">
+        <v>7.836839358787984E-05</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="B60">
+        <v>0.0004216158704366535</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61">
+        <v>59</v>
+      </c>
+      <c r="B61">
+        <v>0.0001332867832388729</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="B62">
+        <v>-2.639706872287206E-05</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="B63">
+        <v>-0.0003698712680488825</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64">
+        <v>62</v>
+      </c>
+      <c r="B64">
+        <v>0.0004343980981502682</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65">
+        <v>63</v>
+      </c>
+      <c r="B65">
+        <v>0.00158964516595006</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66">
+        <v>64</v>
+      </c>
+      <c r="B66">
+        <v>0.0004258326080162078</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67">
+        <v>65</v>
+      </c>
+      <c r="B67">
+        <v>0.00105358543805778</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68">
+        <v>66</v>
+      </c>
+      <c r="B68">
+        <v>0.0002252366975881159</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69">
+        <v>67</v>
+      </c>
+      <c r="B69">
+        <v>0.000256414758041501</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70">
+        <v>68</v>
+      </c>
+      <c r="B70">
+        <v>0.0003589913831092417</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71">
+        <v>69</v>
+      </c>
+      <c r="B71">
+        <v>0.0009245271212421358</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72">
+        <v>70</v>
+      </c>
+      <c r="B72">
+        <v>-0.0005055080400779843</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73">
+        <v>71</v>
+      </c>
+      <c r="B73">
+        <v>-0.001036696485243738</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74">
+        <v>72</v>
+      </c>
+      <c r="B74">
+        <v>8.066751615842804E-05</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75">
+        <v>73</v>
+      </c>
+      <c r="B75">
+        <v>0.0007223171414807439</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76">
+        <v>74</v>
+      </c>
+      <c r="B76">
+        <v>0.001500098034739494</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77">
+        <v>75</v>
+      </c>
+      <c r="B77">
+        <v>-9.988876990973949E-05</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78">
+        <v>76</v>
+      </c>
+      <c r="B78">
+        <v>0.001222511171363294</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79">
+        <v>77</v>
+      </c>
+      <c r="B79">
+        <v>-0.0004489113634917885</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80">
+        <v>78</v>
+      </c>
+      <c r="B80">
+        <v>0.0008600131841376424</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81">
+        <v>79</v>
+      </c>
+      <c r="B81">
+        <v>9.519341983832419E-05</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82">
+        <v>80</v>
+      </c>
+      <c r="B82">
+        <v>0.0001313299871981144</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83">
+        <v>81</v>
+      </c>
+      <c r="B83">
+        <v>0.0003381041460670531</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84">
+        <v>82</v>
+      </c>
+      <c r="B84">
+        <v>-9.283590043196455E-05</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85">
+        <v>83</v>
+      </c>
+      <c r="B85">
+        <v>-0.0001169123424915597</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86">
+        <v>84</v>
+      </c>
+      <c r="B86">
+        <v>-0.0001736694248393178</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87">
+        <v>85</v>
+      </c>
+      <c r="B87">
+        <v>-0.00020884137484245</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88">
+        <v>86</v>
+      </c>
+      <c r="B88">
+        <v>0.0005094276275485754</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89">
+        <v>87</v>
+      </c>
+      <c r="B89">
+        <v>-0.0002357173361815512</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90">
+        <v>88</v>
+      </c>
+      <c r="B90">
+        <v>0.0003410238714423031</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91">
+        <v>89</v>
+      </c>
+      <c r="B91">
+        <v>0.0004080410581082106</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92">
+        <v>90</v>
+      </c>
+      <c r="B92">
+        <v>0.000144528501550667</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93">
+        <v>91</v>
+      </c>
+      <c r="B93">
+        <v>-0.0008643899927847087</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94">
+        <v>92</v>
+      </c>
+      <c r="B94">
+        <v>0.0007277270779013634</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95">
+        <v>93</v>
+      </c>
+      <c r="B95">
+        <v>0.001123272348195314</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96">
+        <v>94</v>
+      </c>
+      <c r="B96">
+        <v>-0.0004129987792111933</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97">
+        <v>95</v>
+      </c>
+      <c r="B97">
+        <v>0.0002657805453054607</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98">
+        <v>96</v>
+      </c>
+      <c r="B98">
+        <v>0.0002519722329452634</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99">
+        <v>97</v>
+      </c>
+      <c r="B99">
+        <v>0.0002188611688325182</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100">
+        <v>98</v>
+      </c>
+      <c r="B100">
+        <v>0.0001140592648880556</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101">
+        <v>99</v>
+      </c>
+      <c r="B101">
+        <v>-0.0003022043965756893</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102">
+        <v>100</v>
+      </c>
+      <c r="B102">
+        <v>-0.0001751717500155792</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103">
+        <v>101</v>
+      </c>
+      <c r="B103">
+        <v>-0.0001059047499438748</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104">
+        <v>102</v>
+      </c>
+      <c r="B104">
+        <v>-0.0004775922279804945</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105">
+        <v>103</v>
+      </c>
+      <c r="B105">
+        <v>0.000317918456858024</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106">
+        <v>104</v>
+      </c>
+      <c r="B106">
+        <v>0.0002934923104476184</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107">
+        <v>105</v>
+      </c>
+      <c r="B107">
+        <v>0.000860891945194453</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108">
+        <v>106</v>
+      </c>
+      <c r="B108">
+        <v>0.001550419139675796</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109">
+        <v>107</v>
+      </c>
+      <c r="B109">
+        <v>-0.0002956031239591539</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110">
+        <v>108</v>
+      </c>
+      <c r="B110">
+        <v>-0.0002108560438500717</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111">
+        <v>109</v>
+      </c>
+      <c r="B111">
+        <v>0.001314871828071773</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112">
+        <v>110</v>
+      </c>
+      <c r="B112">
+        <v>7.47262965887785E-05</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113">
+        <v>111</v>
+      </c>
+      <c r="B113">
+        <v>-0.0002344266249565408</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114">
+        <v>112</v>
+      </c>
+      <c r="B114">
+        <v>0.00100572663359344</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115">
+        <v>113</v>
+      </c>
+      <c r="B115">
+        <v>-0.0001672182115726173</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116">
+        <v>114</v>
+      </c>
+      <c r="B116">
+        <v>0.0002366554836044088</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117">
+        <v>115</v>
+      </c>
+      <c r="B117">
+        <v>0.00258440081961453</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118">
+        <v>116</v>
+      </c>
+      <c r="B118">
+        <v>-0.0002678596647456288</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119">
+        <v>117</v>
+      </c>
+      <c r="B119">
+        <v>0.001025601290166378</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120">
+        <v>118</v>
+      </c>
+      <c r="B120">
+        <v>-0.0001635561347939074</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121">
+        <v>119</v>
+      </c>
+      <c r="B121">
+        <v>0.0002517137327231467</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122">
+        <v>120</v>
+      </c>
+      <c r="B122">
+        <v>0.0005138840060681105</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123">
+        <v>121</v>
+      </c>
+      <c r="B123">
+        <v>-0.0007166818249970675</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124">
+        <v>122</v>
+      </c>
+      <c r="B124">
+        <v>0.000304713350487873</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125">
+        <v>123</v>
+      </c>
+      <c r="B125">
+        <v>0.000799075816757977</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126">
+        <v>124</v>
+      </c>
+      <c r="B126">
+        <v>-0.0003281316021457314</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127">
+        <v>125</v>
+      </c>
+      <c r="B127">
+        <v>0.001844057231210172</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128">
+        <v>126</v>
+      </c>
+      <c r="B128">
+        <v>0.0001898233167594299</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129">
+        <v>127</v>
+      </c>
+      <c r="B129">
+        <v>0.0003884401230607182</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130">
+        <v>128</v>
+      </c>
+      <c r="B130">
+        <v>0.0006419826531782746</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131">
+        <v>129</v>
+      </c>
+      <c r="B131">
+        <v>-0.0003449212817940861</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132">
+        <v>130</v>
+      </c>
+      <c r="B132">
+        <v>7.436232408508658E-05</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133">
+        <v>131</v>
+      </c>
+      <c r="B133">
+        <v>-0.0004326951457187533</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134">
+        <v>132</v>
+      </c>
+      <c r="B134">
+        <v>0.0001555574854137376</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135">
+        <v>133</v>
+      </c>
+      <c r="B135">
+        <v>0.0001422728382749483</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136">
+        <v>134</v>
+      </c>
+      <c r="B136">
+        <v>0.0003569931432139128</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137">
+        <v>135</v>
+      </c>
+      <c r="B137">
+        <v>0.001067321049049497</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138">
+        <v>136</v>
+      </c>
+      <c r="B138">
+        <v>0.0001737776910886168</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139">
+        <v>137</v>
+      </c>
+      <c r="B139">
+        <v>-0.0002562290464993566</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140">
+        <v>138</v>
+      </c>
+      <c r="B140">
+        <v>0.0007519603823311627</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141">
+        <v>139</v>
+      </c>
+      <c r="B141">
+        <v>5.988136399537325E-05</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142">
+        <v>140</v>
+      </c>
+      <c r="B142">
+        <v>-0.0004688517074100673</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143">
+        <v>141</v>
+      </c>
+      <c r="B143">
+        <v>0.004102262668311596</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144">
+        <v>142</v>
+      </c>
+      <c r="B144">
+        <v>-0.0007873516296967864</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145">
+        <v>143</v>
+      </c>
+      <c r="B145">
+        <v>0.0003205541870556772</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146">
+        <v>144</v>
+      </c>
+      <c r="B146">
+        <v>0.0001852007553679869</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147">
+        <v>145</v>
+      </c>
+      <c r="B147">
+        <v>6.878570275148377E-05</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148">
+        <v>146</v>
+      </c>
+      <c r="B148">
+        <v>0.0008902252302505076</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149">
+        <v>147</v>
+      </c>
+      <c r="B149">
+        <v>0.000821317546069622</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150">
+        <v>148</v>
+      </c>
+      <c r="B150">
+        <v>0.000184684366104193</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151">
+        <v>149</v>
+      </c>
+      <c r="B151">
+        <v>0.0002094500814564526</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152">
+        <v>150</v>
+      </c>
+      <c r="B152">
+        <v>0.0001874195586424321</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153">
+        <v>151</v>
+      </c>
+      <c r="B153">
+        <v>0.000432066764915362</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154">
+        <v>152</v>
+      </c>
+      <c r="B154">
+        <v>-0.000249329605139792</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155">
+        <v>153</v>
+      </c>
+      <c r="B155">
+        <v>-0.0001752460084389895</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156">
+        <v>154</v>
+      </c>
+      <c r="B156">
+        <v>0.002176590263843536</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157">
+        <v>155</v>
+      </c>
+      <c r="B157">
+        <v>2.107219188474119E-05</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158">
+        <v>156</v>
+      </c>
+      <c r="B158">
+        <v>0.0004441042256075889</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159">
+        <v>157</v>
+      </c>
+      <c r="B159">
+        <v>0.001060197595506907</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160">
+        <v>158</v>
+      </c>
+      <c r="B160">
+        <v>0.0001989056909224018</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161">
+        <v>159</v>
+      </c>
+      <c r="B161">
+        <v>0.000220820787944831</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162">
+        <v>160</v>
+      </c>
+      <c r="B162">
+        <v>0.0001779756712494418</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163">
+        <v>161</v>
+      </c>
+      <c r="B163">
+        <v>0.000263843423454091</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164">
+        <v>162</v>
+      </c>
+      <c r="B164">
+        <v>0.001043710275553167</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165">
+        <v>163</v>
+      </c>
+      <c r="B165">
+        <v>0.0003475629782769829</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166">
+        <v>164</v>
+      </c>
+      <c r="B166">
+        <v>0.0001786941138561815</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167">
+        <v>165</v>
+      </c>
+      <c r="B167">
+        <v>0.000534522405359894</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168">
+        <v>166</v>
+      </c>
+      <c r="B168">
+        <v>-2.022404856916182E-07</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169">
+        <v>167</v>
+      </c>
+      <c r="B169">
+        <v>0.001669164514169097</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170">
+        <v>168</v>
+      </c>
+      <c r="B170">
+        <v>0.0004570551100187004</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171">
+        <v>169</v>
+      </c>
+      <c r="B171">
+        <v>-1.120462093240349E-05</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172">
+        <v>170</v>
+      </c>
+      <c r="B172">
+        <v>-2.334212467758334E-06</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173">
+        <v>171</v>
+      </c>
+      <c r="B173">
+        <v>-4.64178629044909E-05</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174">
+        <v>172</v>
+      </c>
+      <c r="B174">
+        <v>0.000635890755802393</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175">
+        <v>173</v>
+      </c>
+      <c r="B175">
+        <v>0.0003695078485179693</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176">
+        <v>174</v>
+      </c>
+      <c r="B176">
+        <v>0.0002856050850823522</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177">
+        <v>175</v>
+      </c>
+      <c r="B177">
+        <v>0.0004053556185681373</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178">
+        <v>176</v>
+      </c>
+      <c r="B178">
+        <v>0.0001999865198740736</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179">
+        <v>177</v>
+      </c>
+      <c r="B179">
+        <v>0.0001801775360945612</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180">
+        <v>178</v>
+      </c>
+      <c r="B180">
+        <v>0.000447954807896167</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181">
+        <v>179</v>
+      </c>
+      <c r="B181">
+        <v>0.0003146783856209368</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182">
+        <v>180</v>
+      </c>
+      <c r="B182">
+        <v>0.0004958650679327548</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183">
+        <v>181</v>
+      </c>
+      <c r="B183">
+        <v>-5.809201320516877E-05</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184">
+        <v>182</v>
+      </c>
+      <c r="B184">
+        <v>0.0003229620342608541</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185">
+        <v>183</v>
+      </c>
+      <c r="B185">
+        <v>-1.782638355507515E-05</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186">
+        <v>184</v>
+      </c>
+      <c r="B186">
+        <v>0.0003084346826653928</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187">
+        <v>185</v>
+      </c>
+      <c r="B187">
+        <v>7.668002945138142E-05</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188">
+        <v>186</v>
+      </c>
+      <c r="B188">
+        <v>0.0001094343242584728</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189">
+        <v>187</v>
+      </c>
+      <c r="B189">
+        <v>0.001684625167399645</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190">
+        <v>188</v>
+      </c>
+      <c r="B190">
+        <v>0.0003854221140500158</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191">
+        <v>189</v>
+      </c>
+      <c r="B191">
+        <v>0.0002231150428997353</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192">
+        <v>190</v>
+      </c>
+      <c r="B192">
+        <v>0.0002986185136251152</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193">
+        <v>191</v>
+      </c>
+      <c r="B193">
+        <v>-0.000187405850738287</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194">
+        <v>192</v>
+      </c>
+      <c r="B194">
+        <v>0.001094339299015701</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195">
+        <v>193</v>
+      </c>
+      <c r="B195">
+        <v>0.003233132185414433</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196">
+        <v>194</v>
+      </c>
+      <c r="B196">
+        <v>-0.0001512462185928598</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197">
+        <v>195</v>
+      </c>
+      <c r="B197">
+        <v>-4.38444440078456E-05</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198">
+        <v>196</v>
+      </c>
+      <c r="B198">
+        <v>0.0003625658573582768</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199">
+        <v>197</v>
+      </c>
+      <c r="B199">
+        <v>0.0001169262395706028</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200">
+        <v>198</v>
+      </c>
+      <c r="B200">
+        <v>9.21829923754558E-05</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201">
+        <v>199</v>
+      </c>
+      <c r="B201">
+        <v>0.0003147097595501691</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202">
+        <v>200</v>
+      </c>
+      <c r="B202">
+        <v>0.0001409070828231052</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203">
+        <v>201</v>
+      </c>
+      <c r="B203">
+        <v>-0.0003656476619653404</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204">
+        <v>202</v>
+      </c>
+      <c r="B204">
+        <v>0.001349156140349805</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205">
+        <v>203</v>
+      </c>
+      <c r="B205">
+        <v>0.0002595375117380172</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206">
+        <v>204</v>
+      </c>
+      <c r="B206">
+        <v>6.962195766391233E-05</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207">
+        <v>205</v>
+      </c>
+      <c r="B207">
+        <v>0.0003179188934154809</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208">
+        <v>206</v>
+      </c>
+      <c r="B208">
+        <v>-0.001758087426424026</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209">
+        <v>207</v>
+      </c>
+      <c r="B209">
+        <v>0.001102698035538197</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210">
+        <v>208</v>
+      </c>
+      <c r="B210">
+        <v>0.001200872822664678</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211">
+        <v>209</v>
+      </c>
+      <c r="B211">
+        <v>0.0002070398477371782</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212">
+        <v>210</v>
+      </c>
+      <c r="B212">
+        <v>0.0001634371001273394</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213">
+        <v>211</v>
+      </c>
+      <c r="B213">
+        <v>0.0002488636237103492</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214">
+        <v>212</v>
+      </c>
+      <c r="B214">
+        <v>0.0001238601835211739</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215">
+        <v>213</v>
+      </c>
+      <c r="B215">
+        <v>0.0001516999618615955</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216">
+        <v>214</v>
+      </c>
+      <c r="B216">
+        <v>-5.582371522905305E-05</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217">
+        <v>215</v>
+      </c>
+      <c r="B217">
+        <v>0.0006401030113920569</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218">
+        <v>216</v>
+      </c>
+      <c r="B218">
+        <v>0.0003222829545848072</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219">
+        <v>217</v>
+      </c>
+      <c r="B219">
+        <v>3.634060340118594E-05</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220">
+        <v>218</v>
+      </c>
+      <c r="B220">
+        <v>0.000289570598397404</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221">
+        <v>219</v>
+      </c>
+      <c r="B221">
+        <v>-0.00236764713190496</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222">
+        <v>220</v>
+      </c>
+      <c r="B222">
+        <v>0.0007854094728827477</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223">
+        <v>221</v>
+      </c>
+      <c r="B223">
+        <v>0.0006855967221781611</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224">
+        <v>222</v>
+      </c>
+      <c r="B224">
+        <v>0.0008003589464351535</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225">
+        <v>223</v>
+      </c>
+      <c r="B225">
+        <v>0.0002901421394199133</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226">
+        <v>224</v>
+      </c>
+      <c r="B226">
+        <v>0.0006131842383183539</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227">
+        <v>225</v>
+      </c>
+      <c r="B227">
+        <v>0.0003821636200882494</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228">
+        <v>226</v>
+      </c>
+      <c r="B228">
+        <v>-0.0001766752830008045</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229">
+        <v>227</v>
+      </c>
+      <c r="B229">
+        <v>0.0005044600111432374</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230">
+        <v>228</v>
+      </c>
+      <c r="B230">
+        <v>0.0009552733972668648</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231">
+        <v>229</v>
+      </c>
+      <c r="B231">
+        <v>0.0006464658654294908</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232">
+        <v>230</v>
+      </c>
+      <c r="B232">
+        <v>0.0003317795053590089</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233">
+        <v>231</v>
+      </c>
+      <c r="B233">
+        <v>-0.0001007698010653257</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234">
+        <v>232</v>
+      </c>
+      <c r="B234">
+        <v>0.0001423955545760691</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235">
+        <v>233</v>
+      </c>
+      <c r="B235">
+        <v>0.000330586452037096</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236">
+        <v>234</v>
+      </c>
+      <c r="B236">
+        <v>-0.0001074735555448569</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237">
+        <v>235</v>
+      </c>
+      <c r="B237">
+        <v>0.001066432450897992</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238">
+        <v>236</v>
+      </c>
+      <c r="B238">
+        <v>-0.0001237379037775099</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239">
+        <v>237</v>
+      </c>
+      <c r="B239">
+        <v>-0.0008310861303471029</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240">
+        <v>238</v>
+      </c>
+      <c r="B240">
+        <v>-4.720111974165775E-05</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241">
+        <v>239</v>
+      </c>
+      <c r="B241">
+        <v>0.001978473970666528</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242">
+        <v>240</v>
+      </c>
+      <c r="B242">
+        <v>6.564732757396996E-05</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243">
+        <v>241</v>
+      </c>
+      <c r="B243">
+        <v>5.13426202815026E-05</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="A244">
+        <v>242</v>
+      </c>
+      <c r="B244">
+        <v>0.0002607597853057086</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="A245">
+        <v>243</v>
+      </c>
+      <c r="B245">
+        <v>4.003651702078059E-05</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="A246">
+        <v>244</v>
+      </c>
+      <c r="B246">
+        <v>-8.783608063822612E-05</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2">
+      <c r="A247">
+        <v>245</v>
+      </c>
+      <c r="B247">
+        <v>0.002092856215313077</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248">
+        <v>246</v>
+      </c>
+      <c r="B248">
+        <v>0.0006011614459566772</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2">
+      <c r="A249">
+        <v>247</v>
+      </c>
+      <c r="B249">
+        <v>0.0001554107730044052</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250">
+        <v>248</v>
+      </c>
+      <c r="B250">
+        <v>0.0007033979636617005</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2">
+      <c r="A251">
+        <v>249</v>
+      </c>
+      <c r="B251">
+        <v>0.0002168465725844726</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252">
+        <v>250</v>
+      </c>
+      <c r="B252">
+        <v>0.0001822137273848057</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253">
+        <v>251</v>
+      </c>
+      <c r="B253">
+        <v>0.0003807934699580073</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254">
+        <v>252</v>
+      </c>
+      <c r="B254">
+        <v>1.982281537493691E-05</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255">
+        <v>253</v>
+      </c>
+      <c r="B255">
+        <v>0.001550265704281628</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256">
+        <v>254</v>
+      </c>
+      <c r="B256">
+        <v>0.0004450890119187534</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257">
+        <v>255</v>
+      </c>
+      <c r="B257">
+        <v>0.0003909498627763242</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258">
+        <v>256</v>
+      </c>
+      <c r="B258">
+        <v>0.0002885897411033511</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259">
+        <v>257</v>
+      </c>
+      <c r="B259">
+        <v>-8.334442100021988E-06</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260">
+        <v>258</v>
+      </c>
+      <c r="B260">
+        <v>0.001974522136151791</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="A261">
+        <v>259</v>
+      </c>
+      <c r="B261">
+        <v>-6.58417193335481E-05</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262">
+        <v>260</v>
+      </c>
+      <c r="B262">
+        <v>0.0002710595435928553</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263">
+        <v>261</v>
+      </c>
+      <c r="B263">
+        <v>-3.075628046644852E-05</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="A264">
+        <v>262</v>
+      </c>
+      <c r="B264">
+        <v>-6.462242890847847E-05</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="A265">
+        <v>263</v>
+      </c>
+      <c r="B265">
+        <v>2.980546378239524E-05</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266">
+        <v>264</v>
+      </c>
+      <c r="B266">
+        <v>0.0001184399807243608</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="A267">
+        <v>265</v>
+      </c>
+      <c r="B267">
+        <v>0.0003242113743908703</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268">
+        <v>266</v>
+      </c>
+      <c r="B268">
+        <v>-6.203245720826089E-05</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269">
+        <v>267</v>
+      </c>
+      <c r="B269">
+        <v>0.0001485798420617357</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2">
+      <c r="A270">
+        <v>268</v>
+      </c>
+      <c r="B270">
+        <v>-0.0001546497369417921</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2">
+      <c r="A271">
+        <v>269</v>
+      </c>
+      <c r="B271">
+        <v>0.0004591532342601568</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="A272">
+        <v>270</v>
+      </c>
+      <c r="B272">
+        <v>-0.0007466514362022281</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273">
+        <v>271</v>
+      </c>
+      <c r="B273">
+        <v>0.002293965080752969</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274">
+        <v>272</v>
+      </c>
+      <c r="B274">
+        <v>5.957038592896424E-05</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275">
+        <v>273</v>
+      </c>
+      <c r="B275">
+        <v>8.401241939282045E-05</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276">
+        <v>274</v>
+      </c>
+      <c r="B276">
+        <v>6.689199653919786E-05</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2">
+      <c r="A277">
+        <v>275</v>
+      </c>
+      <c r="B277">
+        <v>0.0001314029650529847</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278">
+        <v>276</v>
+      </c>
+      <c r="B278">
+        <v>-3.708164285853854E-06</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279">
+        <v>277</v>
+      </c>
+      <c r="B279">
+        <v>0.0001956737105501816</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="A280">
+        <v>278</v>
+      </c>
+      <c r="B280">
+        <v>-8.230563253164291E-05</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2">
+      <c r="A281">
+        <v>279</v>
+      </c>
+      <c r="B281">
+        <v>0.0002298216713825241</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2">
+      <c r="A282">
+        <v>280</v>
+      </c>
+      <c r="B282">
+        <v>0.000250817189225927</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2">
+      <c r="A283">
+        <v>281</v>
+      </c>
+      <c r="B283">
+        <v>0.0001697434054221958</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2">
+      <c r="A284">
+        <v>282</v>
+      </c>
+      <c r="B284">
+        <v>-4.467740654945374E-05</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="A285">
+        <v>283</v>
+      </c>
+      <c r="B285">
+        <v>-0.0001070867801900022</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2">
+      <c r="A286">
+        <v>284</v>
+      </c>
+      <c r="B286">
+        <v>-0.001428985502570868</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2">
+      <c r="A287">
+        <v>285</v>
+      </c>
+      <c r="B287">
+        <v>0.00062409887323156</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2">
+      <c r="A288">
+        <v>286</v>
+      </c>
+      <c r="B288">
+        <v>0.0005347933038137853</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289">
+        <v>287</v>
+      </c>
+      <c r="B289">
+        <v>0.0002504966396372765</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2">
+      <c r="A290">
+        <v>288</v>
+      </c>
+      <c r="B290">
+        <v>-1.073596831702162E-05</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2">
+      <c r="A291">
+        <v>289</v>
+      </c>
+      <c r="B291">
+        <v>-2.239069908682723E-05</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292">
+        <v>290</v>
+      </c>
+      <c r="B292">
+        <v>0.0005503518623299897</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2">
+      <c r="A293">
+        <v>291</v>
+      </c>
+      <c r="B293">
+        <v>0.000399085518438369</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="A294">
+        <v>292</v>
+      </c>
+      <c r="B294">
+        <v>-8.168657222995535E-05</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295">
+        <v>293</v>
+      </c>
+      <c r="B295">
+        <v>0.0007076070178300142</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2">
+      <c r="A296">
+        <v>294</v>
+      </c>
+      <c r="B296">
+        <v>0.000351875030901283</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297">
+        <v>295</v>
+      </c>
+      <c r="B297">
+        <v>0.0003930279344785959</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="A298">
+        <v>296</v>
+      </c>
+      <c r="B298">
+        <v>0.0003977626038249582</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299">
+        <v>297</v>
+      </c>
+      <c r="B299">
+        <v>-0.001338961650617421</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="A300">
+        <v>298</v>
+      </c>
+      <c r="B300">
+        <v>0.0004841193149331957</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2">
+      <c r="A301">
+        <v>299</v>
+      </c>
+      <c r="B301">
+        <v>0.0003756391815841198</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="A302">
+        <v>300</v>
+      </c>
+      <c r="B302">
+        <v>0.0001335151464445516</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2">
+      <c r="A303">
+        <v>301</v>
+      </c>
+      <c r="B303">
+        <v>0.0004497291811276227</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2">
+      <c r="A304">
+        <v>302</v>
+      </c>
+      <c r="B304">
+        <v>0.0002910476177930832</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2">
+      <c r="A305">
+        <v>303</v>
+      </c>
+      <c r="B305">
+        <v>0.0003024901379831135</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2">
+      <c r="A306">
+        <v>304</v>
+      </c>
+      <c r="B306">
+        <v>0.0002544750750530511</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2">
+      <c r="A307">
+        <v>305</v>
+      </c>
+      <c r="B307">
+        <v>0.0002458074595779181</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308">
+        <v>306</v>
+      </c>
+      <c r="B308">
+        <v>-0.0001957249332917854</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2">
+      <c r="A309">
+        <v>307</v>
+      </c>
+      <c r="B309">
+        <v>0.000972958339843899</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2">
+      <c r="A310">
+        <v>308</v>
+      </c>
+      <c r="B310">
+        <v>0.0001108535652747378</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2">
+      <c r="A311">
+        <v>309</v>
+      </c>
+      <c r="B311">
+        <v>0.0002664312196429819</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2">
+      <c r="A312">
+        <v>310</v>
+      </c>
+      <c r="B312">
+        <v>-4.106565393158235E-05</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2">
+      <c r="A313">
+        <v>311</v>
+      </c>
+      <c r="B313">
+        <v>-0.0003887670754920691</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314">
+        <v>312</v>
+      </c>
+      <c r="B314">
+        <v>0.001083848648704588</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2">
+      <c r="A315">
+        <v>313</v>
+      </c>
+      <c r="B315">
+        <v>0.001122822635807097</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2">
+      <c r="A316">
+        <v>314</v>
+      </c>
+      <c r="B316">
+        <v>0.0008651104290038347</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2">
+      <c r="A317">
+        <v>315</v>
+      </c>
+      <c r="B317">
+        <v>0.0002175118570448831</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2">
+      <c r="A318">
+        <v>316</v>
+      </c>
+      <c r="B318">
+        <v>0.0002519812260288745</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2">
+      <c r="A319">
+        <v>317</v>
+      </c>
+      <c r="B319">
+        <v>0.0004421517951413989</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2">
+      <c r="A320">
+        <v>318</v>
+      </c>
+      <c r="B320">
+        <v>-0.0001753305550664663</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2">
+      <c r="A321">
+        <v>319</v>
+      </c>
+      <c r="B321">
+        <v>0.000285575952148065</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2">
+      <c r="A322">
+        <v>320</v>
+      </c>
+      <c r="B322">
+        <v>0.000231197802349925</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2">
+      <c r="A323">
+        <v>321</v>
+      </c>
+      <c r="B323">
+        <v>-2.783973468467593E-05</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2">
+      <c r="A324">
+        <v>322</v>
+      </c>
+      <c r="B324">
+        <v>-0.0007014975417405367</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2">
+      <c r="A325">
+        <v>323</v>
+      </c>
+      <c r="B325">
+        <v>-0.001342028728686273</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2">
+      <c r="A326">
+        <v>324</v>
+      </c>
+      <c r="B326">
+        <v>0.0006506193894892931</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2">
+      <c r="A327">
+        <v>325</v>
+      </c>
+      <c r="B327">
+        <v>0.001478178193792701</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2">
+      <c r="A328">
+        <v>326</v>
+      </c>
+      <c r="B328">
+        <v>-0.0002639050071593374</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2">
+      <c r="A329">
+        <v>327</v>
+      </c>
+      <c r="B329">
+        <v>-7.727045885985717E-05</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2">
+      <c r="A330">
+        <v>328</v>
+      </c>
+      <c r="B330">
+        <v>2.087149914586917E-05</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2">
+      <c r="A331">
+        <v>329</v>
+      </c>
+      <c r="B331">
+        <v>0.0001009871775750071</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2">
+      <c r="A332">
+        <v>330</v>
+      </c>
+      <c r="B332">
+        <v>0.001279223128221929</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2">
+      <c r="A333">
+        <v>331</v>
+      </c>
+      <c r="B333">
+        <v>0.001222944352775812</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2">
+      <c r="A334">
+        <v>332</v>
+      </c>
+      <c r="B334">
+        <v>0.0008057138766162097</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2">
+      <c r="A335">
+        <v>333</v>
+      </c>
+      <c r="B335">
+        <v>0.000679941033013165</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2">
+      <c r="A336">
+        <v>334</v>
+      </c>
+      <c r="B336">
+        <v>0.0004678203258663416</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337">
+        <v>335</v>
+      </c>
+      <c r="B337">
+        <v>0.001712886383756995</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="A338">
+        <v>336</v>
+      </c>
+      <c r="B338">
+        <v>0.0005002666148357093</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339">
+        <v>337</v>
+      </c>
+      <c r="B339">
+        <v>0.0008121193968690932</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2">
+      <c r="A340">
+        <v>338</v>
+      </c>
+      <c r="B340">
+        <v>-0.0007378630107268691</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="A341">
+        <v>339</v>
+      </c>
+      <c r="B341">
+        <v>-0.0001032345535350032</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2">
+      <c r="A342">
+        <v>340</v>
+      </c>
+      <c r="B342">
+        <v>1.518157296231948E-05</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="A343">
+        <v>341</v>
+      </c>
+      <c r="B343">
+        <v>2.214082633145154E-05</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2">
+      <c r="A344">
+        <v>342</v>
+      </c>
+      <c r="B344">
+        <v>0.0004385647771414369</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2">
+      <c r="A345">
+        <v>343</v>
+      </c>
+      <c r="B345">
+        <v>0.0006820636335760355</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346">
+        <v>344</v>
+      </c>
+      <c r="B346">
+        <v>4.307862036512233E-05</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="A347">
+        <v>345</v>
+      </c>
+      <c r="B347">
+        <v>0.0004532916645985097</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="A348">
+        <v>346</v>
+      </c>
+      <c r="B348">
+        <v>0.0001365967618767172</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="A349">
+        <v>347</v>
+      </c>
+      <c r="B349">
+        <v>0.0001838421594584361</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2">
+      <c r="A350">
+        <v>348</v>
+      </c>
+      <c r="B350">
+        <v>0.000548758078366518</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2">
+      <c r="A351">
+        <v>349</v>
+      </c>
+      <c r="B351">
+        <v>0.0006820336566306651</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="A352">
+        <v>350</v>
+      </c>
+      <c r="B352">
+        <v>0.001644574105739594</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2">
+      <c r="A353">
+        <v>351</v>
+      </c>
+      <c r="B353">
+        <v>0.0009021487785503268</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2">
+      <c r="A354">
+        <v>352</v>
+      </c>
+      <c r="B354">
+        <v>0.0008252092520706356</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2">
+      <c r="A355">
+        <v>353</v>
+      </c>
+      <c r="B355">
+        <v>0.001305367215536535</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2">
+      <c r="A356">
+        <v>354</v>
+      </c>
+      <c r="B356">
+        <v>0.001259323442354798</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2">
+      <c r="A357">
+        <v>355</v>
+      </c>
+      <c r="B357">
+        <v>0.0004255062958691269</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2">
+      <c r="A358">
+        <v>356</v>
+      </c>
+      <c r="B358">
+        <v>0.0002475997316651046</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2">
+      <c r="A359">
+        <v>357</v>
+      </c>
+      <c r="B359">
+        <v>0.0001378636807203293</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2">
+      <c r="A360">
+        <v>358</v>
+      </c>
+      <c r="B360">
+        <v>0.0005587946507148445</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361">
+        <v>359</v>
+      </c>
+      <c r="B361">
+        <v>-0.0003160887863487005</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362">
+        <v>360</v>
+      </c>
+      <c r="B362">
+        <v>0.0003725360729731619</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363">
+        <v>361</v>
+      </c>
+      <c r="B363">
+        <v>0.002138327807188034</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364">
+        <v>362</v>
+      </c>
+      <c r="B364">
+        <v>-0.000262572051724419</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365">
+        <v>363</v>
+      </c>
+      <c r="B365">
+        <v>-0.001265758648514748</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366">
+        <v>364</v>
+      </c>
+      <c r="B366">
+        <v>-0.0005487186717800796</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367">
+        <v>365</v>
+      </c>
+      <c r="B367">
+        <v>0.0007761640008538961</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368">
+        <v>366</v>
+      </c>
+      <c r="B368">
+        <v>0.0005124117014929652</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369">
+        <v>367</v>
+      </c>
+      <c r="B369">
+        <v>0.0009807456517592072</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370">
+        <v>368</v>
+      </c>
+      <c r="B370">
+        <v>-0.0001058988127624616</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371">
+        <v>369</v>
+      </c>
+      <c r="B371">
+        <v>0.0002762805670499802</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372">
+        <v>370</v>
+      </c>
+      <c r="B372">
+        <v>-0.0003881275479216129</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373">
+        <v>371</v>
+      </c>
+      <c r="B373">
+        <v>0.0004392190894577652</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374">
+        <v>372</v>
+      </c>
+      <c r="B374">
+        <v>0.0002249661047244444</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375">
+        <v>373</v>
+      </c>
+      <c r="B375">
+        <v>-0.000128290441352874</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2">
+      <c r="A376">
+        <v>374</v>
+      </c>
+      <c r="B376">
+        <v>0.0004760733572766185</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377">
+        <v>375</v>
+      </c>
+      <c r="B377">
+        <v>0.00191046146210283</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378">
+        <v>376</v>
+      </c>
+      <c r="B378">
+        <v>0.0008020225213840604</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379">
+        <v>377</v>
+      </c>
+      <c r="B379">
+        <v>0.0008106663008220494</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380">
+        <v>378</v>
+      </c>
+      <c r="B380">
+        <v>-0.0001100482913898304</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2">
+      <c r="A381">
+        <v>379</v>
+      </c>
+      <c r="B381">
+        <v>7.077784539433196E-05</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2">
+      <c r="A382">
+        <v>380</v>
+      </c>
+      <c r="B382">
+        <v>0.0007099955691955984</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
+      <c r="A383">
+        <v>381</v>
+      </c>
+      <c r="B383">
+        <v>7.964532414916903E-05</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2">
+      <c r="A384">
+        <v>382</v>
+      </c>
+      <c r="B384">
+        <v>0.0006832208600826561</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385">
+        <v>383</v>
+      </c>
+      <c r="B385">
+        <v>-2.083226354443468E-05</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2">
+      <c r="A386">
+        <v>384</v>
+      </c>
+      <c r="B386">
+        <v>-0.0003964956267736852</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387">
+        <v>385</v>
+      </c>
+      <c r="B387">
+        <v>0.001451185555197299</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2">
+      <c r="A388">
+        <v>386</v>
+      </c>
+      <c r="B388">
+        <v>0.002205922501161695</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2">
+      <c r="A389">
+        <v>387</v>
+      </c>
+      <c r="B389">
+        <v>0.001358060748316348</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2">
+      <c r="A390">
+        <v>388</v>
+      </c>
+      <c r="B390">
+        <v>0.001088593387976289</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2">
+      <c r="A391">
+        <v>389</v>
+      </c>
+      <c r="B391">
+        <v>-0.0007317588897421956</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2">
+      <c r="A392">
+        <v>390</v>
+      </c>
+      <c r="B392">
+        <v>0.0008798607159405947</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2">
+      <c r="A393">
+        <v>391</v>
+      </c>
+      <c r="B393">
+        <v>0.0007095830515027046</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2">
+      <c r="A394">
+        <v>392</v>
+      </c>
+      <c r="B394">
+        <v>0.001262038014829159</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2">
+      <c r="A395">
+        <v>393</v>
+      </c>
+      <c r="B395">
+        <v>0.0006632239674217999</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2">
+      <c r="A396">
+        <v>394</v>
+      </c>
+      <c r="B396">
+        <v>-0.00030021887505427</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2">
+      <c r="A397">
+        <v>395</v>
+      </c>
+      <c r="B397">
+        <v>0.0001065561809809878</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2">
+      <c r="A398">
+        <v>396</v>
+      </c>
+      <c r="B398">
+        <v>0.0002665011852513999</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2">
+      <c r="A399">
+        <v>397</v>
+      </c>
+      <c r="B399">
+        <v>0.0004076898039784282</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2">
+      <c r="A400">
+        <v>398</v>
+      </c>
+      <c r="B400">
+        <v>-0.0001109282384277321</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2">
+      <c r="A401">
+        <v>399</v>
+      </c>
+      <c r="B401">
+        <v>-8.90400042408146E-05</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2">
+      <c r="A402">
+        <v>400</v>
+      </c>
+      <c r="B402">
+        <v>0.0003483315813355148</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2">
+      <c r="A403">
+        <v>401</v>
+      </c>
+      <c r="B403">
+        <v>-0.0004312538076192141</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2">
+      <c r="A404">
+        <v>402</v>
+      </c>
+      <c r="B404">
+        <v>0.0005723208887502551</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2">
+      <c r="A405">
+        <v>403</v>
+      </c>
+      <c r="B405">
+        <v>0.000502700568176806</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2">
+      <c r="A406">
+        <v>404</v>
+      </c>
+      <c r="B406">
+        <v>-0.0001106476775021292</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2">
+      <c r="A407">
+        <v>405</v>
+      </c>
+      <c r="B407">
+        <v>0.002257152460515499</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2">
+      <c r="A408">
+        <v>406</v>
+      </c>
+      <c r="B408">
+        <v>-0.0006977645098231733</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2">
+      <c r="A409">
+        <v>407</v>
+      </c>
+      <c r="B409">
+        <v>-0.0001905648387037218</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2">
+      <c r="A410">
+        <v>408</v>
+      </c>
+      <c r="B410">
+        <v>0.000368068169336766</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2">
+      <c r="A411">
+        <v>409</v>
+      </c>
+      <c r="B411">
+        <v>-5.058568603999447E-06</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2">
+      <c r="A412">
+        <v>410</v>
+      </c>
+      <c r="B412">
+        <v>-0.000963287428021431</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2">
+      <c r="A413">
+        <v>411</v>
+      </c>
+      <c r="B413">
+        <v>-2.516540189390071E-05</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2">
+      <c r="A414">
+        <v>412</v>
+      </c>
+      <c r="B414">
+        <v>0.0005482053966261446</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2">
+      <c r="A415">
+        <v>413</v>
+      </c>
+      <c r="B415">
+        <v>0.001561447512358427</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2">
+      <c r="A416">
+        <v>414</v>
+      </c>
+      <c r="B416">
+        <v>4.239662666805089E-05</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2">
+      <c r="A417">
+        <v>415</v>
+      </c>
+      <c r="B417">
+        <v>0.0004356439749244601</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2">
+      <c r="A418">
+        <v>416</v>
+      </c>
+      <c r="B418">
+        <v>-0.0002355135075049475</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2">
+      <c r="A419">
+        <v>417</v>
+      </c>
+      <c r="B419">
+        <v>0.0008025554125197232</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2">
+      <c r="A420">
+        <v>418</v>
+      </c>
+      <c r="B420">
+        <v>0.0005792674492113292</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2">
+      <c r="A421">
+        <v>419</v>
+      </c>
+      <c r="B421">
+        <v>0.0005711244302801788</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2">
+      <c r="A422">
+        <v>420</v>
+      </c>
+      <c r="B422">
+        <v>0.00160627078730613</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2">
+      <c r="A423">
+        <v>421</v>
+      </c>
+      <c r="B423">
+        <v>-0.0003315996436867863</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2">
+      <c r="A424">
+        <v>422</v>
+      </c>
+      <c r="B424">
+        <v>0.0009942763717845082</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2">
+      <c r="A425">
+        <v>423</v>
+      </c>
+      <c r="B425">
+        <v>0.0003274241462349892</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2">
+      <c r="A426">
+        <v>424</v>
+      </c>
+      <c r="B426">
+        <v>0.00160323129966855</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2">
+      <c r="A427">
+        <v>425</v>
+      </c>
+      <c r="B427">
+        <v>-0.0005408943397924304</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2">
+      <c r="A428">
+        <v>426</v>
+      </c>
+      <c r="B428">
+        <v>0.00126404722686857</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2">
+      <c r="A429">
+        <v>427</v>
+      </c>
+      <c r="B429">
+        <v>-3.343157004565001E-05</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2">
+      <c r="A430">
+        <v>428</v>
+      </c>
+      <c r="B430">
+        <v>0.001066920114681125</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2">
+      <c r="A431">
+        <v>429</v>
+      </c>
+      <c r="B431">
+        <v>-1.021430398395751E-05</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2">
+      <c r="A432">
+        <v>430</v>
+      </c>
+      <c r="B432">
+        <v>0.0004066028050146997</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2">
+      <c r="A433">
+        <v>431</v>
+      </c>
+      <c r="B433">
+        <v>0.0002709209220483899</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2">
+      <c r="A434">
+        <v>432</v>
+      </c>
+      <c r="B434">
+        <v>0.001384164905175567</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2">
+      <c r="A435">
+        <v>433</v>
+      </c>
+      <c r="B435">
+        <v>0.0003352619532961398</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2">
+      <c r="A436">
+        <v>434</v>
+      </c>
+      <c r="B436">
+        <v>0.0004538223438430578</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2">
+      <c r="A437">
+        <v>435</v>
+      </c>
+      <c r="B437">
+        <v>0.000846442359033972</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2">
+      <c r="A438">
+        <v>436</v>
+      </c>
+      <c r="B438">
+        <v>0.002815281972289085</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2">
+      <c r="A439">
+        <v>437</v>
+      </c>
+      <c r="B439">
+        <v>0.0001811916736187413</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2">
+      <c r="A440">
+        <v>438</v>
+      </c>
+      <c r="B440">
+        <v>0.000164932876941748</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2">
+      <c r="A441">
+        <v>439</v>
+      </c>
+      <c r="B441">
+        <v>0.003152949502691627</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2">
+      <c r="A442">
+        <v>440</v>
+      </c>
+      <c r="B442">
+        <v>2.883791603380814E-05</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2">
+      <c r="A443">
+        <v>441</v>
+      </c>
+      <c r="B443">
+        <v>0.0002876247745007277</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2">
+      <c r="A444">
+        <v>442</v>
+      </c>
+      <c r="B444">
+        <v>0.0002181934105465189</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2">
+      <c r="A445">
+        <v>443</v>
+      </c>
+      <c r="B445">
+        <v>0.000690366723574698</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2">
+      <c r="A446">
+        <v>444</v>
+      </c>
+      <c r="B446">
+        <v>-0.000184737888048403</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2">
+      <c r="A447">
+        <v>445</v>
+      </c>
+      <c r="B447">
+        <v>0.0003207950212527066</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2">
+      <c r="A448">
+        <v>446</v>
+      </c>
+      <c r="B448">
+        <v>0.0002131512155756354</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2">
+      <c r="A449">
+        <v>447</v>
+      </c>
+      <c r="B449">
+        <v>0.0001444494409952313</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2">
+      <c r="A450">
+        <v>448</v>
+      </c>
+      <c r="B450">
+        <v>5.414038969320245E-05</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2">
+      <c r="A451">
+        <v>449</v>
+      </c>
+      <c r="B451">
+        <v>0.0003790508490055799</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2">
+      <c r="A452">
+        <v>450</v>
+      </c>
+      <c r="B452">
+        <v>-0.0001224743027705699</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2">
+      <c r="A453">
+        <v>451</v>
+      </c>
+      <c r="B453">
+        <v>0.0004082956584170461</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2">
+      <c r="A454">
+        <v>452</v>
+      </c>
+      <c r="B454">
+        <v>-0.001106758951209486</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2">
+      <c r="A455">
+        <v>453</v>
+      </c>
+      <c r="B455">
+        <v>-0.001050847466103733</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2">
+      <c r="A456">
+        <v>454</v>
+      </c>
+      <c r="B456">
+        <v>0.001320077804848552</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2">
+      <c r="A457">
+        <v>455</v>
+      </c>
+      <c r="B457">
+        <v>0.0002108423068420961</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2">
+      <c r="A458">
+        <v>456</v>
+      </c>
+      <c r="B458">
+        <v>0.0006718020304106176</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2">
+      <c r="A459">
+        <v>457</v>
+      </c>
+      <c r="B459">
+        <v>0.0008882351685315371</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2">
+      <c r="A460">
+        <v>458</v>
+      </c>
+      <c r="B460">
+        <v>7.540203660028055E-05</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2">
+      <c r="A461">
+        <v>459</v>
+      </c>
+      <c r="B461">
+        <v>0.00115886190906167</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2">
+      <c r="A462">
+        <v>460</v>
+      </c>
+      <c r="B462">
+        <v>0.0004490138962864876</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2">
+      <c r="A463">
+        <v>461</v>
+      </c>
+      <c r="B463">
+        <v>0.0007078422349877656</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2">
+      <c r="A464">
+        <v>462</v>
+      </c>
+      <c r="B464">
+        <v>0.0002304297522641718</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2">
+      <c r="A465">
+        <v>463</v>
+      </c>
+      <c r="B465">
+        <v>-0.0002247123629786074</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2">
+      <c r="A466">
+        <v>464</v>
+      </c>
+      <c r="B466">
+        <v>0.001244946965016425</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2">
+      <c r="A467">
+        <v>465</v>
+      </c>
+      <c r="B467">
+        <v>0.0002745235105976462</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2">
+      <c r="A468">
+        <v>466</v>
+      </c>
+      <c r="B468">
+        <v>0.001223566941916943</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2">
+      <c r="A469">
+        <v>467</v>
+      </c>
+      <c r="B469">
+        <v>0.0005493448697961867</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2">
+      <c r="A470">
+        <v>468</v>
+      </c>
+      <c r="B470">
+        <v>0.001331262523308396</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2">
+      <c r="A471">
+        <v>469</v>
+      </c>
+      <c r="B471">
+        <v>0.0003163837536703795</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2">
+      <c r="A472">
+        <v>470</v>
+      </c>
+      <c r="B472">
+        <v>2.837537431332748E-05</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2">
+      <c r="A473">
+        <v>471</v>
+      </c>
+      <c r="B473">
+        <v>2.002361543418374E-05</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2">
+      <c r="A474">
+        <v>472</v>
+      </c>
+      <c r="B474">
+        <v>0.0003516286378726363</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2">
+      <c r="A475">
+        <v>473</v>
+      </c>
+      <c r="B475">
+        <v>0.000325217202771455</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2">
+      <c r="A476">
+        <v>474</v>
+      </c>
+      <c r="B476">
+        <v>0.0002898550592362881</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2">
+      <c r="A477">
+        <v>475</v>
+      </c>
+      <c r="B477">
+        <v>0.0001794546551536769</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2">
+      <c r="A478">
+        <v>476</v>
+      </c>
+      <c r="B478">
+        <v>-0.0003672578022815287</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2">
+      <c r="A479">
+        <v>477</v>
+      </c>
+      <c r="B479">
+        <v>0.0003876884002238512</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2">
+      <c r="A480">
+        <v>478</v>
+      </c>
+      <c r="B480">
+        <v>0.005311010405421257</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2">
+      <c r="A481">
+        <v>479</v>
+      </c>
+      <c r="B481">
+        <v>0.000299832143355161</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2">
+      <c r="A482">
+        <v>480</v>
+      </c>
+      <c r="B482">
+        <v>-0.0002224925119662657</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2">
+      <c r="A483">
+        <v>481</v>
+      </c>
+      <c r="B483">
+        <v>0.0004297432315070182</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2">
+      <c r="A484">
+        <v>482</v>
+      </c>
+      <c r="B484">
+        <v>-0.0004282382724341005</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2">
+      <c r="A485">
+        <v>483</v>
+      </c>
+      <c r="B485">
+        <v>0.0005651565152220428</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2">
+      <c r="A486">
+        <v>484</v>
+      </c>
+      <c r="B486">
+        <v>-0.0003443880705162883</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2">
+      <c r="A487">
+        <v>485</v>
+      </c>
+      <c r="B487">
+        <v>0.0003443320165388286</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2">
+      <c r="A488">
+        <v>486</v>
+      </c>
+      <c r="B488">
+        <v>-0.0001658258406678215</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2">
+      <c r="A489">
+        <v>487</v>
+      </c>
+      <c r="B489">
+        <v>0.00100683409254998</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2">
+      <c r="A490">
+        <v>488</v>
+      </c>
+      <c r="B490">
+        <v>0.0003646803088486195</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2">
+      <c r="A491">
+        <v>489</v>
+      </c>
+      <c r="B491">
+        <v>7.025524973869324E-05</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2">
+      <c r="A492">
+        <v>490</v>
+      </c>
+      <c r="B492">
+        <v>0.0004166249127592891</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2">
+      <c r="A493">
+        <v>491</v>
+      </c>
+      <c r="B493">
+        <v>0.0005587579216808081</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2">
+      <c r="A494">
+        <v>492</v>
+      </c>
+      <c r="B494">
+        <v>0.0001531614107079804</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2">
+      <c r="A495">
+        <v>493</v>
+      </c>
+      <c r="B495">
+        <v>0.0008865357958711684</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2">
+      <c r="A496">
+        <v>494</v>
+      </c>
+      <c r="B496">
+        <v>-0.000155325818923302</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2">
+      <c r="A497">
+        <v>495</v>
+      </c>
+      <c r="B497">
+        <v>0.000731129024643451</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2">
+      <c r="A498">
+        <v>496</v>
+      </c>
+      <c r="B498">
+        <v>0.0001454304583603516</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2">
+      <c r="A499">
+        <v>497</v>
+      </c>
+      <c r="B499">
+        <v>0.0002278393221786246</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2">
+      <c r="A500">
+        <v>498</v>
+      </c>
+      <c r="B500">
+        <v>-2.564241583513649E-07</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2">
+      <c r="A501">
+        <v>499</v>
+      </c>
+      <c r="B501">
+        <v>0.00052304269047454</v>
+      </c>
+    </row>
+    <row r="502" spans="1:2">
+      <c r="A502">
+        <v>500</v>
+      </c>
+      <c r="B502">
+        <v>0.0004260135465301573</v>
+      </c>
+    </row>
+    <row r="503" spans="1:2">
+      <c r="A503">
+        <v>501</v>
+      </c>
+      <c r="B503">
+        <v>0.001022034441120923</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2">
+      <c r="A504">
+        <v>502</v>
+      </c>
+      <c r="B504">
+        <v>0.001438436098396778</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2">
+      <c r="A505">
+        <v>503</v>
+      </c>
+      <c r="B505">
+        <v>-2.990236134792212E-05</v>
+      </c>
+    </row>
+    <row r="506" spans="1:2">
+      <c r="A506">
+        <v>504</v>
+      </c>
+      <c r="B506">
+        <v>-0.000311249663354829</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2">
+      <c r="A507">
+        <v>505</v>
+      </c>
+      <c r="B507">
+        <v>0.001466601388528943</v>
+      </c>
+    </row>
+    <row r="508" spans="1:2">
+      <c r="A508">
+        <v>506</v>
+      </c>
+      <c r="B508">
+        <v>0.0005837144562974572</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2">
+      <c r="A509">
+        <v>507</v>
+      </c>
+      <c r="B509">
+        <v>-0.0001900496863527223</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2">
+      <c r="A510">
+        <v>508</v>
+      </c>
+      <c r="B510">
+        <v>0.0006518221343867481</v>
+      </c>
+    </row>
+    <row r="511" spans="1:2">
+      <c r="A511">
+        <v>509</v>
+      </c>
+      <c r="B511">
+        <v>0.0001056963446899317</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2">
+      <c r="A512">
+        <v>510</v>
+      </c>
+      <c r="B512">
+        <v>0.0004254510276950896</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2">
+      <c r="A513">
+        <v>511</v>
+      </c>
+      <c r="B513">
+        <v>0.0004396226140670478</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2">
+      <c r="A514">
+        <v>512</v>
+      </c>
+      <c r="B514">
+        <v>0.0002309260598849505</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2">
+      <c r="A515">
+        <v>513</v>
+      </c>
+      <c r="B515">
+        <v>-0.0001094826293410733</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2">
+      <c r="A516">
+        <v>514</v>
+      </c>
+      <c r="B516">
+        <v>1.052598418027628E-05</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2">
+      <c r="A517">
+        <v>515</v>
+      </c>
+      <c r="B517">
+        <v>-2.755126115516759E-05</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2">
+      <c r="A518">
+        <v>516</v>
+      </c>
+      <c r="B518">
+        <v>0.001044475473463535</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2">
+      <c r="A519">
+        <v>517</v>
+      </c>
+      <c r="B519">
+        <v>0.000290906842565164</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2">
+      <c r="A520">
+        <v>518</v>
+      </c>
+      <c r="B520">
+        <v>-3.663550523924641E-05</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2">
+      <c r="A521">
+        <v>519</v>
+      </c>
+      <c r="B521">
+        <v>1.586313373991288E-05</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2">
+      <c r="A522">
+        <v>520</v>
+      </c>
+      <c r="B522">
+        <v>0.0003179940686095506</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2">
+      <c r="A523">
+        <v>521</v>
+      </c>
+      <c r="B523">
+        <v>0.0003281142853666097</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2">
+      <c r="A524">
+        <v>522</v>
+      </c>
+      <c r="B524">
+        <v>0.0007008332177065313</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2">
+      <c r="A525">
+        <v>523</v>
+      </c>
+      <c r="B525">
+        <v>0.001559150754474103</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2">
+      <c r="A526">
+        <v>524</v>
+      </c>
+      <c r="B526">
+        <v>1.09989196062088E-05</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2">
+      <c r="A527">
+        <v>525</v>
+      </c>
+      <c r="B527">
+        <v>0.001951839192770422</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2">
+      <c r="A528">
+        <v>526</v>
+      </c>
+      <c r="B528">
+        <v>-2.513463414288708E-06</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2">
+      <c r="A529">
+        <v>527</v>
+      </c>
+      <c r="B529">
+        <v>-0.0002295221202075481</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2">
+      <c r="A530">
+        <v>528</v>
+      </c>
+      <c r="B530">
+        <v>0.0006367375608533621</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2">
+      <c r="A531">
+        <v>529</v>
+      </c>
+      <c r="B531">
+        <v>0.0006089775706641376</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2">
+      <c r="A532">
+        <v>530</v>
+      </c>
+      <c r="B532">
+        <v>0.0004793980915565044</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2">
+      <c r="A533">
+        <v>531</v>
+      </c>
+      <c r="B533">
+        <v>5.176956619834527E-05</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2">
+      <c r="A534">
+        <v>532</v>
+      </c>
+      <c r="B534">
+        <v>0.0007080257637426257</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2">
+      <c r="A535">
+        <v>533</v>
+      </c>
+      <c r="B535">
+        <v>0.0007098009809851646</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2">
+      <c r="A536">
+        <v>534</v>
+      </c>
+      <c r="B536">
+        <v>0.0002016077050939202</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2">
+      <c r="A537">
+        <v>535</v>
+      </c>
+      <c r="B537">
+        <v>0.001441646483726799</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2">
+      <c r="A538">
+        <v>536</v>
+      </c>
+      <c r="B538">
+        <v>4.9530735850567E-06</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2">
+      <c r="A539">
+        <v>537</v>
+      </c>
+      <c r="B539">
+        <v>0.003133047139272094</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2">
+      <c r="A540">
+        <v>538</v>
+      </c>
+      <c r="B540">
+        <v>-0.0004973050090484321</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2">
+      <c r="A541">
+        <v>539</v>
+      </c>
+      <c r="B541">
+        <v>-0.0003910943341907114</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2">
+      <c r="A542">
+        <v>540</v>
+      </c>
+      <c r="B542">
+        <v>0.0003358739777468145</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2">
+      <c r="A543">
+        <v>541</v>
+      </c>
+      <c r="B543">
+        <v>0.0003412828082218766</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2">
+      <c r="A544">
+        <v>542</v>
+      </c>
+      <c r="B544">
+        <v>-0.00016578177746851</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2">
+      <c r="A545">
+        <v>543</v>
+      </c>
+      <c r="B545">
+        <v>0.000139097377541475</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2">
+      <c r="A546">
+        <v>544</v>
+      </c>
+      <c r="B546">
+        <v>0.000599147635512054</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2">
+      <c r="A547">
+        <v>545</v>
+      </c>
+      <c r="B547">
+        <v>0.0001853376452345401</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2">
+      <c r="A548">
+        <v>546</v>
+      </c>
+      <c r="B548">
+        <v>0.0008490947657264769</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2">
+      <c r="A549">
+        <v>547</v>
+      </c>
+      <c r="B549">
+        <v>0.0009362971177324653</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2">
+      <c r="A550">
+        <v>548</v>
+      </c>
+      <c r="B550">
+        <v>-0.0005711003905162215</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2">
+      <c r="A551">
+        <v>549</v>
+      </c>
+      <c r="B551">
+        <v>0.0005517184035852551</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2">
+      <c r="A552">
+        <v>550</v>
+      </c>
+      <c r="B552">
+        <v>0.001668288838118315</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2">
+      <c r="A553">
+        <v>551</v>
+      </c>
+      <c r="B553">
+        <v>0.001123289810493588</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2">
+      <c r="A554">
+        <v>552</v>
+      </c>
+      <c r="B554">
+        <v>0.000165468649356626</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2">
+      <c r="A555">
+        <v>553</v>
+      </c>
+      <c r="B555">
+        <v>0.0002552109945099801</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2">
+      <c r="A556">
+        <v>554</v>
+      </c>
+      <c r="B556">
+        <v>0.0007928797276690602</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2">
+      <c r="A557">
+        <v>555</v>
+      </c>
+      <c r="B557">
+        <v>0.0005951047642156482</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2">
+      <c r="A558">
+        <v>556</v>
+      </c>
+      <c r="B558">
+        <v>-0.0005987677141092718</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2">
+      <c r="A559">
+        <v>557</v>
+      </c>
+      <c r="B559">
+        <v>0.001141049549914896</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2">
+      <c r="A560">
+        <v>558</v>
+      </c>
+      <c r="B560">
+        <v>6.501116331492085E-06</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2">
+      <c r="A561">
+        <v>559</v>
+      </c>
+      <c r="B561">
+        <v>0.001515058218501508</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2">
+      <c r="A562">
+        <v>560</v>
+      </c>
+      <c r="B562">
+        <v>0.0005863471888005733</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2">
+      <c r="A563">
+        <v>561</v>
+      </c>
+      <c r="B563">
+        <v>2.586175287433434E-05</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2">
+      <c r="A564">
+        <v>562</v>
+      </c>
+      <c r="B564">
+        <v>-0.0006206256221048534</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2">
+      <c r="A565">
+        <v>563</v>
+      </c>
+      <c r="B565">
+        <v>-0.004121799487620592</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2">
+      <c r="A566">
+        <v>564</v>
+      </c>
+      <c r="B566">
+        <v>0.001265258179046214</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2">
+      <c r="A567">
+        <v>565</v>
+      </c>
+      <c r="B567">
+        <v>-0.0007979024667292833</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2">
+      <c r="A568">
+        <v>566</v>
+      </c>
+      <c r="B568">
+        <v>0.0002852502511814237</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2">
+      <c r="A569">
+        <v>567</v>
+      </c>
+      <c r="B569">
+        <v>-4.409478060551919E-05</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2">
+      <c r="A570">
+        <v>568</v>
+      </c>
+      <c r="B570">
+        <v>0.001056475099176168</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2">
+      <c r="A571">
+        <v>569</v>
+      </c>
+      <c r="B571">
+        <v>-0.001149395597167313</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2">
+      <c r="A572">
+        <v>570</v>
+      </c>
+      <c r="B572">
+        <v>0.000198533627553843</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2">
+      <c r="A573">
+        <v>571</v>
+      </c>
+      <c r="B573">
+        <v>0.000625506741926074</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2">
+      <c r="A574">
+        <v>572</v>
+      </c>
+      <c r="B574">
+        <v>0.0010583505500108</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2">
+      <c r="A575">
+        <v>573</v>
+      </c>
+      <c r="B575">
+        <v>0.002299959305673838</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2">
+      <c r="A576">
+        <v>574</v>
+      </c>
+      <c r="B576">
+        <v>0.0005433924961835146</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2">
+      <c r="A577">
+        <v>575</v>
+      </c>
+      <c r="B577">
+        <v>-0.000224234230699949</v>
+      </c>
+    </row>
+    <row r="578" spans="1:2">
+      <c r="A578">
+        <v>576</v>
+      </c>
+      <c r="B578">
+        <v>0.004891063086688519</v>
+      </c>
+    </row>
+    <row r="579" spans="1:2">
+      <c r="A579">
+        <v>577</v>
+      </c>
+      <c r="B579">
+        <v>0.000215167659916915</v>
+      </c>
+    </row>
+    <row r="580" spans="1:2">
+      <c r="A580">
+        <v>578</v>
+      </c>
+      <c r="B580">
+        <v>-3.039537477889098E-05</v>
+      </c>
+    </row>
+    <row r="581" spans="1:2">
+      <c r="A581">
+        <v>579</v>
+      </c>
+      <c r="B581">
+        <v>0.0009624092490412295</v>
+      </c>
+    </row>
+    <row r="582" spans="1:2">
+      <c r="A582">
+        <v>580</v>
+      </c>
+      <c r="B582">
+        <v>0.001063101924955845</v>
+      </c>
+    </row>
+    <row r="583" spans="1:2">
+      <c r="A583">
+        <v>581</v>
+      </c>
+      <c r="B583">
+        <v>0.0001229623157996684</v>
+      </c>
+    </row>
+    <row r="584" spans="1:2">
+      <c r="A584">
+        <v>582</v>
+      </c>
+      <c r="B584">
+        <v>0.0003836628748103976</v>
+      </c>
+    </row>
+    <row r="585" spans="1:2">
+      <c r="A585">
+        <v>583</v>
+      </c>
+      <c r="B585">
+        <v>0.0003951679682359099</v>
+      </c>
+    </row>
+    <row r="586" spans="1:2">
+      <c r="A586">
+        <v>584</v>
+      </c>
+      <c r="B586">
+        <v>0.0001572098262840882</v>
+      </c>
+    </row>
+    <row r="587" spans="1:2">
+      <c r="A587">
+        <v>585</v>
+      </c>
+      <c r="B587">
+        <v>-0.0001954003382707015</v>
+      </c>
+    </row>
+    <row r="588" spans="1:2">
+      <c r="A588">
+        <v>586</v>
+      </c>
+      <c r="B588">
+        <v>-0.0009069623774848878</v>
+      </c>
+    </row>
+    <row r="589" spans="1:2">
+      <c r="A589">
+        <v>587</v>
+      </c>
+      <c r="B589">
+        <v>0.0002630347153171897</v>
+      </c>
+    </row>
+    <row r="590" spans="1:2">
+      <c r="A590">
+        <v>588</v>
+      </c>
+      <c r="B590">
+        <v>-0.0001498923229519278</v>
+      </c>
+    </row>
+    <row r="591" spans="1:2">
+      <c r="A591">
+        <v>589</v>
+      </c>
+      <c r="B591">
+        <v>0.001374467276036739</v>
+      </c>
+    </row>
+    <row r="592" spans="1:2">
+      <c r="A592">
+        <v>590</v>
+      </c>
+      <c r="B592">
+        <v>0.0009514536941424012</v>
+      </c>
+    </row>
+    <row r="593" spans="1:2">
+      <c r="A593">
+        <v>591</v>
+      </c>
+      <c r="B593">
+        <v>0.001531980000436306</v>
+      </c>
+    </row>
+    <row r="594" spans="1:2">
+      <c r="A594">
+        <v>592</v>
+      </c>
+      <c r="B594">
+        <v>-0.0002584555768407881</v>
+      </c>
+    </row>
+    <row r="595" spans="1:2">
+      <c r="A595">
+        <v>593</v>
+      </c>
+      <c r="B595">
+        <v>0.0005305001395754516</v>
+      </c>
+    </row>
+    <row r="596" spans="1:2">
+      <c r="A596">
+        <v>594</v>
+      </c>
+      <c r="B596">
+        <v>0.0003292523906566203</v>
+      </c>
+    </row>
+    <row r="597" spans="1:2">
+      <c r="A597">
+        <v>595</v>
+      </c>
+      <c r="B597">
+        <v>0.0009723735856823623</v>
+      </c>
+    </row>
+    <row r="598" spans="1:2">
+      <c r="A598">
+        <v>596</v>
+      </c>
+      <c r="B598">
+        <v>9.556422446621582E-05</v>
+      </c>
+    </row>
+    <row r="599" spans="1:2">
+      <c r="A599">
+        <v>597</v>
+      </c>
+      <c r="B599">
+        <v>0.0001047611076501198</v>
+      </c>
+    </row>
+    <row r="600" spans="1:2">
+      <c r="A600">
+        <v>598</v>
+      </c>
+      <c r="B600">
+        <v>-0.0006569568649865687</v>
+      </c>
+    </row>
+    <row r="601" spans="1:2">
+      <c r="A601">
+        <v>599</v>
+      </c>
+      <c r="B601">
+        <v>0.0009854567470028996</v>
+      </c>
+    </row>
+    <row r="602" spans="1:2">
+      <c r="A602">
+        <v>600</v>
+      </c>
+      <c r="B602">
+        <v>0.003387783421203494</v>
+      </c>
+    </row>
+    <row r="603" spans="1:2">
+      <c r="A603">
+        <v>601</v>
+      </c>
+      <c r="B603">
+        <v>0.001729166135191917</v>
+      </c>
+    </row>
+    <row r="604" spans="1:2">
+      <c r="A604">
+        <v>602</v>
+      </c>
+      <c r="B604">
+        <v>0.008370477706193924</v>
+      </c>
+    </row>
+    <row r="605" spans="1:2">
+      <c r="A605">
+        <v>603</v>
+      </c>
+      <c r="B605">
+        <v>0.001739124883897603</v>
+      </c>
+    </row>
+    <row r="606" spans="1:2">
+      <c r="A606">
+        <v>604</v>
+      </c>
+      <c r="B606">
+        <v>-0.0001266510662389919</v>
+      </c>
+    </row>
+    <row r="607" spans="1:2">
+      <c r="A607">
+        <v>605</v>
+      </c>
+      <c r="B607">
+        <v>0.001061510178260505</v>
+      </c>
+    </row>
+    <row r="608" spans="1:2">
+      <c r="A608">
+        <v>606</v>
+      </c>
+      <c r="B608">
+        <v>0.00200430303812027</v>
+      </c>
+    </row>
+    <row r="609" spans="1:2">
+      <c r="A609">
+        <v>607</v>
+      </c>
+      <c r="B609">
+        <v>0.0002899889077525586</v>
+      </c>
+    </row>
+    <row r="610" spans="1:2">
+      <c r="A610">
+        <v>608</v>
+      </c>
+      <c r="B610">
+        <v>0.0002087010216200724</v>
+      </c>
+    </row>
+    <row r="611" spans="1:2">
+      <c r="A611">
+        <v>609</v>
+      </c>
+      <c r="B611">
+        <v>0.0004217421810608357</v>
+      </c>
+    </row>
+    <row r="612" spans="1:2">
+      <c r="A612">
+        <v>610</v>
+      </c>
+      <c r="B612">
+        <v>0.0001100319132092409</v>
+      </c>
+    </row>
+    <row r="613" spans="1:2">
+      <c r="A613">
+        <v>611</v>
+      </c>
+      <c r="B613">
+        <v>0.0007496676407754421</v>
+      </c>
+    </row>
+    <row r="614" spans="1:2">
+      <c r="A614">
+        <v>612</v>
+      </c>
+      <c r="B614">
+        <v>3.096507862210274E-05</v>
+      </c>
+    </row>
+    <row r="615" spans="1:2">
+      <c r="A615">
+        <v>613</v>
+      </c>
+      <c r="B615">
+        <v>0.000508316676132381</v>
+      </c>
+    </row>
+    <row r="616" spans="1:2">
+      <c r="A616">
+        <v>614</v>
+      </c>
+      <c r="B616">
+        <v>-0.0002024406130658463</v>
+      </c>
+    </row>
+    <row r="617" spans="1:2">
+      <c r="A617">
+        <v>615</v>
+      </c>
+      <c r="B617">
+        <v>-0.002061466919258237</v>
+      </c>
+    </row>
+    <row r="618" spans="1:2">
+      <c r="A618">
+        <v>616</v>
+      </c>
+      <c r="B618">
+        <v>0.0008896327926777303</v>
+      </c>
+    </row>
+    <row r="619" spans="1:2">
+      <c r="A619">
+        <v>617</v>
+      </c>
+      <c r="B619">
+        <v>-0.0006767074228264391</v>
+      </c>
+    </row>
+    <row r="620" spans="1:2">
+      <c r="A620">
+        <v>618</v>
+      </c>
+      <c r="B620">
+        <v>0.0001210325644933619</v>
+      </c>
+    </row>
+    <row r="621" spans="1:2">
+      <c r="A621">
+        <v>619</v>
+      </c>
+      <c r="B621">
+        <v>0.001967599848285317</v>
+      </c>
+    </row>
+    <row r="622" spans="1:2">
+      <c r="A622">
+        <v>620</v>
+      </c>
+      <c r="B622">
+        <v>0.0005185584886930883</v>
+      </c>
+    </row>
+    <row r="623" spans="1:2">
+      <c r="A623">
+        <v>621</v>
+      </c>
+      <c r="B623">
+        <v>0.0008732787100598216</v>
+      </c>
+    </row>
+    <row r="624" spans="1:2">
+      <c r="A624">
+        <v>622</v>
+      </c>
+      <c r="B624">
+        <v>-0.0005406287382356822</v>
+      </c>
+    </row>
+    <row r="625" spans="1:2">
+      <c r="A625">
+        <v>623</v>
+      </c>
+      <c r="B625">
+        <v>3.532984919729643E-05</v>
+      </c>
+    </row>
+    <row r="626" spans="1:2">
+      <c r="A626">
+        <v>624</v>
+      </c>
+      <c r="B626">
+        <v>-0.0006570788682438433</v>
+      </c>
+    </row>
+    <row r="627" spans="1:2">
+      <c r="A627">
+        <v>625</v>
+      </c>
+      <c r="B627">
+        <v>0.000381855177693069</v>
+      </c>
+    </row>
+    <row r="628" spans="1:2">
+      <c r="A628">
+        <v>626</v>
+      </c>
+      <c r="B628">
+        <v>0.0004712354857474566</v>
+      </c>
+    </row>
+    <row r="629" spans="1:2">
+      <c r="A629">
+        <v>627</v>
+      </c>
+      <c r="B629">
+        <v>-4.98338631587103E-05</v>
+      </c>
+    </row>
+    <row r="630" spans="1:2">
+      <c r="A630">
+        <v>628</v>
+      </c>
+      <c r="B630">
+        <v>0.001053149811923504</v>
+      </c>
+    </row>
+    <row r="631" spans="1:2">
+      <c r="A631">
+        <v>629</v>
+      </c>
+      <c r="B631">
+        <v>0.0003565909282770008</v>
+      </c>
+    </row>
+    <row r="632" spans="1:2">
+      <c r="A632">
+        <v>630</v>
+      </c>
+      <c r="B632">
+        <v>0.001206800807267427</v>
+      </c>
+    </row>
+    <row r="633" spans="1:2">
+      <c r="A633">
+        <v>631</v>
+      </c>
+      <c r="B633">
+        <v>-0.0001158760860562325</v>
+      </c>
+    </row>
+    <row r="634" spans="1:2">
+      <c r="A634">
+        <v>632</v>
+      </c>
+      <c r="B634">
+        <v>0.0005951217608526349</v>
+      </c>
+    </row>
+    <row r="635" spans="1:2">
+      <c r="A635">
+        <v>633</v>
+      </c>
+      <c r="B635">
+        <v>0.001080886810086668</v>
+      </c>
+    </row>
+    <row r="636" spans="1:2">
+      <c r="A636">
+        <v>634</v>
+      </c>
+      <c r="B636">
+        <v>-6.939547893125564E-05</v>
+      </c>
+    </row>
+    <row r="637" spans="1:2">
+      <c r="A637">
+        <v>635</v>
+      </c>
+      <c r="B637">
+        <v>0.0005906514707021415</v>
+      </c>
+    </row>
+    <row r="638" spans="1:2">
+      <c r="A638">
+        <v>636</v>
+      </c>
+      <c r="B638">
+        <v>0.0005166155751794577</v>
+      </c>
+    </row>
+    <row r="639" spans="1:2">
+      <c r="A639">
+        <v>637</v>
+      </c>
+      <c r="B639">
+        <v>0.0001398762105964124</v>
+      </c>
+    </row>
+    <row r="640" spans="1:2">
+      <c r="A640">
+        <v>638</v>
+      </c>
+      <c r="B640">
+        <v>0.001359080662950873</v>
+      </c>
+    </row>
+    <row r="641" spans="1:2">
+      <c r="A641">
+        <v>639</v>
+      </c>
+      <c r="B641">
+        <v>-0.0001260178396478295</v>
+      </c>
+    </row>
+    <row r="642" spans="1:2">
+      <c r="A642">
+        <v>640</v>
+      </c>
+      <c r="B642">
+        <v>0.0001108718424802646</v>
+      </c>
+    </row>
+    <row r="643" spans="1:2">
+      <c r="A643">
+        <v>641</v>
+      </c>
+      <c r="B643">
+        <v>0.002704556565731764</v>
+      </c>
+    </row>
+    <row r="644" spans="1:2">
+      <c r="A644">
+        <v>642</v>
+      </c>
+      <c r="B644">
+        <v>0.0005127679905854166</v>
+      </c>
+    </row>
+    <row r="645" spans="1:2">
+      <c r="A645">
+        <v>643</v>
+      </c>
+      <c r="B645">
+        <v>0.001294036861509085</v>
+      </c>
+    </row>
+    <row r="646" spans="1:2">
+      <c r="A646">
+        <v>644</v>
+      </c>
+      <c r="B646">
+        <v>0.0006963312043808401</v>
+      </c>
+    </row>
+    <row r="647" spans="1:2">
+      <c r="A647">
+        <v>645</v>
+      </c>
+      <c r="B647">
+        <v>-0.0001189591857837513</v>
+      </c>
+    </row>
+    <row r="648" spans="1:2">
+      <c r="A648">
+        <v>646</v>
+      </c>
+      <c r="B648">
+        <v>-0.002091542119160295</v>
+      </c>
+    </row>
+    <row r="649" spans="1:2">
+      <c r="A649">
+        <v>647</v>
+      </c>
+      <c r="B649">
+        <v>0.0009766935836523771</v>
+      </c>
+    </row>
+    <row r="650" spans="1:2">
+      <c r="A650">
+        <v>648</v>
+      </c>
+      <c r="B650">
+        <v>0.001327636069618165</v>
+      </c>
+    </row>
+    <row r="651" spans="1:2">
+      <c r="A651">
+        <v>649</v>
+      </c>
+      <c r="B651">
+        <v>0.000168589991517365</v>
+      </c>
+    </row>
+    <row r="652" spans="1:2">
+      <c r="A652">
+        <v>650</v>
+      </c>
+      <c r="B652">
+        <v>0.001166186295449734</v>
+      </c>
+    </row>
+    <row r="653" spans="1:2">
+      <c r="A653">
+        <v>651</v>
+      </c>
+      <c r="B653">
+        <v>0.0005586182232946157</v>
+      </c>
+    </row>
+    <row r="654" spans="1:2">
+      <c r="A654">
+        <v>652</v>
+      </c>
+      <c r="B654">
+        <v>-0.003384284675121307</v>
+      </c>
+    </row>
+    <row r="655" spans="1:2">
+      <c r="A655">
+        <v>653</v>
+      </c>
+      <c r="B655">
+        <v>0.000841086613945663</v>
+      </c>
+    </row>
+    <row r="656" spans="1:2">
+      <c r="A656">
+        <v>654</v>
+      </c>
+      <c r="B656">
+        <v>-0.001540795783512294</v>
+      </c>
+    </row>
+    <row r="657" spans="1:2">
+      <c r="A657">
+        <v>655</v>
+      </c>
+      <c r="B657">
+        <v>0.0003089387028012425</v>
+      </c>
+    </row>
+    <row r="658" spans="1:2">
+      <c r="A658">
+        <v>656</v>
+      </c>
+      <c r="B658">
+        <v>0.0003941436007153243</v>
+      </c>
+    </row>
+    <row r="659" spans="1:2">
+      <c r="A659">
+        <v>657</v>
+      </c>
+      <c r="B659">
+        <v>-3.231574009987526E-05</v>
+      </c>
+    </row>
+    <row r="660" spans="1:2">
+      <c r="A660">
+        <v>658</v>
+      </c>
+      <c r="B660">
+        <v>0.00045226194197312</v>
+      </c>
+    </row>
+    <row r="661" spans="1:2">
+      <c r="A661">
+        <v>659</v>
+      </c>
+      <c r="B661">
+        <v>0.003388808807358146</v>
+      </c>
+    </row>
+    <row r="662" spans="1:2">
+      <c r="A662">
+        <v>660</v>
+      </c>
+      <c r="B662">
+        <v>0.001078392728231847</v>
+      </c>
+    </row>
+    <row r="663" spans="1:2">
+      <c r="A663">
+        <v>661</v>
+      </c>
+      <c r="B663">
+        <v>-0.0002298636682098731</v>
+      </c>
+    </row>
+    <row r="664" spans="1:2">
+      <c r="A664">
+        <v>662</v>
+      </c>
+      <c r="B664">
+        <v>0.0008060921099968255</v>
+      </c>
+    </row>
+    <row r="665" spans="1:2">
+      <c r="A665">
+        <v>663</v>
+      </c>
+      <c r="B665">
+        <v>0.002098212251439691</v>
+      </c>
+    </row>
+    <row r="666" spans="1:2">
+      <c r="A666">
+        <v>664</v>
+      </c>
+      <c r="B666">
+        <v>0.001432505901902914</v>
+      </c>
+    </row>
+    <row r="667" spans="1:2">
+      <c r="A667">
+        <v>665</v>
+      </c>
+      <c r="B667">
+        <v>-0.0009890981018543243</v>
+      </c>
+    </row>
+    <row r="668" spans="1:2">
+      <c r="A668">
+        <v>666</v>
+      </c>
+      <c r="B668">
+        <v>0.00266208266839385</v>
+      </c>
+    </row>
+    <row r="669" spans="1:2">
+      <c r="A669">
+        <v>667</v>
+      </c>
+      <c r="B669">
+        <v>-0.004857038147747517</v>
+      </c>
+    </row>
+    <row r="670" spans="1:2">
+      <c r="A670">
+        <v>668</v>
+      </c>
+      <c r="B670">
+        <v>0.0009608333930373192</v>
+      </c>
+    </row>
+    <row r="671" spans="1:2">
+      <c r="A671">
+        <v>669</v>
+      </c>
+      <c r="B671">
+        <v>0.0004144709964748472</v>
+      </c>
+    </row>
+    <row r="672" spans="1:2">
+      <c r="A672">
+        <v>670</v>
+      </c>
+      <c r="B672">
+        <v>-1.054960011970252E-05</v>
+      </c>
+    </row>
+    <row r="673" spans="1:2">
+      <c r="A673">
+        <v>671</v>
+      </c>
+      <c r="B673">
+        <v>-0.0003523060586303473</v>
+      </c>
+    </row>
+    <row r="674" spans="1:2">
+      <c r="A674">
+        <v>672</v>
+      </c>
+      <c r="B674">
+        <v>0.0003005127364303917</v>
+      </c>
+    </row>
+    <row r="675" spans="1:2">
+      <c r="A675">
+        <v>673</v>
+      </c>
+      <c r="B675">
+        <v>0.0001886134123196825</v>
+      </c>
+    </row>
+    <row r="676" spans="1:2">
+      <c r="A676">
+        <v>674</v>
+      </c>
+      <c r="B676">
+        <v>0.0004014289006590843</v>
+      </c>
+    </row>
+    <row r="677" spans="1:2">
+      <c r="A677">
+        <v>675</v>
+      </c>
+      <c r="B677">
+        <v>0.0007654228247702122</v>
+      </c>
+    </row>
+    <row r="678" spans="1:2">
+      <c r="A678">
+        <v>676</v>
+      </c>
+      <c r="B678">
+        <v>0.0007525793625973165</v>
+      </c>
+    </row>
+    <row r="679" spans="1:2">
+      <c r="A679">
+        <v>677</v>
+      </c>
+      <c r="B679">
+        <v>0.0006466691847890615</v>
+      </c>
+    </row>
+    <row r="680" spans="1:2">
+      <c r="A680">
+        <v>678</v>
+      </c>
+      <c r="B680">
+        <v>-0.0002608591748867184</v>
+      </c>
+    </row>
+    <row r="681" spans="1:2">
+      <c r="A681">
+        <v>679</v>
+      </c>
+      <c r="B681">
+        <v>-0.0001189552785945125</v>
+      </c>
+    </row>
+    <row r="682" spans="1:2">
+      <c r="A682">
+        <v>680</v>
+      </c>
+      <c r="B682">
+        <v>0.006185547448694706</v>
+      </c>
+    </row>
+    <row r="683" spans="1:2">
+      <c r="A683">
+        <v>681</v>
+      </c>
+      <c r="B683">
+        <v>-0.0005180874723009765</v>
+      </c>
+    </row>
+    <row r="684" spans="1:2">
+      <c r="A684">
+        <v>682</v>
+      </c>
+      <c r="B684">
+        <v>-0.001284626894630492</v>
+      </c>
+    </row>
+    <row r="685" spans="1:2">
+      <c r="A685">
+        <v>683</v>
+      </c>
+      <c r="B685">
+        <v>-0.0001524773251730949</v>
+      </c>
+    </row>
+    <row r="686" spans="1:2">
+      <c r="A686">
+        <v>684</v>
+      </c>
+      <c r="B686">
+        <v>0.0006212254520505667</v>
+      </c>
+    </row>
+    <row r="687" spans="1:2">
+      <c r="A687">
+        <v>685</v>
+      </c>
+      <c r="B687">
+        <v>0.000631637463811785</v>
+      </c>
+    </row>
+    <row r="688" spans="1:2">
+      <c r="A688">
+        <v>686</v>
+      </c>
+      <c r="B688">
+        <v>-0.0002248133241664618</v>
+      </c>
+    </row>
+    <row r="689" spans="1:2">
+      <c r="A689">
+        <v>687</v>
+      </c>
+      <c r="B689">
+        <v>0.0005509207840077579</v>
+      </c>
+    </row>
+    <row r="690" spans="1:2">
+      <c r="A690">
+        <v>688</v>
+      </c>
+      <c r="B690">
+        <v>-0.0005434595514088869</v>
+      </c>
+    </row>
+    <row r="691" spans="1:2">
+      <c r="A691">
+        <v>689</v>
+      </c>
+      <c r="B691">
+        <v>0.001576025271788239</v>
+      </c>
+    </row>
+    <row r="692" spans="1:2">
+      <c r="A692">
+        <v>690</v>
+      </c>
+      <c r="B692">
+        <v>-0.0002035790676018223</v>
+      </c>
+    </row>
+    <row r="693" spans="1:2">
+      <c r="A693">
+        <v>691</v>
+      </c>
+      <c r="B693">
+        <v>-0.0004085606196895242</v>
+      </c>
+    </row>
+    <row r="694" spans="1:2">
+      <c r="A694">
+        <v>692</v>
+      </c>
+      <c r="B694">
+        <v>0.0004592238983605057</v>
+      </c>
+    </row>
+    <row r="695" spans="1:2">
+      <c r="A695">
+        <v>693</v>
+      </c>
+      <c r="B695">
+        <v>0.0007757052662782371</v>
+      </c>
+    </row>
+    <row r="696" spans="1:2">
+      <c r="A696">
+        <v>694</v>
+      </c>
+      <c r="B696">
+        <v>0.0003986730298493057</v>
+      </c>
+    </row>
+    <row r="697" spans="1:2">
+      <c r="A697">
+        <v>695</v>
+      </c>
+      <c r="B697">
+        <v>8.428803994320333E-06</v>
+      </c>
+    </row>
+    <row r="698" spans="1:2">
+      <c r="A698">
+        <v>696</v>
+      </c>
+      <c r="B698">
+        <v>0.0007956991903483868</v>
+      </c>
+    </row>
+    <row r="699" spans="1:2">
+      <c r="A699">
+        <v>697</v>
+      </c>
+      <c r="B699">
+        <v>0.0001199191028717905</v>
+      </c>
+    </row>
+    <row r="700" spans="1:2">
+      <c r="A700">
+        <v>698</v>
+      </c>
+      <c r="B700">
+        <v>-5.642487667500973E-05</v>
+      </c>
+    </row>
+    <row r="701" spans="1:2">
+      <c r="A701">
+        <v>699</v>
+      </c>
+      <c r="B701">
+        <v>-6.049560033716261E-05</v>
+      </c>
+    </row>
+    <row r="702" spans="1:2">
+      <c r="A702">
+        <v>700</v>
+      </c>
+      <c r="B702">
+        <v>-0.0001660253765294328</v>
+      </c>
+    </row>
+    <row r="703" spans="1:2">
+      <c r="A703">
+        <v>701</v>
+      </c>
+      <c r="B703">
+        <v>0.001662898808717728</v>
+      </c>
+    </row>
+    <row r="704" spans="1:2">
+      <c r="A704">
+        <v>702</v>
+      </c>
+      <c r="B704">
+        <v>0.0005773481680080295</v>
+      </c>
+    </row>
+    <row r="705" spans="1:2">
+      <c r="A705">
+        <v>703</v>
+      </c>
+      <c r="B705">
+        <v>0.0001049453348969109</v>
+      </c>
+    </row>
+    <row r="706" spans="1:2">
+      <c r="A706">
+        <v>704</v>
+      </c>
+      <c r="B706">
+        <v>0.000636893673799932</v>
+      </c>
+    </row>
+    <row r="707" spans="1:2">
+      <c r="A707">
+        <v>705</v>
+      </c>
+      <c r="B707">
+        <v>6.013576421537437E-05</v>
+      </c>
+    </row>
+    <row r="708" spans="1:2">
+      <c r="A708">
+        <v>706</v>
+      </c>
+      <c r="B708">
+        <v>0.00570909446105361</v>
+      </c>
+    </row>
+    <row r="709" spans="1:2">
+      <c r="A709">
+        <v>707</v>
+      </c>
+      <c r="B709">
+        <v>-0.0009203585796058178</v>
+      </c>
+    </row>
+    <row r="710" spans="1:2">
+      <c r="A710">
+        <v>708</v>
+      </c>
+      <c r="B710">
+        <v>0.0007319580763578415</v>
+      </c>
+    </row>
+    <row r="711" spans="1:2">
+      <c r="A711">
+        <v>709</v>
+      </c>
+      <c r="B711">
+        <v>0.0002337370387976989</v>
+      </c>
+    </row>
+    <row r="712" spans="1:2">
+      <c r="A712">
+        <v>710</v>
+      </c>
+      <c r="B712">
+        <v>-0.0004736709815915674</v>
+      </c>
+    </row>
+    <row r="713" spans="1:2">
+      <c r="A713">
+        <v>711</v>
+      </c>
+      <c r="B713">
+        <v>0.0006141088670119643</v>
+      </c>
+    </row>
+    <row r="714" spans="1:2">
+      <c r="A714">
+        <v>712</v>
+      </c>
+      <c r="B714">
+        <v>6.284429400693625E-05</v>
+      </c>
+    </row>
+    <row r="715" spans="1:2">
+      <c r="A715">
+        <v>713</v>
+      </c>
+      <c r="B715">
+        <v>0.0002744891389738768</v>
+      </c>
+    </row>
+    <row r="716" spans="1:2">
+      <c r="A716">
+        <v>714</v>
+      </c>
+      <c r="B716">
+        <v>2.87869784187933E-06</v>
+      </c>
+    </row>
+    <row r="717" spans="1:2">
+      <c r="A717">
+        <v>715</v>
+      </c>
+      <c r="B717">
+        <v>0.001450788229703903</v>
+      </c>
+    </row>
+    <row r="718" spans="1:2">
+      <c r="A718">
+        <v>716</v>
+      </c>
+      <c r="B718">
+        <v>0.0001737859565764666</v>
+      </c>
+    </row>
+    <row r="719" spans="1:2">
+      <c r="A719">
+        <v>717</v>
+      </c>
+      <c r="B719">
+        <v>0.0003312000189907849</v>
+      </c>
+    </row>
+    <row r="720" spans="1:2">
+      <c r="A720">
+        <v>718</v>
+      </c>
+      <c r="B720">
+        <v>0.0009865773608908057</v>
+      </c>
+    </row>
+    <row r="721" spans="1:2">
+      <c r="A721">
+        <v>719</v>
+      </c>
+      <c r="B721">
+        <v>-0.0007616421207785606</v>
+      </c>
+    </row>
+    <row r="722" spans="1:2">
+      <c r="A722">
+        <v>720</v>
+      </c>
+      <c r="B722">
+        <v>0.0002757035836111754</v>
+      </c>
+    </row>
+    <row r="723" spans="1:2">
+      <c r="A723">
+        <v>721</v>
+      </c>
+      <c r="B723">
+        <v>-1.57248941832222E-05</v>
+      </c>
+    </row>
+    <row r="724" spans="1:2">
+      <c r="A724">
+        <v>722</v>
+      </c>
+      <c r="B724">
+        <v>0.0003260693047195673</v>
+      </c>
+    </row>
+    <row r="725" spans="1:2">
+      <c r="A725">
+        <v>723</v>
+      </c>
+      <c r="B725">
+        <v>0.0004787824873346835</v>
+      </c>
+    </row>
+    <row r="726" spans="1:2">
+      <c r="A726">
+        <v>724</v>
+      </c>
+      <c r="B726">
+        <v>-0.0004321441520005465</v>
+      </c>
+    </row>
+    <row r="727" spans="1:2">
+      <c r="A727">
+        <v>725</v>
+      </c>
+      <c r="B727">
+        <v>0.0007157964282669127</v>
+      </c>
+    </row>
+    <row r="728" spans="1:2">
+      <c r="A728">
+        <v>726</v>
+      </c>
+      <c r="B728">
+        <v>0.0007436819141730666</v>
+      </c>
+    </row>
+    <row r="729" spans="1:2">
+      <c r="A729">
+        <v>727</v>
+      </c>
+      <c r="B729">
+        <v>0.0006632941658608615</v>
+      </c>
+    </row>
+    <row r="730" spans="1:2">
+      <c r="A730">
+        <v>728</v>
+      </c>
+      <c r="B730">
+        <v>-0.0005123512237332761</v>
+      </c>
+    </row>
+    <row r="731" spans="1:2">
+      <c r="A731">
+        <v>729</v>
+      </c>
+      <c r="B731">
+        <v>0.0005611816304735839</v>
+      </c>
+    </row>
+    <row r="732" spans="1:2">
+      <c r="A732">
+        <v>730</v>
+      </c>
+      <c r="B732">
+        <v>0.0001594800705788657</v>
+      </c>
+    </row>
+    <row r="733" spans="1:2">
+      <c r="A733">
+        <v>731</v>
+      </c>
+      <c r="B733">
+        <v>-0.0008008689037524164</v>
+      </c>
+    </row>
+    <row r="734" spans="1:2">
+      <c r="A734">
+        <v>732</v>
+      </c>
+      <c r="B734">
+        <v>0.00532642612233758</v>
+      </c>
+    </row>
+    <row r="735" spans="1:2">
+      <c r="A735">
+        <v>733</v>
+      </c>
+      <c r="B735">
+        <v>0.001398843131028116</v>
+      </c>
+    </row>
+    <row r="736" spans="1:2">
+      <c r="A736">
+        <v>734</v>
+      </c>
+      <c r="B736">
+        <v>0.0004009448166470975</v>
+      </c>
+    </row>
+    <row r="737" spans="1:2">
+      <c r="A737">
+        <v>735</v>
+      </c>
+      <c r="B737">
+        <v>0.0001279043935937807</v>
+      </c>
+    </row>
+    <row r="738" spans="1:2">
+      <c r="A738">
+        <v>736</v>
+      </c>
+      <c r="B738">
+        <v>0.0004744110046885908</v>
+      </c>
+    </row>
+    <row r="739" spans="1:2">
+      <c r="A739">
+        <v>737</v>
+      </c>
+      <c r="B739">
+        <v>0.0003795308875851333</v>
+      </c>
+    </row>
+    <row r="740" spans="1:2">
+      <c r="A740">
+        <v>738</v>
+      </c>
+      <c r="B740">
+        <v>0.0001128152798628435</v>
+      </c>
+    </row>
+    <row r="741" spans="1:2">
+      <c r="A741">
+        <v>739</v>
+      </c>
+      <c r="B741">
+        <v>0.0001811007095966488</v>
+      </c>
+    </row>
+    <row r="742" spans="1:2">
+      <c r="A742">
+        <v>740</v>
+      </c>
+      <c r="B742">
+        <v>8.276686276076362E-05</v>
+      </c>
+    </row>
+    <row r="743" spans="1:2">
+      <c r="A743">
+        <v>741</v>
+      </c>
+      <c r="B743">
+        <v>0.000456392765045166</v>
+      </c>
+    </row>
+    <row r="744" spans="1:2">
+      <c r="A744">
+        <v>742</v>
+      </c>
+      <c r="B744">
+        <v>-0.000113694833999034</v>
+      </c>
+    </row>
+    <row r="745" spans="1:2">
+      <c r="A745">
+        <v>743</v>
+      </c>
+      <c r="B745">
+        <v>0.0006223706295713782</v>
+      </c>
+    </row>
+    <row r="746" spans="1:2">
+      <c r="A746">
+        <v>744</v>
+      </c>
+      <c r="B746">
+        <v>-0.0008635313133709133</v>
+      </c>
+    </row>
+    <row r="747" spans="1:2">
+      <c r="A747">
+        <v>745</v>
+      </c>
+      <c r="B747">
+        <v>0.003526360495015979</v>
+      </c>
+    </row>
+    <row r="748" spans="1:2">
+      <c r="A748">
+        <v>746</v>
+      </c>
+      <c r="B748">
+        <v>0.00111051497515291</v>
+      </c>
+    </row>
+    <row r="749" spans="1:2">
+      <c r="A749">
+        <v>747</v>
+      </c>
+      <c r="B749">
+        <v>0.001664008595980704</v>
+      </c>
+    </row>
+    <row r="750" spans="1:2">
+      <c r="A750">
+        <v>748</v>
+      </c>
+      <c r="B750">
+        <v>0.0002916860685218126</v>
+      </c>
+    </row>
+    <row r="751" spans="1:2">
+      <c r="A751">
+        <v>749</v>
+      </c>
+      <c r="B751">
+        <v>0.0004949700669385493</v>
+      </c>
+    </row>
+    <row r="752" spans="1:2">
+      <c r="A752">
+        <v>750</v>
+      </c>
+      <c r="B752">
+        <v>-0.0002781871880870312</v>
+      </c>
+    </row>
+    <row r="753" spans="1:2">
+      <c r="A753">
+        <v>751</v>
+      </c>
+      <c r="B753">
+        <v>0.0002306015958311036</v>
+      </c>
+    </row>
+    <row r="754" spans="1:2">
+      <c r="A754">
+        <v>752</v>
+      </c>
+      <c r="B754">
+        <v>0.00095987698296085</v>
+      </c>
+    </row>
+    <row r="755" spans="1:2">
+      <c r="A755">
+        <v>753</v>
+      </c>
+      <c r="B755">
+        <v>0.000231796846492216</v>
+      </c>
+    </row>
+    <row r="756" spans="1:2">
+      <c r="A756">
+        <v>754</v>
+      </c>
+      <c r="B756">
+        <v>0.0003534677380230278</v>
+      </c>
+    </row>
+    <row r="757" spans="1:2">
+      <c r="A757">
+        <v>755</v>
+      </c>
+      <c r="B757">
+        <v>0.0006857239059172571</v>
+      </c>
+    </row>
+    <row r="758" spans="1:2">
+      <c r="A758">
+        <v>756</v>
+      </c>
+      <c r="B758">
+        <v>0.0001180608596769162</v>
+      </c>
+    </row>
+    <row r="759" spans="1:2">
+      <c r="A759">
+        <v>757</v>
+      </c>
+      <c r="B759">
+        <v>0.0006453015957958996</v>
+      </c>
+    </row>
+    <row r="760" spans="1:2">
+      <c r="A760">
+        <v>758</v>
+      </c>
+      <c r="B760">
+        <v>-0.001817171229049563</v>
+      </c>
+    </row>
+    <row r="761" spans="1:2">
+      <c r="A761">
+        <v>759</v>
+      </c>
+      <c r="B761">
+        <v>0.0006331720505841076</v>
+      </c>
+    </row>
+    <row r="762" spans="1:2">
+      <c r="A762">
+        <v>760</v>
+      </c>
+      <c r="B762">
+        <v>9.916380804497749E-05</v>
+      </c>
+    </row>
+    <row r="763" spans="1:2">
+      <c r="A763">
+        <v>761</v>
+      </c>
+      <c r="B763">
+        <v>0.0001254657545359805</v>
+      </c>
+    </row>
+    <row r="764" spans="1:2">
+      <c r="A764">
+        <v>762</v>
+      </c>
+      <c r="B764">
+        <v>0.0001813518319977447</v>
+      </c>
+    </row>
+    <row r="765" spans="1:2">
+      <c r="A765">
+        <v>763</v>
+      </c>
+      <c r="B765">
+        <v>-9.29446287045721E-06</v>
+      </c>
+    </row>
+    <row r="766" spans="1:2">
+      <c r="A766">
+        <v>764</v>
+      </c>
+      <c r="B766">
+        <v>0.0007343748002313077</v>
+      </c>
+    </row>
+    <row r="767" spans="1:2">
+      <c r="A767">
+        <v>765</v>
+      </c>
+      <c r="B767">
+        <v>0.002335076685994864</v>
+      </c>
+    </row>
+    <row r="768" spans="1:2">
+      <c r="A768">
+        <v>766</v>
+      </c>
+      <c r="B768">
+        <v>0.0006813422660343349</v>
+      </c>
+    </row>
+    <row r="769" spans="1:2">
+      <c r="A769">
+        <v>767</v>
+      </c>
+      <c r="B769">
+        <v>-9.496595157543197E-05</v>
+      </c>
+    </row>
+    <row r="770" spans="1:2">
+      <c r="A770">
+        <v>768</v>
+      </c>
+      <c r="B770">
+        <v>0.0003137795720249414</v>
+      </c>
+    </row>
+    <row r="771" spans="1:2">
+      <c r="A771">
+        <v>769</v>
+      </c>
+      <c r="B771">
+        <v>0.0006163718062452972</v>
+      </c>
+    </row>
+    <row r="772" spans="1:2">
+      <c r="A772">
+        <v>770</v>
+      </c>
+      <c r="B772">
+        <v>-0.0001058563648257405</v>
+      </c>
+    </row>
+    <row r="773" spans="1:2">
+      <c r="A773">
+        <v>771</v>
+      </c>
+      <c r="B773">
+        <v>-5.819863145006821E-05</v>
+      </c>
+    </row>
+    <row r="774" spans="1:2">
+      <c r="A774">
+        <v>772</v>
+      </c>
+      <c r="B774">
+        <v>0.0005662196781486273</v>
+      </c>
+    </row>
+    <row r="775" spans="1:2">
+      <c r="A775">
+        <v>773</v>
+      </c>
+      <c r="B775">
+        <v>0.001369744190014899</v>
+      </c>
+    </row>
+    <row r="776" spans="1:2">
+      <c r="A776">
+        <v>774</v>
+      </c>
+      <c r="B776">
+        <v>0.001483570667915046</v>
+      </c>
+    </row>
+    <row r="777" spans="1:2">
+      <c r="A777">
+        <v>775</v>
+      </c>
+      <c r="B777">
+        <v>-9.743378177518025E-05</v>
+      </c>
+    </row>
+    <row r="778" spans="1:2">
+      <c r="A778">
+        <v>776</v>
+      </c>
+      <c r="B778">
+        <v>0.0002995313552673906</v>
+      </c>
+    </row>
+    <row r="779" spans="1:2">
+      <c r="A779">
+        <v>777</v>
+      </c>
+      <c r="B779">
+        <v>0.0001213588257087395</v>
+      </c>
+    </row>
+    <row r="780" spans="1:2">
+      <c r="A780">
+        <v>778</v>
+      </c>
+      <c r="B780">
+        <v>0.001651629107072949</v>
+      </c>
+    </row>
+    <row r="781" spans="1:2">
+      <c r="A781">
+        <v>779</v>
+      </c>
+      <c r="B781">
+        <v>0.00068812002427876</v>
+      </c>
+    </row>
+    <row r="782" spans="1:2">
+      <c r="A782">
+        <v>780</v>
+      </c>
+      <c r="B782">
+        <v>-4.835756408283487E-05</v>
+      </c>
+    </row>
+    <row r="783" spans="1:2">
+      <c r="A783">
+        <v>781</v>
+      </c>
+      <c r="B783">
+        <v>0.001102247158996761</v>
+      </c>
+    </row>
+    <row r="784" spans="1:2">
+      <c r="A784">
+        <v>782</v>
+      </c>
+      <c r="B784">
+        <v>0.0004829906101804227</v>
+      </c>
+    </row>
+    <row r="785" spans="1:2">
+      <c r="A785">
+        <v>783</v>
+      </c>
+      <c r="B785">
+        <v>-0.0001874268637038767</v>
+      </c>
+    </row>
+    <row r="786" spans="1:2">
+      <c r="A786">
+        <v>784</v>
+      </c>
+      <c r="B786">
+        <v>4.019212792627513E-05</v>
+      </c>
+    </row>
+    <row r="787" spans="1:2">
+      <c r="A787">
+        <v>785</v>
+      </c>
+      <c r="B787">
+        <v>0.000351620459696278</v>
+      </c>
+    </row>
+    <row r="788" spans="1:2">
+      <c r="A788">
+        <v>786</v>
+      </c>
+      <c r="B788">
+        <v>0.0004774284607265145</v>
+      </c>
+    </row>
+    <row r="789" spans="1:2">
+      <c r="A789">
+        <v>787</v>
+      </c>
+      <c r="B789">
+        <v>-0.0002142315497621894</v>
+      </c>
+    </row>
+    <row r="790" spans="1:2">
+      <c r="A790">
+        <v>788</v>
+      </c>
+      <c r="B790">
+        <v>0.0001392668345943093</v>
+      </c>
+    </row>
+    <row r="791" spans="1:2">
+      <c r="A791">
+        <v>789</v>
+      </c>
+      <c r="B791">
+        <v>0.0006404263549484313</v>
+      </c>
+    </row>
+    <row r="792" spans="1:2">
+      <c r="A792">
+        <v>790</v>
+      </c>
+      <c r="B792">
+        <v>0.0004149631422478706</v>
+      </c>
+    </row>
+    <row r="793" spans="1:2">
+      <c r="A793">
+        <v>791</v>
+      </c>
+      <c r="B793">
+        <v>0.001520326593890786</v>
+      </c>
+    </row>
+    <row r="794" spans="1:2">
+      <c r="A794">
+        <v>792</v>
+      </c>
+      <c r="B794">
+        <v>0.0004929988062940538</v>
+      </c>
+    </row>
+    <row r="795" spans="1:2">
+      <c r="A795">
+        <v>793</v>
+      </c>
+      <c r="B795">
+        <v>0.0004783714830409735</v>
+      </c>
+    </row>
+    <row r="796" spans="1:2">
+      <c r="A796">
+        <v>794</v>
+      </c>
+      <c r="B796">
+        <v>-0.0001006863967631944</v>
+      </c>
+    </row>
+    <row r="797" spans="1:2">
+      <c r="A797">
+        <v>795</v>
+      </c>
+      <c r="B797">
+        <v>0.0003901627787854522</v>
+      </c>
+    </row>
+    <row r="798" spans="1:2">
+      <c r="A798">
+        <v>796</v>
+      </c>
+      <c r="B798">
+        <v>-0.0004388128581922501</v>
+      </c>
+    </row>
+    <row r="799" spans="1:2">
+      <c r="A799">
+        <v>797</v>
+      </c>
+      <c r="B799">
+        <v>-0.0002565384493209422</v>
+      </c>
+    </row>
+    <row r="800" spans="1:2">
+      <c r="A800">
+        <v>798</v>
+      </c>
+      <c r="B800">
+        <v>-0.0002598847786430269</v>
+      </c>
+    </row>
+    <row r="801" spans="1:2">
+      <c r="A801">
+        <v>799</v>
+      </c>
+      <c r="B801">
+        <v>0.0005375074688345194</v>
+      </c>
+    </row>
+    <row r="802" spans="1:2">
+      <c r="A802">
+        <v>800</v>
+      </c>
+      <c r="B802">
+        <v>0.0002142493904102594</v>
+      </c>
+    </row>
+    <row r="803" spans="1:2">
+      <c r="A803">
+        <v>801</v>
+      </c>
+      <c r="B803">
+        <v>-0.0002327998081455007</v>
+      </c>
+    </row>
+    <row r="804" spans="1:2">
+      <c r="A804">
+        <v>802</v>
+      </c>
+      <c r="B804">
+        <v>-0.000183026771992445</v>
+      </c>
+    </row>
+    <row r="805" spans="1:2">
+      <c r="A805">
+        <v>803</v>
+      </c>
+      <c r="B805">
+        <v>-9.213751764036715E-05</v>
+      </c>
+    </row>
+    <row r="806" spans="1:2">
+      <c r="A806">
+        <v>804</v>
+      </c>
+      <c r="B806">
+        <v>0.001345350057817996</v>
+      </c>
+    </row>
+    <row r="807" spans="1:2">
+      <c r="A807">
+        <v>805</v>
+      </c>
+      <c r="B807">
+        <v>-0.0002801870869006962</v>
+      </c>
+    </row>
+    <row r="808" spans="1:2">
+      <c r="A808">
+        <v>806</v>
+      </c>
+      <c r="B808">
+        <v>0.001004044432193041</v>
+      </c>
+    </row>
+    <row r="809" spans="1:2">
+      <c r="A809">
+        <v>807</v>
+      </c>
+      <c r="B809">
+        <v>0.000561326858587563</v>
+      </c>
+    </row>
+    <row r="810" spans="1:2">
+      <c r="A810">
+        <v>808</v>
+      </c>
+      <c r="B810">
+        <v>0.0001896687463158742</v>
+      </c>
+    </row>
+    <row r="811" spans="1:2">
+      <c r="A811">
+        <v>809</v>
+      </c>
+      <c r="B811">
+        <v>2.076129567285534E-05</v>
+      </c>
+    </row>
+    <row r="812" spans="1:2">
+      <c r="A812">
+        <v>810</v>
+      </c>
+      <c r="B812">
+        <v>0.001297351787798107</v>
+      </c>
+    </row>
+    <row r="813" spans="1:2">
+      <c r="A813">
+        <v>811</v>
+      </c>
+      <c r="B813">
+        <v>0.0009853440569713712</v>
+      </c>
+    </row>
+    <row r="814" spans="1:2">
+      <c r="A814">
+        <v>812</v>
+      </c>
+      <c r="B814">
+        <v>0.0003898486320395023</v>
+      </c>
+    </row>
+    <row r="815" spans="1:2">
+      <c r="A815">
+        <v>813</v>
+      </c>
+      <c r="B815">
+        <v>0.001324190758168697</v>
+      </c>
+    </row>
+    <row r="816" spans="1:2">
+      <c r="A816">
+        <v>814</v>
+      </c>
+      <c r="B816">
+        <v>0.0008810095605440438</v>
+      </c>
+    </row>
+    <row r="817" spans="1:2">
+      <c r="A817">
+        <v>815</v>
+      </c>
+      <c r="B817">
+        <v>0.0004278002306818962</v>
+      </c>
+    </row>
+    <row r="818" spans="1:2">
+      <c r="A818">
+        <v>816</v>
+      </c>
+      <c r="B818">
+        <v>-0.0003162099455948919</v>
+      </c>
+    </row>
+    <row r="819" spans="1:2">
+      <c r="A819">
+        <v>817</v>
+      </c>
+      <c r="B819">
+        <v>0.001115376478992403</v>
       </c>
     </row>
   </sheetData>
@@ -8934,12 +15478,508 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1"/>
+  <dimension ref="A1:B63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:2">
+    <row r="1" spans="1:2">
       <c r="B1" t="s">
         <v>471</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>-0.001678228378295898</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0.002998948097229004</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0.0002199411392211914</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>0.00455474853515625</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>0.003274679183959961</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>0.004258394241333008</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>0.002000808715820312</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>0.0006799697875976562</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>0.006761431694030762</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>0.004412174224853516</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>0.004941463470458984</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>0.005082368850708008</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>0.006615400314331055</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>0.003221750259399414</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>0.007399916648864746</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>0.001956820487976074</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>0.001743316650390625</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <v>0.005417943000793457</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <v>0.004966497421264648</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21">
+        <v>0.006249785423278809</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <v>0.002646565437316895</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23">
+        <v>8.428096771240234E-05</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24">
+        <v>0.002617001533508301</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25">
+        <v>0.002780318260192871</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26">
+        <v>0.002905011177062988</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27">
+        <v>0.008772850036621094</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28">
+        <v>0.004014492034912109</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29">
+        <v>0.006342291831970215</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30">
+        <v>0.005237460136413574</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31">
+        <v>0.007218837738037109</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32">
+        <v>0.004291772842407227</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33">
+        <v>0.003724932670593262</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34">
+        <v>0.007697820663452148</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35">
+        <v>0.0103604793548584</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36">
+        <v>0.001282215118408203</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37">
+        <v>0.007484674453735352</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38">
+        <v>0.008269548416137695</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39">
+        <v>0.003863215446472168</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40">
+        <v>0.006082415580749512</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41">
+        <v>0.002854466438293457</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42">
+        <v>0.007142782211303711</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43">
+        <v>0.006049156188964844</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44">
+        <v>0.006934523582458496</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45">
+        <v>-0.001187622547149658</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46">
+        <v>0.01189124584197998</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47">
+        <v>0.004649758338928223</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48">
+        <v>0.0196688175201416</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49">
+        <v>0.002209782600402832</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50">
+        <v>0.005372047424316406</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51">
+        <v>0.006968498229980469</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52">
+        <v>0.0037994384765625</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53">
+        <v>0.002999305725097656</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54">
+        <v>0.006283760070800781</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55">
+        <v>0.004909873008728027</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56">
+        <v>0.007625818252563477</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="B57">
+        <v>0.00494539737701416</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="B58">
+        <v>0.007907390594482422</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="B59">
+        <v>0.008358359336853027</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="B60">
+        <v>0.00477147102355957</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61">
+        <v>59</v>
+      </c>
+      <c r="B61">
+        <v>0.006772398948669434</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="B62">
+        <v>0.005223512649536133</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="B63">
+        <v>0.001120686531066895</v>
       </c>
     </row>
   </sheetData>
@@ -8949,12 +15989,108 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:2">
+    <row r="1" spans="1:2">
       <c r="B1" t="s">
         <v>471</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.009392380714416504</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0.0182337760925293</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0.02755355834960938</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>0.02049136161804199</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>0.01107954978942871</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>0.03198063373565674</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>0.02763283252716064</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>0.02887153625488281</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>0.03116750717163086</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>0.03938186168670654</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>0.02587497234344482</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>0.03318107128143311</v>
       </c>
     </row>
   </sheetData>
